--- a/output/weekly_tracker.xlsx
+++ b/output/weekly_tracker.xlsx
@@ -1929,17 +1929,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H18"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1981,516 +1981,6 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Detected At</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Converse</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Mar 5 Converse x Hello Kitty Chuck Taylor 70 Swarovski®</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-03-06T05:03:21Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-03-05</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Mar 5 Toddler Shoes Nike Little Max '95</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-03-06T05:03:21Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-03-06T05:03:21Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Air Jordan 4 Imperial Purple</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-03-06T05:03:21Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Air Max 95 Big Bubble Neon Yellow</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-03-06T05:03:21Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Air Max Ishod Iron Grey and Photon Dust</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2026-03-06T05:03:21Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Converse</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Converse x Hello Kitty Chuck Taylor 70 Swarovski®</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2026-03-06T05:03:21Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Nike SB Ishod Apparel Collection</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2026-03-06T05:03:21Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2026-03-06T05:03:21Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Air Jordan 4 Imperial Purple</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2026-03-06T05:03:21Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Air Max Ishod Iron Grey and Photon Dust</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2026-03-06T05:03:21Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Converse</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Converse x Hello Kitty Chuck Taylor 70 Swarovski®</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2026-03-06T05:03:21Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Nike SB Ishod Apparel Collection</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2026-03-06T05:03:21Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Zoom Vomero 5 Hyper Royal</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2026-03-06T05:03:21Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Mar 10 Zoom Vomero 5 Hyper Royal</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2026-03-06T05:03:21Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-03-27</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Mar 27 Baby/Toddler Shoes Nike Little Posite Pro</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2026-03-06T05:03:21Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Apr 3 Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>2026-03-06T05:03:21Z</t>
         </is>
       </c>
     </row>

--- a/output/weekly_tracker.xlsx
+++ b/output/weekly_tracker.xlsx
@@ -7639,17 +7639,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="13" customWidth="1" min="3" max="3"/>
-    <col width="60" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7691,1746 +7691,6 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Detected At</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Adidas</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>CLOT by Edison Chen x adidas Superstar DS 'Coffee'</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Nike Air Max 95 WMNS 'Soft Yellow' From £ 185</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Nike Astra Ultra WMNS 'Black' From £ 100</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Patta x Nike Air Max 1 ’87 'Hyper Crimson' From £ 150</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Solebox x Clarks Wallabee 'Black'</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Adidas</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Adidas Anthony Edwards 2 Georgia Bulldogs</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Air Jordan 1 High OG Pale Ivory / Psychic Blue</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Air Jordan 1 High OG WMNS 'Psychic Blue' From £ 163</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Air Jordan 1 Low OG 'Rabbit Floral Swoosh' From £ 145</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Air Jordan 1 Low OG Sail / Off White</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Air Jordan 4 GS Imperial Purple / Multi</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Air Jordan 4 OG Lakers</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Adidas</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Clot x Adidas Superstar Footwear White / Coffee</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NAKED Copenhagen x Nike Shox Z 'Metallic Hematite Grey'</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>NAKED Copenhagen x Nike Shox Z Calistra 'Black'</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Nike Air Max 95 Zip 'Phantom &amp; Light Crimson' From £ 185</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Nike Shox Ride 2 Black / Metallic Dark Grey</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Jacquemus x Nike Moon Shoe SP 'Fauna Brown' From £ 163</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Jacquemus x Nike Moon Shoe SP 'Soft Pearl' From £ 163</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Jacquemus x Nike Moon Soft Pearl / Sail</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Balenciaga 3xl Split Logo Eggshell / Red</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Balenciaga 3xl Split Logo White / Navy</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Balenciaga Basketball Mule Silver / Black</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Balenciaga City Balenciaga Grey</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Balenciaga City WMNS Petal Pink</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Balenciaga City WMNS Silver</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Balenciaga Hamptons Medium Worn-Out WMNS Pink / White</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Balenciaga Hamptons Platform WMNS White</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Balenciaga Monday Ultra Black</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Balenciaga Runner WMNS Blue / Yellow</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Balenciaga Speed 2.0 Full Clear Sole Recycled Knit WMNS Black / Beige</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Balenciaga Track Piercing Black</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Balenciaga Track Signature WMNS Beige / Pink</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Balenciaga Track Trail Laces White / Red</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Balenciaga Triple S Canvas Blue</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Balenciaga Triple S Sporty Suede WMNS Brown</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>New Balance</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>New Balance 1890 'Faded Black &amp; Utility Green' From £ 160</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>New Balance</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>New Balance ABZORB 2000 'Grey Matter' From £ 170</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>New Balance</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>New Balance ABZORB 2000 'Ice Wine' From £ 170</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-03-11</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Nike Vomero Premium 'Black' From £ 200</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>ASICS</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>ASICS GEL-KAYANO 14 'Light Navy' From £ 154</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>New Balance</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>New Balance 993 Made in USA 'Passion Fruit' From £ 205</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Nike Air Force 1 ’07 'Cherry Blossom' From £ 120</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Nike Air Max 95 'Paisley Bandana' From £ 180</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Nike Air Force 1 Low 'Asparagus &amp; Chlorophyll' From £ 118</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Veneda Carter x Nike Air Max Muse 'White &amp; Racer Blue' From £ 145</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Air Jordan 13 Retro 'True Red' - 2026 From £ 185</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Air Jordan 9 Retro 'Flint Grey' - 2026 From £ 190</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2026-03-14</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Travis Scott x Air Jordan Jumpman Jack 'Green Spark' From £ 185</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Crocs</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>One Piece x Crocs Classic Clog 'Zoro'</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2026-03-19</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>New Balance</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>New Balance 991v1 Made in UK 'Oyster Grey' From £ 220</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>New Balance</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>New Balance 1890 'Star Burst' From £ 160</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2026-03-26</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Crocs</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>One Piece x Crocs Classic Clog 'Thousand Sunny'</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2026-03-28</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Air Jordan 3 'Spring Is In The Air' From £ 190</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Nike Mind 001 Pregame Mule 'Light Smoke Grey' From £ 80</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Nike Mind 001 Slide 'Black' From £ 80</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Nike Mind 001 WMNS Pregame Mules 'Black' From £ 80</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Nike Mind 001 WMNS Pregame Mules 'Light Smoke Grey' From £ 80</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>2026-03-06T07:44:41Z</t>
         </is>
       </c>
     </row>

--- a/output/weekly_tracker.xlsx
+++ b/output/weekly_tracker.xlsx
@@ -2557,7 +2557,7 @@
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Platform WMNS White</t>
+          <t>Balenciaga Hamptons Platform WMNS Black</t>
         </is>
       </c>
       <c r="H40" s="10" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="K40" s="10" t="inlineStr">
         <is>
-          <t>/balenciaga-hamptons-platform-wmns-white</t>
+          <t>/balenciaga-hamptons-platform-wmns-black</t>
         </is>
       </c>
       <c r="L40" s="10" t="inlineStr"/>
@@ -2611,10 +2611,14 @@
       </c>
       <c r="G41" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Monday Ultra Black</t>
-        </is>
-      </c>
-      <c r="H41" s="10" t="inlineStr"/>
+          <t>Balenciaga Hamptons Platform WMNS White</t>
+        </is>
+      </c>
+      <c r="H41" s="10" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I41" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -2627,7 +2631,7 @@
       </c>
       <c r="K41" s="10" t="inlineStr">
         <is>
-          <t>/balenciaga-monday-ultra-black</t>
+          <t>/balenciaga-hamptons-platform-wmns-white</t>
         </is>
       </c>
       <c r="L41" s="10" t="inlineStr"/>
@@ -2661,14 +2665,10 @@
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Runner WMNS Blue / Yellow</t>
-        </is>
-      </c>
-      <c r="H42" s="10" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Balenciaga Monday Ultra Black</t>
+        </is>
+      </c>
+      <c r="H42" s="10" t="inlineStr"/>
       <c r="I42" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="K42" s="10" t="inlineStr">
         <is>
-          <t>/balenciaga-runner-wmns-blue-yellow</t>
+          <t>/balenciaga-monday-ultra-black</t>
         </is>
       </c>
       <c r="L42" s="10" t="inlineStr"/>
@@ -2715,12 +2715,12 @@
       </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Speed 2.0 Full Clear Sole Recycled Knit WMNS Black / Beige</t>
+          <t>Balenciaga Runner WMNS Blue / Yellow</t>
         </is>
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>women, exclusive</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I43" s="9" t="inlineStr">
@@ -2735,7 +2735,7 @@
       </c>
       <c r="K43" s="10" t="inlineStr">
         <is>
-          <t>/balenciaga-speed-2-0-full-clear-sole-recycled-knit-wmns-black-beige</t>
+          <t>/balenciaga-runner-wmns-blue-yellow</t>
         </is>
       </c>
       <c r="L43" s="10" t="inlineStr"/>
@@ -2769,10 +2769,14 @@
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Track Piercing Black</t>
-        </is>
-      </c>
-      <c r="H44" s="10" t="inlineStr"/>
+          <t>Balenciaga Speed 2.0 Full Clear Sole Recycled Knit WMNS Black / Beige</t>
+        </is>
+      </c>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>women, exclusive</t>
+        </is>
+      </c>
       <c r="I44" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -2785,7 +2789,7 @@
       </c>
       <c r="K44" s="10" t="inlineStr">
         <is>
-          <t>/balenciaga-track-piercing-black</t>
+          <t>/balenciaga-speed-2-0-full-clear-sole-recycled-knit-wmns-black-beige</t>
         </is>
       </c>
       <c r="L44" s="10" t="inlineStr"/>
@@ -2819,14 +2823,10 @@
       </c>
       <c r="G45" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Track Signature WMNS Beige / Pink</t>
-        </is>
-      </c>
-      <c r="H45" s="10" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Balenciaga Track Piercing Black</t>
+        </is>
+      </c>
+      <c r="H45" s="10" t="inlineStr"/>
       <c r="I45" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="K45" s="10" t="inlineStr">
         <is>
-          <t>/balenciaga-track-signature-wmns-beige-pink</t>
+          <t>/balenciaga-track-piercing-black</t>
         </is>
       </c>
       <c r="L45" s="10" t="inlineStr"/>
@@ -2873,10 +2873,14 @@
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Track Trail Laces White / Red</t>
-        </is>
-      </c>
-      <c r="H46" s="10" t="inlineStr"/>
+          <t>Balenciaga Track Signature WMNS Beige / Pink</t>
+        </is>
+      </c>
+      <c r="H46" s="10" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I46" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -2889,7 +2893,7 @@
       </c>
       <c r="K46" s="10" t="inlineStr">
         <is>
-          <t>/balenciaga-track-trail-laces-white-red</t>
+          <t>/balenciaga-track-signature-wmns-beige-pink</t>
         </is>
       </c>
       <c r="L46" s="10" t="inlineStr"/>
@@ -2923,7 +2927,7 @@
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Triple S Canvas Blue</t>
+          <t>Balenciaga Track Trail Laces White / Red</t>
         </is>
       </c>
       <c r="H47" s="10" t="inlineStr"/>
@@ -2939,7 +2943,7 @@
       </c>
       <c r="K47" s="10" t="inlineStr">
         <is>
-          <t>/balenciaga-triple-s-canvas-blue</t>
+          <t>/balenciaga-track-trail-laces-white-red</t>
         </is>
       </c>
       <c r="L47" s="10" t="inlineStr"/>
@@ -2973,14 +2977,10 @@
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Triple S Sporty Suede WMNS Brown</t>
-        </is>
-      </c>
-      <c r="H48" s="10" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Balenciaga Triple S Canvas Blue</t>
+        </is>
+      </c>
+      <c r="H48" s="10" t="inlineStr"/>
       <c r="I48" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -2993,7 +2993,7 @@
       </c>
       <c r="K48" s="10" t="inlineStr">
         <is>
-          <t>/balenciaga-triple-s-sporty-suede-wmns-brown</t>
+          <t>/balenciaga-triple-s-canvas-blue</t>
         </is>
       </c>
       <c r="L48" s="10" t="inlineStr"/>
@@ -5937,7 +5937,7 @@
       </c>
       <c r="G40" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Platform WMNS White</t>
+          <t>Balenciaga Hamptons Platform WMNS Black</t>
         </is>
       </c>
       <c r="H40" s="10" t="inlineStr">
@@ -5957,7 +5957,7 @@
       </c>
       <c r="K40" s="10" t="inlineStr">
         <is>
-          <t>/balenciaga-hamptons-platform-wmns-white</t>
+          <t>/balenciaga-hamptons-platform-wmns-black</t>
         </is>
       </c>
       <c r="L40" s="10" t="inlineStr"/>
@@ -5991,10 +5991,14 @@
       </c>
       <c r="G41" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Monday Ultra Black</t>
-        </is>
-      </c>
-      <c r="H41" s="10" t="inlineStr"/>
+          <t>Balenciaga Hamptons Platform WMNS White</t>
+        </is>
+      </c>
+      <c r="H41" s="10" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I41" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -6007,7 +6011,7 @@
       </c>
       <c r="K41" s="10" t="inlineStr">
         <is>
-          <t>/balenciaga-monday-ultra-black</t>
+          <t>/balenciaga-hamptons-platform-wmns-white</t>
         </is>
       </c>
       <c r="L41" s="10" t="inlineStr"/>
@@ -6041,14 +6045,10 @@
       </c>
       <c r="G42" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Runner WMNS Blue / Yellow</t>
-        </is>
-      </c>
-      <c r="H42" s="10" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Balenciaga Monday Ultra Black</t>
+        </is>
+      </c>
+      <c r="H42" s="10" t="inlineStr"/>
       <c r="I42" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="K42" s="10" t="inlineStr">
         <is>
-          <t>/balenciaga-runner-wmns-blue-yellow</t>
+          <t>/balenciaga-monday-ultra-black</t>
         </is>
       </c>
       <c r="L42" s="10" t="inlineStr"/>
@@ -6095,12 +6095,12 @@
       </c>
       <c r="G43" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Speed 2.0 Full Clear Sole Recycled Knit WMNS Black / Beige</t>
+          <t>Balenciaga Runner WMNS Blue / Yellow</t>
         </is>
       </c>
       <c r="H43" s="10" t="inlineStr">
         <is>
-          <t>women, exclusive</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I43" s="9" t="inlineStr">
@@ -6115,7 +6115,7 @@
       </c>
       <c r="K43" s="10" t="inlineStr">
         <is>
-          <t>/balenciaga-speed-2-0-full-clear-sole-recycled-knit-wmns-black-beige</t>
+          <t>/balenciaga-runner-wmns-blue-yellow</t>
         </is>
       </c>
       <c r="L43" s="10" t="inlineStr"/>
@@ -6149,10 +6149,14 @@
       </c>
       <c r="G44" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Track Piercing Black</t>
-        </is>
-      </c>
-      <c r="H44" s="10" t="inlineStr"/>
+          <t>Balenciaga Speed 2.0 Full Clear Sole Recycled Knit WMNS Black / Beige</t>
+        </is>
+      </c>
+      <c r="H44" s="10" t="inlineStr">
+        <is>
+          <t>women, exclusive</t>
+        </is>
+      </c>
       <c r="I44" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -6165,7 +6169,7 @@
       </c>
       <c r="K44" s="10" t="inlineStr">
         <is>
-          <t>/balenciaga-track-piercing-black</t>
+          <t>/balenciaga-speed-2-0-full-clear-sole-recycled-knit-wmns-black-beige</t>
         </is>
       </c>
       <c r="L44" s="10" t="inlineStr"/>
@@ -6199,14 +6203,10 @@
       </c>
       <c r="G45" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Track Signature WMNS Beige / Pink</t>
-        </is>
-      </c>
-      <c r="H45" s="10" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Balenciaga Track Piercing Black</t>
+        </is>
+      </c>
+      <c r="H45" s="10" t="inlineStr"/>
       <c r="I45" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -6219,7 +6219,7 @@
       </c>
       <c r="K45" s="10" t="inlineStr">
         <is>
-          <t>/balenciaga-track-signature-wmns-beige-pink</t>
+          <t>/balenciaga-track-piercing-black</t>
         </is>
       </c>
       <c r="L45" s="10" t="inlineStr"/>
@@ -6253,10 +6253,14 @@
       </c>
       <c r="G46" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Track Trail Laces White / Red</t>
-        </is>
-      </c>
-      <c r="H46" s="10" t="inlineStr"/>
+          <t>Balenciaga Track Signature WMNS Beige / Pink</t>
+        </is>
+      </c>
+      <c r="H46" s="10" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I46" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -6269,7 +6273,7 @@
       </c>
       <c r="K46" s="10" t="inlineStr">
         <is>
-          <t>/balenciaga-track-trail-laces-white-red</t>
+          <t>/balenciaga-track-signature-wmns-beige-pink</t>
         </is>
       </c>
       <c r="L46" s="10" t="inlineStr"/>
@@ -6303,7 +6307,7 @@
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Triple S Canvas Blue</t>
+          <t>Balenciaga Track Trail Laces White / Red</t>
         </is>
       </c>
       <c r="H47" s="10" t="inlineStr"/>
@@ -6319,7 +6323,7 @@
       </c>
       <c r="K47" s="10" t="inlineStr">
         <is>
-          <t>/balenciaga-triple-s-canvas-blue</t>
+          <t>/balenciaga-track-trail-laces-white-red</t>
         </is>
       </c>
       <c r="L47" s="10" t="inlineStr"/>
@@ -6353,14 +6357,10 @@
       </c>
       <c r="G48" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Triple S Sporty Suede WMNS Brown</t>
-        </is>
-      </c>
-      <c r="H48" s="10" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Balenciaga Triple S Canvas Blue</t>
+        </is>
+      </c>
+      <c r="H48" s="10" t="inlineStr"/>
       <c r="I48" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -6373,7 +6373,7 @@
       </c>
       <c r="K48" s="10" t="inlineStr">
         <is>
-          <t>/balenciaga-triple-s-sporty-suede-wmns-brown</t>
+          <t>/balenciaga-triple-s-canvas-blue</t>
         </is>
       </c>
       <c r="L48" s="10" t="inlineStr"/>
@@ -7639,17 +7639,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
-    <col width="7" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
+    <col width="45" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="17" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7691,6 +7691,66 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Detected At</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NEW</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Balenciaga Hamptons Platform WMNS Black</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr"/>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2026-03-06T08:00:50Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>REMOVED</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Balenciaga Triple S Sporty Suede WMNS Brown</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-03-06T08:00:50Z</t>
         </is>
       </c>
     </row>
@@ -10033,7 +10093,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Platform WMNS White</t>
+          <t>Balenciaga Hamptons Platform WMNS Black</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -10053,7 +10113,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>/balenciaga-hamptons-platform-wmns-white</t>
+          <t>/balenciaga-hamptons-platform-wmns-black</t>
         </is>
       </c>
       <c r="L38" t="inlineStr"/>
@@ -10095,10 +10155,14 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Balenciaga Monday Ultra Black</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr"/>
+          <t>Balenciaga Hamptons Platform WMNS White</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I39" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -10111,7 +10175,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>/balenciaga-monday-ultra-black</t>
+          <t>/balenciaga-hamptons-platform-wmns-white</t>
         </is>
       </c>
       <c r="L39" t="inlineStr"/>
@@ -10153,14 +10217,10 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Balenciaga Runner WMNS Blue / Yellow</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Balenciaga Monday Ultra Black</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -10173,7 +10233,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>/balenciaga-runner-wmns-blue-yellow</t>
+          <t>/balenciaga-monday-ultra-black</t>
         </is>
       </c>
       <c r="L40" t="inlineStr"/>
@@ -10215,12 +10275,12 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Balenciaga Speed 2.0 Full Clear Sole Recycled Knit WMNS Black / Beige</t>
+          <t>Balenciaga Runner WMNS Blue / Yellow</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>women, exclusive</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -10235,13 +10295,13 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>/balenciaga-speed-2-0-full-clear-sole-recycled-knit-wmns-black-beige</t>
+          <t>/balenciaga-runner-wmns-blue-yellow</t>
         </is>
       </c>
       <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="O41" t="n">
         <v>50</v>
@@ -10277,10 +10337,14 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Balenciaga Track Piercing Black</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr"/>
+          <t>Balenciaga Speed 2.0 Full Clear Sole Recycled Knit WMNS Black / Beige</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>women, exclusive</t>
+        </is>
+      </c>
       <c r="I42" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -10293,13 +10357,13 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>/balenciaga-track-piercing-black</t>
+          <t>/balenciaga-speed-2-0-full-clear-sole-recycled-knit-wmns-black-beige</t>
         </is>
       </c>
       <c r="L42" t="inlineStr"/>
       <c r="M42" t="inlineStr"/>
       <c r="N42" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="O42" t="n">
         <v>50</v>
@@ -10335,14 +10399,10 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Balenciaga Track Signature WMNS Beige / Pink</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Balenciaga Track Piercing Black</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
       <c r="I43" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -10355,7 +10415,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>/balenciaga-track-signature-wmns-beige-pink</t>
+          <t>/balenciaga-track-piercing-black</t>
         </is>
       </c>
       <c r="L43" t="inlineStr"/>
@@ -10397,10 +10457,14 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Balenciaga Track Trail Laces White / Red</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr"/>
+          <t>Balenciaga Track Signature WMNS Beige / Pink</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I44" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -10413,7 +10477,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>/balenciaga-track-trail-laces-white-red</t>
+          <t>/balenciaga-track-signature-wmns-beige-pink</t>
         </is>
       </c>
       <c r="L44" t="inlineStr"/>
@@ -10455,7 +10519,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Balenciaga Triple S Canvas Blue</t>
+          <t>Balenciaga Track Trail Laces White / Red</t>
         </is>
       </c>
       <c r="H45" t="inlineStr"/>
@@ -10471,7 +10535,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>/balenciaga-triple-s-canvas-blue</t>
+          <t>/balenciaga-track-trail-laces-white-red</t>
         </is>
       </c>
       <c r="L45" t="inlineStr"/>
@@ -10513,14 +10577,10 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Balenciaga Triple S Sporty Suede WMNS Brown</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Balenciaga Triple S Canvas Blue</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
       <c r="I46" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -10533,7 +10593,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>/balenciaga-triple-s-sporty-suede-wmns-brown</t>
+          <t>/balenciaga-triple-s-canvas-blue</t>
         </is>
       </c>
       <c r="L46" t="inlineStr"/>

--- a/output/weekly_tracker.xlsx
+++ b/output/weekly_tracker.xlsx
@@ -7639,17 +7639,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="45" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7691,66 +7691,6 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Detected At</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>Balenciaga Hamptons Platform WMNS Black</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr"/>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-03-06T08:00:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Balenciaga Triple S Sporty Suede WMNS Brown</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-03-06T08:00:50Z</t>
         </is>
       </c>
     </row>

--- a/output/weekly_tracker.xlsx
+++ b/output/weekly_tracker.xlsx
@@ -2403,7 +2403,9 @@
       <c r="A36" s="4" t="n">
         <v>46088</v>
       </c>
-      <c r="B36" s="5" t="inlineStr"/>
+      <c r="B36" s="5" t="n">
+        <v>219</v>
+      </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -2513,7 +2515,9 @@
       <c r="A38" s="4" t="n">
         <v>46088</v>
       </c>
-      <c r="B38" s="5" t="inlineStr"/>
+      <c r="B38" s="5" t="n">
+        <v>299</v>
+      </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
           <t>MED</t>
@@ -2912,7 +2916,9 @@
       <c r="A45" s="4" t="n">
         <v>46088</v>
       </c>
-      <c r="B45" s="5" t="inlineStr"/>
+      <c r="B45" s="5" t="n">
+        <v>400</v>
+      </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
           <t>MED</t>
@@ -7397,7 +7403,9 @@
       <c r="A36" s="4" t="n">
         <v>46088</v>
       </c>
-      <c r="B36" s="5" t="inlineStr"/>
+      <c r="B36" s="5" t="n">
+        <v>219</v>
+      </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
           <t>LOW</t>
@@ -7507,7 +7515,9 @@
       <c r="A38" s="4" t="n">
         <v>46088</v>
       </c>
-      <c r="B38" s="5" t="inlineStr"/>
+      <c r="B38" s="5" t="n">
+        <v>299</v>
+      </c>
       <c r="C38" s="11" t="inlineStr">
         <is>
           <t>MED</t>
@@ -7906,7 +7916,9 @@
       <c r="A45" s="4" t="n">
         <v>46088</v>
       </c>
-      <c r="B45" s="5" t="inlineStr"/>
+      <c r="B45" s="5" t="n">
+        <v>400</v>
+      </c>
       <c r="C45" s="11" t="inlineStr">
         <is>
           <t>MED</t>
@@ -10899,17 +10911,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H55"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="20" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="7" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="18" customWidth="1" min="7" max="7"/>
-    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+    <col width="17" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -10951,2274 +10963,6 @@
       <c r="H1" t="inlineStr">
         <is>
           <t>Detected At</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Adidas</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>adidas Anthony Edwards 2 MENS • BLACK/MULTI</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Adidas</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>App entry Nike Grade School Air Griffey Max OG BOYS GRADE SCHOOL • BLUE/BLACK/VOLT</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>App entry Nike Griffey Max 1 MENS • BLUE/BLACK/VOLT</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Crocs</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Crocs Classic Clog One Piece MENS • GREEN/BLACK</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Jordan Air Jordan Retro 1 Hi WOMENS • WHITE/BLUE</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Jordan Retro 4 Imperial Purple MENS • PURPLE/BLACK/YELLOW</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Jordan Retro 1 High OG GIRLS PRE-SCHOOL • PALE IVORY/PSYCHIC BLUE/COCONUT MILK</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Nike Air Force 1 '07 MENS • YELLOW PULSE/PINK FOAM/MULTI</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Nike Air Force 1 BOYS GRADE SCHOOL • YELLOW PULSE/PINK FOAM/EMERALD RISE</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Nike Air Max 95 OG MENS • OFF NOIR/OFF NOIR/BLACK</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Nike Air Max Uptempo '95 MENS • UNIVERSITY RED/WHITE/BLACK</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Nike Dunk Low MENS • EMERALD RISE/YELLOW PULSE/HYDRANGEAS</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Nike Sabrina 3 MENS • YELLOW STRIKE/APPLE GREEN/PALE YELLOW</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>PUMA Hali 1 MENS • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>CONFIDENCE_CHANGED</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Skip To Main</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>confidence</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>PRIORITY_CHANGED</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Jordan Air Jordan Retro 1 Hi WOMENS • WHITE/BLUE</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>priority</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>PRIORITY_CHANGED</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Jordan Retro 4 Imperial Purple MENS • PURPLE/BLACK/YELLOW</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>priority</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>PRIORITY_CHANGED</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Nike Air Max 95 OG MENS • OFF NOIR/OFF NOIR/BLACK</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>priority</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>PRIORITY_CHANGED</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>priority</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>PRIORITY_CHANGED</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Nike Dunk Low MENS • EMERALD RISE/YELLOW PULSE/HYDRANGEAS</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>priority</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Watch</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Adidas</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>adidas Anthony Edwards 2 MENS • BLACK/MULTI</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Adidas</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>App entry Nike Grade School Air Griffey Max OG BOYS GRADE SCHOOL • BLUE/BLACK/VOLT</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>App entry Nike Griffey Max 1 MENS • BLUE/BLACK/VOLT</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Crocs</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Crocs Classic Clog One Piece MENS • GREEN/BLACK</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Jordan Air Jordan Retro 1 Hi WOMENS • WHITE/BLUE</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Jordan Retro 4 Imperial Purple MENS • PURPLE/BLACK/YELLOW</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Jordan Retro 1 High OG GIRLS PRE-SCHOOL • PALE IVORY/PSYCHIC BLUE/COCONUT MILK</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Jordan Retro 13 BOYS GRADE SCHOOL • WHITE/BLACK/TRUE RED</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Nike Air Force 1 '07 MENS • YELLOW PULSE/PINK FOAM/MULTI</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Nike Air Force 1 BOYS GRADE SCHOOL • YELLOW PULSE/PINK FOAM/EMERALD RISE</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Nike Air Max 95 OG MENS • OFF NOIR/OFF NOIR/BLACK</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Nike Air Max Uptempo '95 MENS • UNIVERSITY RED/WHITE/BLACK</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Nike Dunk Low MENS • EMERALD RISE/YELLOW PULSE/HYDRANGEAS</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F48" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Nike Sabrina 3 MENS • YELLOW STRIKE/APPLE GREEN/PALE YELLOW</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>PUMA Hali 1 MENS • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Reebok</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • BLUE/GREEN</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>RETAIL_CHANGED</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2026-03-06</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Skip To Main</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr">
-        <is>
-          <t>retailPrice</t>
-        </is>
-      </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>2026-03-06T09:08:17Z</t>
         </is>
       </c>
     </row>
@@ -15363,7 +13107,7 @@
         <v>46088</v>
       </c>
       <c r="B34" t="n">
-        <v>0</v>
+        <v>219</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -15489,7 +13233,7 @@
         <v>46088</v>
       </c>
       <c r="B36" t="n">
-        <v>0</v>
+        <v>299</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -15944,7 +13688,7 @@
         <v>46088</v>
       </c>
       <c r="B43" t="n">
-        <v>0</v>
+        <v>400</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>

--- a/output/weekly_tracker.xlsx
+++ b/output/weekly_tracker.xlsx
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O81"/>
+  <dimension ref="A1:O82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -780,12 +780,12 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
+          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>hot-model</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
@@ -803,7 +803,7 @@
       </c>
       <c r="L6" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
+          <t>/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
         </is>
       </c>
       <c r="M6" s="10" t="inlineStr"/>
@@ -837,12 +837,12 @@
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>Air Jordan 4 Imperial Purple</t>
+          <t>Air Jordan 13 Retro White and University Red</t>
         </is>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>hot-model, exclusive</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="L7" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-4-imperial-purple</t>
+          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
       <c r="M7" s="10" t="inlineStr"/>
@@ -872,9 +872,9 @@
         <v>46089</v>
       </c>
       <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -889,15 +889,19 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>Converse x Hello Kitty Chuck Taylor 70 Swarovski®</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="inlineStr"/>
+          <t>Air Jordan 4 Imperial Purple</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>hot-model, exclusive</t>
+        </is>
+      </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -913,7 +917,7 @@
       </c>
       <c r="L8" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/converse-hello-kitty-chuck-taylor-70-swarovski</t>
+          <t>/launch/t/air-jordan-4-imperial-purple</t>
         </is>
       </c>
       <c r="M8" s="10" t="inlineStr"/>
@@ -4779,9 +4783,9 @@
         <v>46099</v>
       </c>
       <c r="B79" s="5" t="inlineStr"/>
-      <c r="C79" s="11" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -4796,23 +4800,27 @@
       </c>
       <c r="F79" s="9" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G79" s="10" t="inlineStr">
         <is>
-          <t>One Piece x Crocs Classic Clog 'Zoro'</t>
-        </is>
-      </c>
-      <c r="H79" s="10" t="inlineStr"/>
+          <t>Mar 18 Air Jordan 1 Low OG Sail and Coconut Milk</t>
+        </is>
+      </c>
+      <c r="H79" s="10" t="inlineStr">
+        <is>
+          <t>hot-model</t>
+        </is>
+      </c>
       <c r="I79" s="9" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="J79" s="9" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="K79" s="9" t="n">
@@ -4820,7 +4828,7 @@
       </c>
       <c r="L79" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-zoro-212953-90h/706159</t>
+          <t>/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
         </is>
       </c>
       <c r="M79" s="10" t="inlineStr"/>
@@ -4829,7 +4837,7 @@
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
-        <v>46100</v>
+        <v>46099</v>
       </c>
       <c r="B80" s="5" t="inlineStr"/>
       <c r="C80" s="11" t="inlineStr">
@@ -4849,12 +4857,12 @@
       </c>
       <c r="F80" s="9" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="G80" s="10" t="inlineStr">
         <is>
-          <t>New Balance 991v1 Made in UK 'Oyster Grey' From £ 220</t>
+          <t>One Piece x Crocs Classic Clog 'Zoro'</t>
         </is>
       </c>
       <c r="H80" s="10" t="inlineStr"/>
@@ -4873,7 +4881,7 @@
       </c>
       <c r="L80" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-991v1-made-in-uk-oyster-grey-m991cr1/706155</t>
+          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-zoro-212953-90h/706159</t>
         </is>
       </c>
       <c r="M80" s="10" t="inlineStr"/>
@@ -4882,7 +4890,7 @@
     </row>
     <row r="81">
       <c r="A81" s="4" t="n">
-        <v>46101</v>
+        <v>46100</v>
       </c>
       <c r="B81" s="5" t="inlineStr"/>
       <c r="C81" s="11" t="inlineStr">
@@ -4902,19 +4910,15 @@
       </c>
       <c r="F81" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G81" s="10" t="inlineStr">
         <is>
-          <t>Nike First Sight Noir WMNS 'Black' From £ 110</t>
-        </is>
-      </c>
-      <c r="H81" s="10" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>New Balance 991v1 Made in UK 'Oyster Grey' From £ 220</t>
+        </is>
+      </c>
+      <c r="H81" s="10" t="inlineStr"/>
       <c r="I81" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -4930,12 +4934,69 @@
       </c>
       <c r="L81" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-first-sight-noir-wmns-black-hq2409-001/706328</t>
+          <t>https://thedropdate.com/sneakers/new-balance-991v1-made-in-uk-oyster-grey-m991cr1/706155</t>
         </is>
       </c>
       <c r="M81" s="10" t="inlineStr"/>
       <c r="N81" s="10" t="inlineStr"/>
       <c r="O81" s="5" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" s="4" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B82" s="5" t="inlineStr"/>
+      <c r="C82" s="11" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D82" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E82" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F82" s="9" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G82" s="10" t="inlineStr">
+        <is>
+          <t>Nike First Sight Noir WMNS 'Black' From £ 110</t>
+        </is>
+      </c>
+      <c r="H82" s="10" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I82" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J82" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K82" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L82" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/nike-first-sight-noir-wmns-black-hq2409-001/706328</t>
+        </is>
+      </c>
+      <c r="M82" s="10" t="inlineStr"/>
+      <c r="N82" s="10" t="inlineStr"/>
+      <c r="O82" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5204,12 +5265,12 @@
       </c>
       <c r="G6" s="10" t="inlineStr">
         <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
+          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>hot-model</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
@@ -5227,7 +5288,7 @@
       </c>
       <c r="L6" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
+          <t>/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
         </is>
       </c>
       <c r="M6" s="10" t="inlineStr"/>
@@ -5261,12 +5322,12 @@
       </c>
       <c r="G7" s="10" t="inlineStr">
         <is>
-          <t>Air Jordan 4 Imperial Purple</t>
+          <t>Air Jordan 13 Retro White and University Red</t>
         </is>
       </c>
       <c r="H7" s="10" t="inlineStr">
         <is>
-          <t>hot-model, exclusive</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="I7" s="9" t="inlineStr">
@@ -5284,7 +5345,7 @@
       </c>
       <c r="L7" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-4-imperial-purple</t>
+          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
       <c r="M7" s="10" t="inlineStr"/>
@@ -5296,9 +5357,9 @@
         <v>46089</v>
       </c>
       <c r="B8" s="5" t="inlineStr"/>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D8" s="7" t="inlineStr">
@@ -5313,15 +5374,19 @@
       </c>
       <c r="F8" s="9" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G8" s="10" t="inlineStr">
         <is>
-          <t>Converse x Hello Kitty Chuck Taylor 70 Swarovski®</t>
-        </is>
-      </c>
-      <c r="H8" s="10" t="inlineStr"/>
+          <t>Air Jordan 4 Imperial Purple</t>
+        </is>
+      </c>
+      <c r="H8" s="10" t="inlineStr">
+        <is>
+          <t>hot-model, exclusive</t>
+        </is>
+      </c>
       <c r="I8" s="9" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -5337,7 +5402,7 @@
       </c>
       <c r="L8" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/converse-hello-kitty-chuck-taylor-70-swarovski</t>
+          <t>/launch/t/air-jordan-4-imperial-purple</t>
         </is>
       </c>
       <c r="M8" s="10" t="inlineStr"/>
@@ -9203,9 +9268,9 @@
         <v>46099</v>
       </c>
       <c r="B79" s="5" t="inlineStr"/>
-      <c r="C79" s="11" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -9220,23 +9285,27 @@
       </c>
       <c r="F79" s="9" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G79" s="10" t="inlineStr">
         <is>
-          <t>One Piece x Crocs Classic Clog 'Zoro'</t>
-        </is>
-      </c>
-      <c r="H79" s="10" t="inlineStr"/>
+          <t>Mar 18 Air Jordan 1 Low OG Sail and Coconut Milk</t>
+        </is>
+      </c>
+      <c r="H79" s="10" t="inlineStr">
+        <is>
+          <t>hot-model</t>
+        </is>
+      </c>
       <c r="I79" s="9" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="J79" s="9" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="K79" s="9" t="n">
@@ -9244,7 +9313,7 @@
       </c>
       <c r="L79" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-zoro-212953-90h/706159</t>
+          <t>/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
         </is>
       </c>
       <c r="M79" s="10" t="inlineStr"/>
@@ -9253,7 +9322,7 @@
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
-        <v>46100</v>
+        <v>46099</v>
       </c>
       <c r="B80" s="5" t="inlineStr"/>
       <c r="C80" s="11" t="inlineStr">
@@ -9273,12 +9342,12 @@
       </c>
       <c r="F80" s="9" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="G80" s="10" t="inlineStr">
         <is>
-          <t>New Balance 991v1 Made in UK 'Oyster Grey' From £ 220</t>
+          <t>One Piece x Crocs Classic Clog 'Zoro'</t>
         </is>
       </c>
       <c r="H80" s="10" t="inlineStr"/>
@@ -9297,7 +9366,7 @@
       </c>
       <c r="L80" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-991v1-made-in-uk-oyster-grey-m991cr1/706155</t>
+          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-zoro-212953-90h/706159</t>
         </is>
       </c>
       <c r="M80" s="10" t="inlineStr"/>
@@ -9306,7 +9375,7 @@
     </row>
     <row r="81">
       <c r="A81" s="4" t="n">
-        <v>46101</v>
+        <v>46100</v>
       </c>
       <c r="B81" s="5" t="inlineStr"/>
       <c r="C81" s="11" t="inlineStr">
@@ -9326,19 +9395,15 @@
       </c>
       <c r="F81" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G81" s="10" t="inlineStr">
         <is>
-          <t>Nike First Sight Noir WMNS 'Black' From £ 110</t>
-        </is>
-      </c>
-      <c r="H81" s="10" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>New Balance 991v1 Made in UK 'Oyster Grey' From £ 220</t>
+        </is>
+      </c>
+      <c r="H81" s="10" t="inlineStr"/>
       <c r="I81" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -9354,7 +9419,7 @@
       </c>
       <c r="L81" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-first-sight-noir-wmns-black-hq2409-001/706328</t>
+          <t>https://thedropdate.com/sneakers/new-balance-991v1-made-in-uk-oyster-grey-m991cr1/706155</t>
         </is>
       </c>
       <c r="M81" s="10" t="inlineStr"/>
@@ -9363,7 +9428,7 @@
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
-        <v>46107</v>
+        <v>46101</v>
       </c>
       <c r="B82" s="5" t="inlineStr"/>
       <c r="C82" s="11" t="inlineStr">
@@ -9383,15 +9448,19 @@
       </c>
       <c r="F82" s="9" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G82" s="10" t="inlineStr">
         <is>
-          <t>One Piece x Crocs Classic Clog 'Thousand Sunny'</t>
-        </is>
-      </c>
-      <c r="H82" s="10" t="inlineStr"/>
+          <t>Nike First Sight Noir WMNS 'Black' From £ 110</t>
+        </is>
+      </c>
+      <c r="H82" s="10" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I82" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -9407,7 +9476,7 @@
       </c>
       <c r="L82" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-thousand-sunny-212126-90h/706160</t>
+          <t>https://thedropdate.com/sneakers/nike-first-sight-noir-wmns-black-hq2409-001/706328</t>
         </is>
       </c>
       <c r="M82" s="10" t="inlineStr"/>
@@ -9436,12 +9505,12 @@
       </c>
       <c r="F83" s="9" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="G83" s="10" t="inlineStr">
         <is>
-          <t>New Balance 1890 'Star Burst' From £ 160</t>
+          <t>One Piece x Crocs Classic Clog 'Thousand Sunny'</t>
         </is>
       </c>
       <c r="H83" s="10" t="inlineStr"/>
@@ -9460,7 +9529,7 @@
       </c>
       <c r="L83" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-1890-black-yellow-u18903rb/705946</t>
+          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-thousand-sunny-212126-90h/706160</t>
         </is>
       </c>
       <c r="M83" s="10" t="inlineStr"/>
@@ -9469,7 +9538,7 @@
     </row>
     <row r="84">
       <c r="A84" s="4" t="n">
-        <v>46108</v>
+        <v>46107</v>
       </c>
       <c r="B84" s="5" t="inlineStr"/>
       <c r="C84" s="11" t="inlineStr">
@@ -9489,23 +9558,23 @@
       </c>
       <c r="F84" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G84" s="10" t="inlineStr">
         <is>
-          <t>Mar 27 Baby/Toddler Shoes Nike Little Posite Pro</t>
+          <t>New Balance 1890 'Star Burst' From £ 160</t>
         </is>
       </c>
       <c r="H84" s="10" t="inlineStr"/>
       <c r="I84" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J84" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K84" s="9" t="n">
@@ -9513,7 +9582,7 @@
       </c>
       <c r="L84" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-foamposite-pro-university-blue-and-white</t>
+          <t>https://thedropdate.com/sneakers/new-balance-1890-black-yellow-u18903rb/705946</t>
         </is>
       </c>
       <c r="M84" s="10" t="inlineStr"/>
@@ -9522,12 +9591,12 @@
     </row>
     <row r="85">
       <c r="A85" s="4" t="n">
-        <v>46109</v>
+        <v>46108</v>
       </c>
       <c r="B85" s="5" t="inlineStr"/>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="C85" s="11" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D85" s="7" t="inlineStr">
@@ -9542,27 +9611,23 @@
       </c>
       <c r="F85" s="9" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G85" s="10" t="inlineStr">
         <is>
-          <t>Air Jordan 3 'Spring Is In The Air' From £ 190</t>
-        </is>
-      </c>
-      <c r="H85" s="10" t="inlineStr">
-        <is>
-          <t>hot-model</t>
-        </is>
-      </c>
+          <t>Mar 27 Baby/Toddler Shoes Nike Little Posite Pro</t>
+        </is>
+      </c>
+      <c r="H85" s="10" t="inlineStr"/>
       <c r="I85" s="9" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="J85" s="9" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="K85" s="9" t="n">
@@ -9570,7 +9635,7 @@
       </c>
       <c r="L85" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/air-jordan-3-spring-is-in-the-air-if4396-100/703366</t>
+          <t>/launch/t/air-foamposite-pro-university-blue-and-white</t>
         </is>
       </c>
       <c r="M85" s="10" t="inlineStr"/>
@@ -9579,17 +9644,17 @@
     </row>
     <row r="86">
       <c r="A86" s="4" t="n">
-        <v>46113</v>
+        <v>46109</v>
       </c>
       <c r="B86" s="5" t="inlineStr"/>
-      <c r="C86" s="11" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D86" s="12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="E86" s="8" t="inlineStr">
@@ -9599,15 +9664,19 @@
       </c>
       <c r="F86" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G86" s="10" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Pregame Mule 'Light Smoke Grey' From £ 80</t>
-        </is>
-      </c>
-      <c r="H86" s="10" t="inlineStr"/>
+          <t>Air Jordan 3 'Spring Is In The Air' From £ 190</t>
+        </is>
+      </c>
+      <c r="H86" s="10" t="inlineStr">
+        <is>
+          <t>hot-model</t>
+        </is>
+      </c>
       <c r="I86" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -9619,11 +9688,11 @@
         </is>
       </c>
       <c r="K86" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L86" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mule-light-smoke-grey-hq4307-003/647220</t>
+          <t>https://thedropdate.com/sneakers/air-jordan-3-spring-is-in-the-air-if4396-100/703366</t>
         </is>
       </c>
       <c r="M86" s="10" t="inlineStr"/>
@@ -9640,9 +9709,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D87" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E87" s="8" t="inlineStr">
@@ -9657,7 +9726,7 @@
       </c>
       <c r="G87" s="10" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Slide 'Black' From £ 80</t>
+          <t>Nike Mind 001 Pregame Mule 'Light Smoke Grey' From £ 80</t>
         </is>
       </c>
       <c r="H87" s="10" t="inlineStr"/>
@@ -9672,11 +9741,11 @@
         </is>
       </c>
       <c r="K87" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L87" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-mind-001-slide-black-hq4307-001/672235</t>
+          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mule-light-smoke-grey-hq4307-003/647220</t>
         </is>
       </c>
       <c r="M87" s="10" t="inlineStr"/>
@@ -9710,14 +9779,10 @@
       </c>
       <c r="G88" s="10" t="inlineStr">
         <is>
-          <t>Nike Mind 001 WMNS Pregame Mules 'Black' From £ 80</t>
-        </is>
-      </c>
-      <c r="H88" s="10" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Nike Mind 001 Slide 'Black' From £ 80</t>
+        </is>
+      </c>
+      <c r="H88" s="10" t="inlineStr"/>
       <c r="I88" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -9733,7 +9798,7 @@
       </c>
       <c r="L88" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mules-hq4309-001/678052</t>
+          <t>https://thedropdate.com/sneakers/nike-mind-001-slide-black-hq4307-001/672235</t>
         </is>
       </c>
       <c r="M88" s="10" t="inlineStr"/>
@@ -9742,7 +9807,7 @@
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
-        <v>46115</v>
+        <v>46113</v>
       </c>
       <c r="B89" s="5" t="inlineStr"/>
       <c r="C89" s="11" t="inlineStr">
@@ -9767,22 +9832,22 @@
       </c>
       <c r="G89" s="10" t="inlineStr">
         <is>
-          <t>Apr 3 Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
+          <t>Nike Mind 001 WMNS Pregame Mules 'Black' From £ 80</t>
         </is>
       </c>
       <c r="H89" s="10" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I89" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J89" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K89" s="9" t="n">
@@ -9790,7 +9855,7 @@
       </c>
       <c r="L89" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
+          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mules-hq4309-001/678052</t>
         </is>
       </c>
       <c r="M89" s="10" t="inlineStr"/>
@@ -9812,13 +9877,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H59"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="61" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
@@ -9870,22 +9935,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>adidas Anthony Edwards 2 MENS • BLACK/MULTI</t>
+          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -9893,7 +9958,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-07T16:54:46Z</t>
+          <t>2026-03-07T17:46:10Z</t>
         </is>
       </c>
     </row>
@@ -9905,17 +9970,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-08</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
+          <t>Converse x Hello Kitty Chuck Taylor 70 Swarovski®</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -9923,29 +9988,29 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-07T16:54:46Z</t>
+          <t>2026-03-07T17:46:10Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>adidas Originals Anthony Edwards 2 ASW PE BOYS GRADE SCHOOL • MULTI/MULTI</t>
+          <t>Mar 18 Air Jordan 1 Low OG Sail and Coconut Milk</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -9953,7 +10018,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-07T16:54:46Z</t>
+          <t>2026-03-07T17:46:10Z</t>
         </is>
       </c>
     </row>
@@ -9965,17 +10030,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Air Jordan 1 High OG WMNS 'Psychic Blue' From £ 163</t>
+          <t>Apr 3 Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -9983,1627 +10048,7 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Air Jordan 1 Low OG 'Rabbit Floral Swoosh' From £ 145</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>App entry Jordan Air Jordan Retro 1 Hi WOMENS • WHITE/BLUE</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>App entry Jordan Retro 4 Imperial Purple MENS • PURPLE/BLACK/YELLOW</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Crocs</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Crocs Classic Clog One Piece MENS • GREEN/BLACK</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Jordan Retro 1 HI OG Remastered GIRLS TODDLER • PALE IVORY/PSYCHIC BLUE/COCONUT MILK</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Jordan Retro 1 High OG GIRLS PRE-SCHOOL • PALE IVORY/PSYCHIC BLUE/COCONUT MILK</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Jordan Retro 13 BOYS GRADE SCHOOL • WHITE/BLACK/TRUE RED</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>NAKED Copenhagen x Nike Shox Z 'Metallic Hematite Grey'</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>NAKED Copenhagen x Nike Shox Z Calistra 'Black'</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Nike Air Force 1 '07 MENS • YELLOW PULSE/PINK FOAM/MULTI</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Nike Air Force 1 BOYS GRADE SCHOOL • YELLOW PULSE/PINK FOAM/EMERALD RISE</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Nike Air Max 95 GIRLS PRE-SCHOOL • BLACK/PINK FOAM/MEDIUM GREY</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>Nike Air Max 95 Zip 'Phantom &amp; Light Crimson' From £ 185</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Nike Air Max Uptempo '95 MENS • UNIVERSITY RED/WHITE/BLACK</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Nike Dunk Low MENS • EMERALD RISE/YELLOW PULSE/HYDRANGEAS</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Nike Sabrina 3 MENS • YELLOW STRIKE/APPLE GREEN/PALE YELLOW</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>PUMA Hali 1 MENS • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Reebok</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • BLUE/GREEN</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Skip To Main</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Vans Pearlized LX Old Skool 36 WOMENS • BLACK/NAVY</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Adidas</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Converse</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Converse SHAI 001 Blush MENS • TICKLED PINK/GERANIUM PINK</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Crocs</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Crocs Classic Clog One Piece MENS • GREEN/BLACK</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Jordan Retro 13 BOYS GRADE SCHOOL • WHITE/BLACK/TRUE RED</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>Nike Air Force 1 '07 MENS • YELLOW PULSE/PINK FOAM/MULTI</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>Nike Air Force 1 BOYS GRADE SCHOOL • YELLOW PULSE/PINK FOAM/EMERALD RISE</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Nike Air Max 95 GIRLS PRE-SCHOOL • BLACK/PINK FOAM/MEDIUM GREY</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Nike Air Max Uptempo '95 MENS • UNIVERSITY RED/WHITE/BLACK</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>Nike Dunk Low MENS • EMERALD RISE/YELLOW PULSE/HYDRANGEAS</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Nike Sabrina 3 MENS • YELLOW STRIKE/APPLE GREEN/PALE YELLOW</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>PUMA Hali 1 MENS • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Reebok</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • BLUE/GREEN</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Skip To Main</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Vans Pearlized LX Old Skool 36 WOMENS • BLACK/NAVY</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>2026-03-07T16:54:46Z</t>
+          <t>2026-03-07T17:46:10Z</t>
         </is>
       </c>
     </row>
@@ -11886,12 +10331,12 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
+          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>hot-model, retro</t>
+          <t>hot-model</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -11909,7 +10354,7 @@
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
+          <t>/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
         </is>
       </c>
       <c r="M4" t="inlineStr"/>
@@ -11951,12 +10396,12 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Air Jordan 4 Imperial Purple</t>
+          <t>Air Jordan 13 Retro White and University Red</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>hot-model, exclusive</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -11974,13 +10419,13 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-4-imperial-purple</t>
+          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="n">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="P5" t="n">
         <v>50</v>
@@ -11996,7 +10441,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -12011,15 +10456,19 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Converse x Hello Kitty Chuck Taylor 70 Swarovski®</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
+          <t>Air Jordan 4 Imperial Purple</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>hot-model, exclusive</t>
+        </is>
+      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>playwright-linkscan</t>
@@ -12035,13 +10484,13 @@
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>/launch/t/converse-hello-kitty-chuck-taylor-70-swarovski</t>
+          <t>/launch/t/air-jordan-4-imperial-purple</t>
         </is>
       </c>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>32</v>
       </c>
       <c r="P6" t="n">
         <v>50</v>
@@ -16471,7 +14920,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -16486,23 +14935,27 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>One Piece x Crocs Classic Clog 'Zoro'</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr"/>
+          <t>Mar 18 Air Jordan 1 Low OG Sail and Coconut Milk</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>hot-model</t>
+        </is>
+      </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="K77" t="n">
@@ -16510,13 +14963,13 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-zoro-212953-90h/706159</t>
+          <t>/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="P77" t="n">
         <v>50</v>
@@ -16525,7 +14978,7 @@
     </row>
     <row r="78">
       <c r="A78" s="14" t="n">
-        <v>46100</v>
+        <v>46099</v>
       </c>
       <c r="B78" t="n">
         <v>0</v>
@@ -16547,12 +15000,12 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>New Balance 991v1 Made in UK 'Oyster Grey' From £ 220</t>
+          <t>One Piece x Crocs Classic Clog 'Zoro'</t>
         </is>
       </c>
       <c r="H78" t="inlineStr"/>
@@ -16571,7 +15024,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-991v1-made-in-uk-oyster-grey-m991cr1/706155</t>
+          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-zoro-212953-90h/706159</t>
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
@@ -16586,7 +15039,7 @@
     </row>
     <row r="79">
       <c r="A79" s="14" t="n">
-        <v>46101</v>
+        <v>46100</v>
       </c>
       <c r="B79" t="n">
         <v>0</v>
@@ -16608,19 +15061,15 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Nike First Sight Noir WMNS 'Black' From £ 110</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>New Balance 991v1 Made in UK 'Oyster Grey' From £ 220</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr"/>
       <c r="I79" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -16636,13 +15085,13 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-first-sight-noir-wmns-black-hq2409-001/706328</t>
+          <t>https://thedropdate.com/sneakers/new-balance-991v1-made-in-uk-oyster-grey-m991cr1/706155</t>
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P79" t="n">
         <v>50</v>
@@ -16651,7 +15100,7 @@
     </row>
     <row r="80">
       <c r="A80" s="14" t="n">
-        <v>46107</v>
+        <v>46101</v>
       </c>
       <c r="B80" t="n">
         <v>0</v>
@@ -16673,15 +15122,19 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>One Piece x Crocs Classic Clog 'Thousand Sunny'</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>Nike First Sight Noir WMNS 'Black' From £ 110</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -16697,13 +15150,13 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-thousand-sunny-212126-90h/706160</t>
+          <t>https://thedropdate.com/sneakers/nike-first-sight-noir-wmns-black-hq2409-001/706328</t>
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P80" t="n">
         <v>50</v>
@@ -16734,12 +15187,12 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>New Balance 1890 'Star Burst' From £ 160</t>
+          <t>One Piece x Crocs Classic Clog 'Thousand Sunny'</t>
         </is>
       </c>
       <c r="H81" t="inlineStr"/>
@@ -16758,7 +15211,7 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-1890-black-yellow-u18903rb/705946</t>
+          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-thousand-sunny-212126-90h/706160</t>
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
@@ -16773,7 +15226,7 @@
     </row>
     <row r="82">
       <c r="A82" s="14" t="n">
-        <v>46108</v>
+        <v>46107</v>
       </c>
       <c r="B82" t="n">
         <v>0</v>
@@ -16795,23 +15248,23 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Mar 27 Baby/Toddler Shoes Nike Little Posite Pro</t>
+          <t>New Balance 1890 'Star Burst' From £ 160</t>
         </is>
       </c>
       <c r="H82" t="inlineStr"/>
       <c r="I82" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K82" t="n">
@@ -16819,13 +15272,13 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>/launch/t/air-foamposite-pro-university-blue-and-white</t>
+          <t>https://thedropdate.com/sneakers/new-balance-1890-black-yellow-u18903rb/705946</t>
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P82" t="n">
         <v>50</v>
@@ -16834,14 +15287,14 @@
     </row>
     <row r="83">
       <c r="A83" s="14" t="n">
-        <v>46109</v>
+        <v>46108</v>
       </c>
       <c r="B83" t="n">
         <v>0</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16856,27 +15309,23 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Air Jordan 3 'Spring Is In The Air' From £ 190</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr">
-        <is>
-          <t>hot-model</t>
-        </is>
-      </c>
+          <t>Mar 27 Baby/Toddler Shoes Nike Little Posite Pro</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr"/>
       <c r="I83" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="K83" t="n">
@@ -16884,13 +15333,13 @@
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/air-jordan-3-spring-is-in-the-air-if4396-100/703366</t>
+          <t>/launch/t/air-foamposite-pro-university-blue-and-white</t>
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="P83" t="n">
         <v>50</v>
@@ -16899,19 +15348,19 @@
     </row>
     <row r="84">
       <c r="A84" s="14" t="n">
-        <v>46113</v>
+        <v>46109</v>
       </c>
       <c r="B84" t="n">
         <v>0</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -16921,15 +15370,19 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Pregame Mule 'Light Smoke Grey' From £ 80</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>Air Jordan 3 'Spring Is In The Air' From £ 190</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>hot-model</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -16941,20 +15394,20 @@
         </is>
       </c>
       <c r="K84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mule-light-smoke-grey-hq4307-003/647220</t>
+          <t>https://thedropdate.com/sneakers/air-jordan-3-spring-is-in-the-air-if4396-100/703366</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="P84" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="Q84" t="inlineStr"/>
     </row>
@@ -16972,7 +15425,7 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -16987,7 +15440,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Slide 'Black' From £ 80</t>
+          <t>Nike Mind 001 Pregame Mule 'Light Smoke Grey' From £ 80</t>
         </is>
       </c>
       <c r="H85" t="inlineStr"/>
@@ -17002,11 +15455,11 @@
         </is>
       </c>
       <c r="K85" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-mind-001-slide-black-hq4307-001/672235</t>
+          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mule-light-smoke-grey-hq4307-003/647220</t>
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
@@ -17015,7 +15468,7 @@
         <v>12</v>
       </c>
       <c r="P85" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="Q85" t="inlineStr"/>
     </row>
@@ -17048,14 +15501,10 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nike Mind 001 WMNS Pregame Mules 'Black' From £ 80</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Nike Mind 001 Slide 'Black' From £ 80</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr"/>
       <c r="I86" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -17071,7 +15520,7 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mules-hq4309-001/678052</t>
+          <t>https://thedropdate.com/sneakers/nike-mind-001-slide-black-hq4307-001/672235</t>
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
@@ -17086,7 +15535,7 @@
     </row>
     <row r="87">
       <c r="A87" s="14" t="n">
-        <v>46115</v>
+        <v>46113</v>
       </c>
       <c r="B87" t="n">
         <v>0</v>
@@ -17113,22 +15562,22 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Apr 3 Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
+          <t>Nike Mind 001 WMNS Pregame Mules 'Black' From £ 80</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K87" t="n">
@@ -17136,7 +15585,7 @@
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
+          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mules-hq4309-001/678052</t>
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
@@ -17329,7 +15778,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4">
@@ -17357,7 +15806,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8">
@@ -17377,7 +15826,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
@@ -17413,17 +15862,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="B14" t="n">
@@ -17475,7 +15924,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
     </row>
     <row r="21">
@@ -17485,7 +15934,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22"/>

--- a/output/weekly_tracker.xlsx
+++ b/output/weekly_tracker.xlsx
@@ -1220,7 +1220,7 @@
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga 3xl Extreme Lace Eggshell / Multicolor</t>
+          <t>Balenciaga 3xl Split Logo Eggshell / Red</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr"/>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="L14" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-3xl-extreme-lace-eggshell-multicolor</t>
+          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-eggshell-red</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr"/>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga 3xl Split Logo Eggshell / Red</t>
+          <t>Balenciaga 3xl Split Logo White / Navy</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr"/>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-eggshell-red</t>
+          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-white-navy</t>
         </is>
       </c>
       <c r="M15" s="10" t="inlineStr"/>
@@ -1326,10 +1326,14 @@
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga 3xl Split Logo White / Navy</t>
-        </is>
-      </c>
-      <c r="H16" s="10" t="inlineStr"/>
+          <t>Balenciaga Basketball Mule Silver / Black</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -1345,7 +1349,7 @@
       </c>
       <c r="L16" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-white-navy</t>
+          <t>https://www.kicksonfire.com/balenciaga-basketball-mule-silver-black</t>
         </is>
       </c>
       <c r="M16" s="10" t="inlineStr"/>
@@ -1379,14 +1383,10 @@
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Basketball Mule Silver / Black</t>
-        </is>
-      </c>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>basketball</t>
-        </is>
-      </c>
+          <t>Balenciaga City Balenciaga Grey</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr"/>
       <c r="I17" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="L17" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-basketball-mule-silver-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-balenciaga-grey</t>
         </is>
       </c>
       <c r="M17" s="10" t="inlineStr"/>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City Balenciaga Grey</t>
+          <t>Balenciaga City Granny Green</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr"/>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="L18" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-balenciaga-grey</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-granny-green</t>
         </is>
       </c>
       <c r="M18" s="10" t="inlineStr"/>
@@ -1489,10 +1489,14 @@
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City Granny Green</t>
-        </is>
-      </c>
-      <c r="H19" s="10" t="inlineStr"/>
+          <t>Balenciaga City WMNS Black</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -1508,7 +1512,7 @@
       </c>
       <c r="L19" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-granny-green</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-wmns-black</t>
         </is>
       </c>
       <c r="M19" s="10" t="inlineStr"/>
@@ -1542,12 +1546,12 @@
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City WMNS Black</t>
+          <t>Balenciaga City WMNS Petal Pink</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>women, exclusive</t>
         </is>
       </c>
       <c r="I20" s="9" t="inlineStr">
@@ -1565,7 +1569,7 @@
       </c>
       <c r="L20" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-wmns-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-wmns-petal-pink</t>
         </is>
       </c>
       <c r="M20" s="10" t="inlineStr"/>
@@ -1599,12 +1603,12 @@
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City WMNS Petal Pink</t>
+          <t>Balenciaga City WMNS Silver</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>women, exclusive</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
@@ -1622,7 +1626,7 @@
       </c>
       <c r="L21" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-wmns-petal-pink</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-wmns-silver</t>
         </is>
       </c>
       <c r="M21" s="10" t="inlineStr"/>
@@ -1656,12 +1660,12 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City WMNS Silver</t>
+          <t>Balenciaga Hamptons Medium Worn-Out Navy / Taupe</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>exclusive</t>
         </is>
       </c>
       <c r="I22" s="9" t="inlineStr">
@@ -1679,7 +1683,7 @@
       </c>
       <c r="L22" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-wmns-silver</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-navy-taupe</t>
         </is>
       </c>
       <c r="M22" s="10" t="inlineStr"/>
@@ -1713,12 +1717,12 @@
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Medium Worn-Out Navy / Taupe</t>
+          <t>Balenciaga Hamptons Medium Worn-Out WMNS Pink / White</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>exclusive</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr">
@@ -1736,7 +1740,7 @@
       </c>
       <c r="L23" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-navy-taupe</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-wmns-pink-white</t>
         </is>
       </c>
       <c r="M23" s="10" t="inlineStr"/>
@@ -1770,7 +1774,7 @@
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Medium Worn-Out WMNS Pink / White</t>
+          <t>Balenciaga Hamptons Platform WMNS Black</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
@@ -1793,7 +1797,7 @@
       </c>
       <c r="L24" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-wmns-pink-white</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-black</t>
         </is>
       </c>
       <c r="M24" s="10" t="inlineStr"/>
@@ -1827,7 +1831,7 @@
       </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Platform WMNS Black</t>
+          <t>Balenciaga Hamptons Platform WMNS White</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr">
@@ -1850,7 +1854,7 @@
       </c>
       <c r="L25" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-white</t>
         </is>
       </c>
       <c r="M25" s="10" t="inlineStr"/>
@@ -1884,14 +1888,10 @@
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Platform WMNS White</t>
-        </is>
-      </c>
-      <c r="H26" s="10" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Balenciaga Monday Ultra Black</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr"/>
       <c r="I26" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="L26" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-white</t>
+          <t>https://www.kicksonfire.com/balenciaga-monday-ultra-black</t>
         </is>
       </c>
       <c r="M26" s="10" t="inlineStr"/>
@@ -1941,10 +1941,14 @@
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Monday Ultra Black</t>
-        </is>
-      </c>
-      <c r="H27" s="10" t="inlineStr"/>
+          <t>Balenciaga Monday Ultra WMNS Brown / White</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -1960,7 +1964,7 @@
       </c>
       <c r="L27" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-monday-ultra-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-monday-ultra-wmns-brown-white</t>
         </is>
       </c>
       <c r="M27" s="10" t="inlineStr"/>
@@ -3041,10 +3045,14 @@
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
-        </is>
-      </c>
-      <c r="H47" s="10" t="inlineStr"/>
+          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
+        </is>
+      </c>
+      <c r="H47" s="10" t="inlineStr">
+        <is>
+          <t>exclusive</t>
+        </is>
+      </c>
       <c r="I47" s="9" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -4842,7 +4850,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O86"/>
+  <dimension ref="A1:O87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -5534,7 +5542,7 @@
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga 3xl Extreme Lace Eggshell / Multicolor</t>
+          <t>Balenciaga 3xl Split Logo Eggshell / Red</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr"/>
@@ -5553,7 +5561,7 @@
       </c>
       <c r="L14" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-3xl-extreme-lace-eggshell-multicolor</t>
+          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-eggshell-red</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr"/>
@@ -5587,7 +5595,7 @@
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga 3xl Split Logo Eggshell / Red</t>
+          <t>Balenciaga 3xl Split Logo White / Navy</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr"/>
@@ -5606,7 +5614,7 @@
       </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-eggshell-red</t>
+          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-white-navy</t>
         </is>
       </c>
       <c r="M15" s="10" t="inlineStr"/>
@@ -5640,10 +5648,14 @@
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga 3xl Split Logo White / Navy</t>
-        </is>
-      </c>
-      <c r="H16" s="10" t="inlineStr"/>
+          <t>Balenciaga Basketball Mule Silver / Black</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -5659,7 +5671,7 @@
       </c>
       <c r="L16" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-white-navy</t>
+          <t>https://www.kicksonfire.com/balenciaga-basketball-mule-silver-black</t>
         </is>
       </c>
       <c r="M16" s="10" t="inlineStr"/>
@@ -5693,14 +5705,10 @@
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Basketball Mule Silver / Black</t>
-        </is>
-      </c>
-      <c r="H17" s="10" t="inlineStr">
-        <is>
-          <t>basketball</t>
-        </is>
-      </c>
+          <t>Balenciaga City Balenciaga Grey</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr"/>
       <c r="I17" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -5716,7 +5724,7 @@
       </c>
       <c r="L17" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-basketball-mule-silver-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-balenciaga-grey</t>
         </is>
       </c>
       <c r="M17" s="10" t="inlineStr"/>
@@ -5750,7 +5758,7 @@
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City Balenciaga Grey</t>
+          <t>Balenciaga City Granny Green</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr"/>
@@ -5769,7 +5777,7 @@
       </c>
       <c r="L18" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-balenciaga-grey</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-granny-green</t>
         </is>
       </c>
       <c r="M18" s="10" t="inlineStr"/>
@@ -5803,10 +5811,14 @@
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City Granny Green</t>
-        </is>
-      </c>
-      <c r="H19" s="10" t="inlineStr"/>
+          <t>Balenciaga City WMNS Black</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I19" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -5822,7 +5834,7 @@
       </c>
       <c r="L19" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-granny-green</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-wmns-black</t>
         </is>
       </c>
       <c r="M19" s="10" t="inlineStr"/>
@@ -5856,12 +5868,12 @@
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City WMNS Black</t>
+          <t>Balenciaga City WMNS Petal Pink</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>women, exclusive</t>
         </is>
       </c>
       <c r="I20" s="9" t="inlineStr">
@@ -5879,7 +5891,7 @@
       </c>
       <c r="L20" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-wmns-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-wmns-petal-pink</t>
         </is>
       </c>
       <c r="M20" s="10" t="inlineStr"/>
@@ -5913,12 +5925,12 @@
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City WMNS Petal Pink</t>
+          <t>Balenciaga City WMNS Silver</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>women, exclusive</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
@@ -5936,7 +5948,7 @@
       </c>
       <c r="L21" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-wmns-petal-pink</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-wmns-silver</t>
         </is>
       </c>
       <c r="M21" s="10" t="inlineStr"/>
@@ -5970,12 +5982,12 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City WMNS Silver</t>
+          <t>Balenciaga Hamptons Medium Worn-Out Navy / Taupe</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>exclusive</t>
         </is>
       </c>
       <c r="I22" s="9" t="inlineStr">
@@ -5993,7 +6005,7 @@
       </c>
       <c r="L22" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-wmns-silver</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-navy-taupe</t>
         </is>
       </c>
       <c r="M22" s="10" t="inlineStr"/>
@@ -6027,12 +6039,12 @@
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Medium Worn-Out Navy / Taupe</t>
+          <t>Balenciaga Hamptons Medium Worn-Out WMNS Pink / White</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>exclusive</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr">
@@ -6050,7 +6062,7 @@
       </c>
       <c r="L23" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-navy-taupe</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-wmns-pink-white</t>
         </is>
       </c>
       <c r="M23" s="10" t="inlineStr"/>
@@ -6084,7 +6096,7 @@
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Medium Worn-Out WMNS Pink / White</t>
+          <t>Balenciaga Hamptons Platform WMNS Black</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
@@ -6107,7 +6119,7 @@
       </c>
       <c r="L24" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-wmns-pink-white</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-black</t>
         </is>
       </c>
       <c r="M24" s="10" t="inlineStr"/>
@@ -6141,7 +6153,7 @@
       </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Platform WMNS Black</t>
+          <t>Balenciaga Hamptons Platform WMNS White</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr">
@@ -6164,7 +6176,7 @@
       </c>
       <c r="L25" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-white</t>
         </is>
       </c>
       <c r="M25" s="10" t="inlineStr"/>
@@ -6198,14 +6210,10 @@
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Platform WMNS White</t>
-        </is>
-      </c>
-      <c r="H26" s="10" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Balenciaga Monday Ultra Black</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr"/>
       <c r="I26" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -6221,7 +6229,7 @@
       </c>
       <c r="L26" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-white</t>
+          <t>https://www.kicksonfire.com/balenciaga-monday-ultra-black</t>
         </is>
       </c>
       <c r="M26" s="10" t="inlineStr"/>
@@ -6255,10 +6263,14 @@
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Monday Ultra Black</t>
-        </is>
-      </c>
-      <c r="H27" s="10" t="inlineStr"/>
+          <t>Balenciaga Monday Ultra WMNS Brown / White</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I27" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -6274,7 +6286,7 @@
       </c>
       <c r="L27" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-monday-ultra-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-monday-ultra-wmns-brown-white</t>
         </is>
       </c>
       <c r="M27" s="10" t="inlineStr"/>
@@ -7355,10 +7367,14 @@
       </c>
       <c r="G47" s="10" t="inlineStr">
         <is>
-          <t>Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
-        </is>
-      </c>
-      <c r="H47" s="10" t="inlineStr"/>
+          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
+        </is>
+      </c>
+      <c r="H47" s="10" t="inlineStr">
+        <is>
+          <t>exclusive</t>
+        </is>
+      </c>
       <c r="I47" s="9" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -9519,6 +9535,63 @@
       <c r="M86" s="10" t="inlineStr"/>
       <c r="N86" s="10" t="inlineStr"/>
       <c r="O86" s="5" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B87" s="5" t="inlineStr"/>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F87" s="9" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G87" s="10" t="inlineStr">
+        <is>
+          <t>Apr 3 Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
+        </is>
+      </c>
+      <c r="H87" s="10" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="I87" s="9" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="J87" s="9" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="K87" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L87" s="10" t="inlineStr">
+        <is>
+          <t>/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
+        </is>
+      </c>
+      <c r="M87" s="10" t="inlineStr"/>
+      <c r="N87" s="10" t="inlineStr"/>
+      <c r="O87" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -9535,12 +9608,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="9" customWidth="1" min="3" max="3"/>
     <col width="70" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
@@ -9593,22 +9666,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Mar 7 Baby/Toddler Shoes Jordan 1 Retro High OG</t>
+          <t>Balenciaga Monday Ultra WMNS Brown / White</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -9616,7 +9689,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-08T06:02:02Z</t>
+          <t>2026-03-08T16:56:59Z</t>
         </is>
       </c>
     </row>
@@ -9628,17 +9701,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-07</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Mar 7 Baby/Toddler Shoes Jordan 4 Retro "Imperial Purple"</t>
+          <t>Balenciaga 3xl Extreme Lace Eggshell / Multicolor</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -9646,29 +9719,29 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-08T06:02:02Z</t>
+          <t>2026-03-08T16:56:59Z</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
+          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -9676,7 +9749,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-08T06:02:02Z</t>
+          <t>2026-03-08T16:56:59Z</t>
         </is>
       </c>
     </row>
@@ -9688,17 +9761,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
+          <t>Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -9706,29 +9779,29 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-08T06:02:02Z</t>
+          <t>2026-03-08T16:56:59Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Air Jordan 4 Imperial Purple</t>
+          <t>Apr 3 Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -9736,727 +9809,7 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Air Max Ishod Iron Grey and Photon Dust</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr"/>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Nike SB Ishod Apparel Collection</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Nike Shox Ride 2 Black / Metallic Dark Grey</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2026-03-08</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>Zoom Vomero 5 Hyper Royal</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Air Jordan 4 Imperial Purple</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>Air Max Ishod Iron Grey and Photon Dust</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>Nike SB Ishod Apparel Collection</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-03-09</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>Zoom Vomero 5 Hyper Royal</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>Balenciaga 3xl Extreme Lace Eggshell / Multicolor</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Mar 10 Zoom Vomero 5 Hyper Royal</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Crocs</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Converse</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Converse SHAI 001 Blush MENS • TICKLED PINK/GERANIUM PINK</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr"/>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Jordan Grade School Retro 13 True Red BOYS GRADE SCHOOL • WHITE/BLACK/TRUE RED</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr"/>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Nike Air Max Uptempo '95 MENS • UNIVERSITY RED/WHITE/BLACK</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Nike Grade School Air Force 1 '07 BOYS GRADE SCHOOL • YELLOW PULSE/PINK FOAM/EMERALD RISE</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>PUMA All-Pro NITRO MENS • SAND DUNE/PURE PINK/GREEN FRUIT</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Converse</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Converse SHAI 001 Blush MENS • TICKLED PINK/GERANIUM PINK</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Crocs</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Crocs Classic Clog One Piece MENS • GREEN/BLACK</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Jordan Retro 13 BOYS GRADE SCHOOL • WHITE/BLACK/TRUE RED</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Nike Air Force 1 BOYS GRADE SCHOOL • YELLOW PULSE/PINK FOAM/EMERALD RISE</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Nike Air Max 95 GIRLS PRE-SCHOOL • BLACK/PINK FOAM/MEDIUM GREY</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Nike Air Max Uptempo '95 MENS • UNIVERSITY RED/WHITE/BLACK</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>2026-03-08T06:02:02Z</t>
+          <t>2026-03-08T16:56:59Z</t>
         </is>
       </c>
     </row>
@@ -10471,7 +9824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q84"/>
+  <dimension ref="A1:Q85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -11243,7 +10596,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Balenciaga 3xl Extreme Lace Eggshell / Multicolor</t>
+          <t>Balenciaga 3xl Split Logo Eggshell / Red</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -11262,7 +10615,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-3xl-extreme-lace-eggshell-multicolor</t>
+          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-eggshell-red</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -11304,7 +10657,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Balenciaga 3xl Split Logo Eggshell / Red</t>
+          <t>Balenciaga 3xl Split Logo White / Navy</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -11323,7 +10676,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-eggshell-red</t>
+          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-white-navy</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -11365,10 +10718,14 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Balenciaga 3xl Split Logo White / Navy</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr"/>
+          <t>Balenciaga Basketball Mule Silver / Black</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
       <c r="I14" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -11384,7 +10741,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-white-navy</t>
+          <t>https://www.kicksonfire.com/balenciaga-basketball-mule-silver-black</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -11426,14 +10783,10 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Balenciaga Basketball Mule Silver / Black</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>basketball</t>
-        </is>
-      </c>
+          <t>Balenciaga City Balenciaga Grey</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
       <c r="I15" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -11449,7 +10802,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-basketball-mule-silver-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-balenciaga-grey</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -11491,7 +10844,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Balenciaga City Balenciaga Grey</t>
+          <t>Balenciaga City Granny Green</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -11510,7 +10863,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-balenciaga-grey</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-granny-green</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -11552,10 +10905,14 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Balenciaga City Granny Green</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr"/>
+          <t>Balenciaga City WMNS Black</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I17" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -11571,7 +10928,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-granny-green</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-wmns-black</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -11613,12 +10970,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Balenciaga City WMNS Black</t>
+          <t>Balenciaga City WMNS Petal Pink</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>women, exclusive</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -11636,13 +10993,13 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-wmns-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-wmns-petal-pink</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="P18" t="n">
         <v>50</v>
@@ -11678,12 +11035,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Balenciaga City WMNS Petal Pink</t>
+          <t>Balenciaga City WMNS Silver</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>women, exclusive</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -11701,13 +11058,13 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-wmns-petal-pink</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-wmns-silver</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="P19" t="n">
         <v>50</v>
@@ -11743,12 +11100,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Balenciaga City WMNS Silver</t>
+          <t>Balenciaga Hamptons Medium Worn-Out Navy / Taupe</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>exclusive</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -11766,13 +11123,13 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-wmns-silver</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-navy-taupe</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="P20" t="n">
         <v>50</v>
@@ -11808,12 +11165,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Medium Worn-Out Navy / Taupe</t>
+          <t>Balenciaga Hamptons Medium Worn-Out WMNS Pink / White</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>exclusive</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -11831,13 +11188,13 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-navy-taupe</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-wmns-pink-white</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="P21" t="n">
         <v>50</v>
@@ -11873,7 +11230,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Medium Worn-Out WMNS Pink / White</t>
+          <t>Balenciaga Hamptons Platform WMNS Black</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -11896,7 +11253,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-wmns-pink-white</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-black</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
@@ -11938,7 +11295,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Platform WMNS Black</t>
+          <t>Balenciaga Hamptons Platform WMNS White</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -11961,7 +11318,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-white</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
@@ -12003,14 +11360,10 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Platform WMNS White</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Balenciaga Monday Ultra Black</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
       <c r="I24" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -12026,7 +11379,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-white</t>
+          <t>https://www.kicksonfire.com/balenciaga-monday-ultra-black</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -12068,10 +11421,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Balenciaga Monday Ultra Black</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr"/>
+          <t>Balenciaga Monday Ultra WMNS Brown / White</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I25" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -12087,7 +11444,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-monday-ultra-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-monday-ultra-wmns-brown-white</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>
@@ -13328,10 +12685,14 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
-        </is>
-      </c>
-      <c r="H45" t="inlineStr"/>
+          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>exclusive</t>
+        </is>
+      </c>
       <c r="I45" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -13353,7 +12714,7 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="P45" t="n">
         <v>50</v>
@@ -15810,6 +15171,71 @@
         <v>50</v>
       </c>
       <c r="Q84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="14" t="n">
+        <v>46115</v>
+      </c>
+      <c r="B85" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Apr 3 Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="J85" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="K85" t="n">
+        <v>1</v>
+      </c>
+      <c r="L85" t="inlineStr">
+        <is>
+          <t>/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr"/>
+      <c r="N85" t="inlineStr"/>
+      <c r="O85" t="n">
+        <v>12</v>
+      </c>
+      <c r="P85" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q85" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -16001,7 +15427,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="5"/>
@@ -16019,7 +15445,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="8">
@@ -16147,7 +15573,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="22"/>
@@ -16175,7 +15601,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="26">

--- a/output/weekly_tracker.xlsx
+++ b/output/weekly_tracker.xlsx
@@ -1220,7 +1220,7 @@
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga 3xl Split Logo Eggshell / Red</t>
+          <t>Balenciaga 3xl Extreme Lace Eggshell / Multicolor</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr"/>
@@ -1239,7 +1239,7 @@
       </c>
       <c r="L14" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-eggshell-red</t>
+          <t>https://www.kicksonfire.com/balenciaga-3xl-extreme-lace-eggshell-multicolor</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr"/>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga 3xl Split Logo White / Navy</t>
+          <t>Balenciaga 3xl Split Logo Eggshell / Red</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr"/>
@@ -1292,7 +1292,7 @@
       </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-white-navy</t>
+          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-eggshell-red</t>
         </is>
       </c>
       <c r="M15" s="10" t="inlineStr"/>
@@ -1326,14 +1326,10 @@
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Basketball Mule Silver / Black</t>
-        </is>
-      </c>
-      <c r="H16" s="10" t="inlineStr">
-        <is>
-          <t>basketball</t>
-        </is>
-      </c>
+          <t>Balenciaga 3xl Split Logo White / Navy</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr"/>
       <c r="I16" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -1349,7 +1345,7 @@
       </c>
       <c r="L16" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-basketball-mule-silver-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-white-navy</t>
         </is>
       </c>
       <c r="M16" s="10" t="inlineStr"/>
@@ -1383,10 +1379,14 @@
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City Balenciaga Grey</t>
-        </is>
-      </c>
-      <c r="H17" s="10" t="inlineStr"/>
+          <t>Balenciaga Basketball Mule Silver / Black</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -1402,7 +1402,7 @@
       </c>
       <c r="L17" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-balenciaga-grey</t>
+          <t>https://www.kicksonfire.com/balenciaga-basketball-mule-silver-black</t>
         </is>
       </c>
       <c r="M17" s="10" t="inlineStr"/>
@@ -1436,7 +1436,7 @@
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City Granny Green</t>
+          <t>Balenciaga City Balenciaga Grey</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr"/>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="L18" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-granny-green</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-balenciaga-grey</t>
         </is>
       </c>
       <c r="M18" s="10" t="inlineStr"/>
@@ -1489,14 +1489,10 @@
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City WMNS Black</t>
-        </is>
-      </c>
-      <c r="H19" s="10" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Balenciaga City Granny Green</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr"/>
       <c r="I19" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -1512,7 +1508,7 @@
       </c>
       <c r="L19" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-wmns-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-granny-green</t>
         </is>
       </c>
       <c r="M19" s="10" t="inlineStr"/>
@@ -1546,12 +1542,12 @@
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City WMNS Petal Pink</t>
+          <t>Balenciaga City WMNS Black</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>women, exclusive</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I20" s="9" t="inlineStr">
@@ -1569,7 +1565,7 @@
       </c>
       <c r="L20" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-wmns-petal-pink</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-wmns-black</t>
         </is>
       </c>
       <c r="M20" s="10" t="inlineStr"/>
@@ -1603,12 +1599,12 @@
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City WMNS Silver</t>
+          <t>Balenciaga City WMNS Petal Pink</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>women, exclusive</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
@@ -1626,7 +1622,7 @@
       </c>
       <c r="L21" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-wmns-silver</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-wmns-petal-pink</t>
         </is>
       </c>
       <c r="M21" s="10" t="inlineStr"/>
@@ -1660,12 +1656,12 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Medium Worn-Out Navy / Taupe</t>
+          <t>Balenciaga City WMNS Silver</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>exclusive</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I22" s="9" t="inlineStr">
@@ -1683,7 +1679,7 @@
       </c>
       <c r="L22" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-navy-taupe</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-wmns-silver</t>
         </is>
       </c>
       <c r="M22" s="10" t="inlineStr"/>
@@ -1717,12 +1713,12 @@
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Medium Worn-Out WMNS Pink / White</t>
+          <t>Balenciaga Hamptons Medium Worn-Out Navy / Taupe</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>exclusive</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr">
@@ -1740,7 +1736,7 @@
       </c>
       <c r="L23" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-wmns-pink-white</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-navy-taupe</t>
         </is>
       </c>
       <c r="M23" s="10" t="inlineStr"/>
@@ -1774,7 +1770,7 @@
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Platform WMNS Black</t>
+          <t>Balenciaga Hamptons Medium Worn-Out WMNS Pink / White</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
@@ -1797,7 +1793,7 @@
       </c>
       <c r="L24" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-wmns-pink-white</t>
         </is>
       </c>
       <c r="M24" s="10" t="inlineStr"/>
@@ -1831,7 +1827,7 @@
       </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Platform WMNS White</t>
+          <t>Balenciaga Hamptons Platform WMNS Black</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr">
@@ -1854,7 +1850,7 @@
       </c>
       <c r="L25" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-white</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-black</t>
         </is>
       </c>
       <c r="M25" s="10" t="inlineStr"/>
@@ -1888,10 +1884,14 @@
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Monday Ultra Black</t>
-        </is>
-      </c>
-      <c r="H26" s="10" t="inlineStr"/>
+          <t>Balenciaga Hamptons Platform WMNS White</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -1907,7 +1907,7 @@
       </c>
       <c r="L26" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-monday-ultra-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-white</t>
         </is>
       </c>
       <c r="M26" s="10" t="inlineStr"/>
@@ -1941,14 +1941,10 @@
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Monday Ultra WMNS Brown / White</t>
-        </is>
-      </c>
-      <c r="H27" s="10" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Balenciaga Monday Ultra Black</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr"/>
       <c r="I27" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -1964,7 +1960,7 @@
       </c>
       <c r="L27" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-monday-ultra-wmns-brown-white</t>
+          <t>https://www.kicksonfire.com/balenciaga-monday-ultra-black</t>
         </is>
       </c>
       <c r="M27" s="10" t="inlineStr"/>
@@ -5542,7 +5538,7 @@
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga 3xl Split Logo Eggshell / Red</t>
+          <t>Balenciaga 3xl Extreme Lace Eggshell / Multicolor</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr"/>
@@ -5561,7 +5557,7 @@
       </c>
       <c r="L14" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-eggshell-red</t>
+          <t>https://www.kicksonfire.com/balenciaga-3xl-extreme-lace-eggshell-multicolor</t>
         </is>
       </c>
       <c r="M14" s="10" t="inlineStr"/>
@@ -5595,7 +5591,7 @@
       </c>
       <c r="G15" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga 3xl Split Logo White / Navy</t>
+          <t>Balenciaga 3xl Split Logo Eggshell / Red</t>
         </is>
       </c>
       <c r="H15" s="10" t="inlineStr"/>
@@ -5614,7 +5610,7 @@
       </c>
       <c r="L15" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-white-navy</t>
+          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-eggshell-red</t>
         </is>
       </c>
       <c r="M15" s="10" t="inlineStr"/>
@@ -5648,14 +5644,10 @@
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Basketball Mule Silver / Black</t>
-        </is>
-      </c>
-      <c r="H16" s="10" t="inlineStr">
-        <is>
-          <t>basketball</t>
-        </is>
-      </c>
+          <t>Balenciaga 3xl Split Logo White / Navy</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr"/>
       <c r="I16" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -5671,7 +5663,7 @@
       </c>
       <c r="L16" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-basketball-mule-silver-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-white-navy</t>
         </is>
       </c>
       <c r="M16" s="10" t="inlineStr"/>
@@ -5705,10 +5697,14 @@
       </c>
       <c r="G17" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City Balenciaga Grey</t>
-        </is>
-      </c>
-      <c r="H17" s="10" t="inlineStr"/>
+          <t>Balenciaga Basketball Mule Silver / Black</t>
+        </is>
+      </c>
+      <c r="H17" s="10" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
       <c r="I17" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -5724,7 +5720,7 @@
       </c>
       <c r="L17" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-balenciaga-grey</t>
+          <t>https://www.kicksonfire.com/balenciaga-basketball-mule-silver-black</t>
         </is>
       </c>
       <c r="M17" s="10" t="inlineStr"/>
@@ -5758,7 +5754,7 @@
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City Granny Green</t>
+          <t>Balenciaga City Balenciaga Grey</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr"/>
@@ -5777,7 +5773,7 @@
       </c>
       <c r="L18" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-granny-green</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-balenciaga-grey</t>
         </is>
       </c>
       <c r="M18" s="10" t="inlineStr"/>
@@ -5811,14 +5807,10 @@
       </c>
       <c r="G19" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City WMNS Black</t>
-        </is>
-      </c>
-      <c r="H19" s="10" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Balenciaga City Granny Green</t>
+        </is>
+      </c>
+      <c r="H19" s="10" t="inlineStr"/>
       <c r="I19" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -5834,7 +5826,7 @@
       </c>
       <c r="L19" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-wmns-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-granny-green</t>
         </is>
       </c>
       <c r="M19" s="10" t="inlineStr"/>
@@ -5868,12 +5860,12 @@
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City WMNS Petal Pink</t>
+          <t>Balenciaga City WMNS Black</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr">
         <is>
-          <t>women, exclusive</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I20" s="9" t="inlineStr">
@@ -5891,7 +5883,7 @@
       </c>
       <c r="L20" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-wmns-petal-pink</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-wmns-black</t>
         </is>
       </c>
       <c r="M20" s="10" t="inlineStr"/>
@@ -5925,12 +5917,12 @@
       </c>
       <c r="G21" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga City WMNS Silver</t>
+          <t>Balenciaga City WMNS Petal Pink</t>
         </is>
       </c>
       <c r="H21" s="10" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>women, exclusive</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
@@ -5948,7 +5940,7 @@
       </c>
       <c r="L21" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-wmns-silver</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-wmns-petal-pink</t>
         </is>
       </c>
       <c r="M21" s="10" t="inlineStr"/>
@@ -5982,12 +5974,12 @@
       </c>
       <c r="G22" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Medium Worn-Out Navy / Taupe</t>
+          <t>Balenciaga City WMNS Silver</t>
         </is>
       </c>
       <c r="H22" s="10" t="inlineStr">
         <is>
-          <t>exclusive</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I22" s="9" t="inlineStr">
@@ -6005,7 +5997,7 @@
       </c>
       <c r="L22" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-navy-taupe</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-wmns-silver</t>
         </is>
       </c>
       <c r="M22" s="10" t="inlineStr"/>
@@ -6039,12 +6031,12 @@
       </c>
       <c r="G23" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Medium Worn-Out WMNS Pink / White</t>
+          <t>Balenciaga Hamptons Medium Worn-Out Navy / Taupe</t>
         </is>
       </c>
       <c r="H23" s="10" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>exclusive</t>
         </is>
       </c>
       <c r="I23" s="9" t="inlineStr">
@@ -6062,7 +6054,7 @@
       </c>
       <c r="L23" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-wmns-pink-white</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-navy-taupe</t>
         </is>
       </c>
       <c r="M23" s="10" t="inlineStr"/>
@@ -6096,7 +6088,7 @@
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Platform WMNS Black</t>
+          <t>Balenciaga Hamptons Medium Worn-Out WMNS Pink / White</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
@@ -6119,7 +6111,7 @@
       </c>
       <c r="L24" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-wmns-pink-white</t>
         </is>
       </c>
       <c r="M24" s="10" t="inlineStr"/>
@@ -6153,7 +6145,7 @@
       </c>
       <c r="G25" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Platform WMNS White</t>
+          <t>Balenciaga Hamptons Platform WMNS Black</t>
         </is>
       </c>
       <c r="H25" s="10" t="inlineStr">
@@ -6176,7 +6168,7 @@
       </c>
       <c r="L25" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-white</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-black</t>
         </is>
       </c>
       <c r="M25" s="10" t="inlineStr"/>
@@ -6210,10 +6202,14 @@
       </c>
       <c r="G26" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Monday Ultra Black</t>
-        </is>
-      </c>
-      <c r="H26" s="10" t="inlineStr"/>
+          <t>Balenciaga Hamptons Platform WMNS White</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I26" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -6229,7 +6225,7 @@
       </c>
       <c r="L26" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-monday-ultra-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-white</t>
         </is>
       </c>
       <c r="M26" s="10" t="inlineStr"/>
@@ -6263,14 +6259,10 @@
       </c>
       <c r="G27" s="10" t="inlineStr">
         <is>
-          <t>Balenciaga Monday Ultra WMNS Brown / White</t>
-        </is>
-      </c>
-      <c r="H27" s="10" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Balenciaga Monday Ultra Black</t>
+        </is>
+      </c>
+      <c r="H27" s="10" t="inlineStr"/>
       <c r="I27" s="9" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -6286,7 +6278,7 @@
       </c>
       <c r="L27" s="10" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-monday-ultra-wmns-brown-white</t>
+          <t>https://www.kicksonfire.com/balenciaga-monday-ultra-black</t>
         </is>
       </c>
       <c r="M27" s="10" t="inlineStr"/>
@@ -9608,13 +9600,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="9" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="51" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
@@ -9681,7 +9673,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Balenciaga Monday Ultra WMNS Brown / White</t>
+          <t>Balenciaga 3xl Extreme Lace Eggshell / Multicolor</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -9689,7 +9681,7 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-08T16:56:59Z</t>
+          <t>2026-03-08T17:51:33Z</t>
         </is>
       </c>
     </row>
@@ -9711,7 +9703,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Balenciaga 3xl Extreme Lace Eggshell / Multicolor</t>
+          <t>Balenciaga Monday Ultra WMNS Brown / White</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -9719,97 +9711,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-08T16:56:59Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Crocs</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>2026-03-08T16:56:59Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Crocs</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>2026-03-08T16:56:59Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2026-04-03</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>Apr 3 Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2026-03-08T16:56:59Z</t>
+          <t>2026-03-08T17:51:33Z</t>
         </is>
       </c>
     </row>
@@ -10596,7 +10498,7 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Balenciaga 3xl Split Logo Eggshell / Red</t>
+          <t>Balenciaga 3xl Extreme Lace Eggshell / Multicolor</t>
         </is>
       </c>
       <c r="H12" t="inlineStr"/>
@@ -10615,7 +10517,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-eggshell-red</t>
+          <t>https://www.kicksonfire.com/balenciaga-3xl-extreme-lace-eggshell-multicolor</t>
         </is>
       </c>
       <c r="M12" t="inlineStr"/>
@@ -10657,7 +10559,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Balenciaga 3xl Split Logo White / Navy</t>
+          <t>Balenciaga 3xl Split Logo Eggshell / Red</t>
         </is>
       </c>
       <c r="H13" t="inlineStr"/>
@@ -10676,7 +10578,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-white-navy</t>
+          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-eggshell-red</t>
         </is>
       </c>
       <c r="M13" t="inlineStr"/>
@@ -10718,14 +10620,10 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Balenciaga Basketball Mule Silver / Black</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>basketball</t>
-        </is>
-      </c>
+          <t>Balenciaga 3xl Split Logo White / Navy</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
       <c r="I14" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -10741,7 +10639,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-basketball-mule-silver-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-3xl-split-logo-white-navy</t>
         </is>
       </c>
       <c r="M14" t="inlineStr"/>
@@ -10783,10 +10681,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Balenciaga City Balenciaga Grey</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr"/>
+          <t>Balenciaga Basketball Mule Silver / Black</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
       <c r="I15" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -10802,7 +10704,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-balenciaga-grey</t>
+          <t>https://www.kicksonfire.com/balenciaga-basketball-mule-silver-black</t>
         </is>
       </c>
       <c r="M15" t="inlineStr"/>
@@ -10844,7 +10746,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Balenciaga City Granny Green</t>
+          <t>Balenciaga City Balenciaga Grey</t>
         </is>
       </c>
       <c r="H16" t="inlineStr"/>
@@ -10863,7 +10765,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-granny-green</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-balenciaga-grey</t>
         </is>
       </c>
       <c r="M16" t="inlineStr"/>
@@ -10905,14 +10807,10 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Balenciaga City WMNS Black</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Balenciaga City Granny Green</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
       <c r="I17" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -10928,7 +10826,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-wmns-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-granny-green</t>
         </is>
       </c>
       <c r="M17" t="inlineStr"/>
@@ -10970,12 +10868,12 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Balenciaga City WMNS Petal Pink</t>
+          <t>Balenciaga City WMNS Black</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>women, exclusive</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -10993,13 +10891,13 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-wmns-petal-pink</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-wmns-black</t>
         </is>
       </c>
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="P18" t="n">
         <v>50</v>
@@ -11035,12 +10933,12 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Balenciaga City WMNS Silver</t>
+          <t>Balenciaga City WMNS Petal Pink</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>women, exclusive</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -11058,13 +10956,13 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-city-wmns-silver</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-wmns-petal-pink</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
       <c r="N19" t="inlineStr"/>
       <c r="O19" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="P19" t="n">
         <v>50</v>
@@ -11100,12 +10998,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Medium Worn-Out Navy / Taupe</t>
+          <t>Balenciaga City WMNS Silver</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>exclusive</t>
+          <t>women</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -11123,13 +11021,13 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-navy-taupe</t>
+          <t>https://www.kicksonfire.com/balenciaga-city-wmns-silver</t>
         </is>
       </c>
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="P20" t="n">
         <v>50</v>
@@ -11165,12 +11063,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Medium Worn-Out WMNS Pink / White</t>
+          <t>Balenciaga Hamptons Medium Worn-Out Navy / Taupe</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>exclusive</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -11188,13 +11086,13 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-wmns-pink-white</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-navy-taupe</t>
         </is>
       </c>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="P21" t="n">
         <v>50</v>
@@ -11230,7 +11128,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Platform WMNS Black</t>
+          <t>Balenciaga Hamptons Medium Worn-Out WMNS Pink / White</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
@@ -11253,7 +11151,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-medium-worn-out-wmns-pink-white</t>
         </is>
       </c>
       <c r="M22" t="inlineStr"/>
@@ -11295,7 +11193,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Balenciaga Hamptons Platform WMNS White</t>
+          <t>Balenciaga Hamptons Platform WMNS Black</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -11318,7 +11216,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-white</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-black</t>
         </is>
       </c>
       <c r="M23" t="inlineStr"/>
@@ -11360,10 +11258,14 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Balenciaga Monday Ultra Black</t>
-        </is>
-      </c>
-      <c r="H24" t="inlineStr"/>
+          <t>Balenciaga Hamptons Platform WMNS White</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
       <c r="I24" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -11379,7 +11281,7 @@
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-monday-ultra-black</t>
+          <t>https://www.kicksonfire.com/balenciaga-hamptons-platform-wmns-white</t>
         </is>
       </c>
       <c r="M24" t="inlineStr"/>
@@ -11421,14 +11323,10 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Balenciaga Monday Ultra WMNS Brown / White</t>
-        </is>
-      </c>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>Balenciaga Monday Ultra Black</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr">
         <is>
           <t>kicksonfire</t>
@@ -11444,7 +11342,7 @@
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>https://www.kicksonfire.com/balenciaga-monday-ultra-wmns-brown-white</t>
+          <t>https://www.kicksonfire.com/balenciaga-monday-ultra-black</t>
         </is>
       </c>
       <c r="M25" t="inlineStr"/>

--- a/output/weekly_tracker.xlsx
+++ b/output/weekly_tracker.xlsx
@@ -528,7 +528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O83"/>
+  <dimension ref="A1:O96"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="26" customWidth="1" min="1" max="1"/>
@@ -983,9 +983,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -1000,7 +1000,7 @@
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>Jordan Retro 13 BOYS TODDLER • WHITE/BLACK/TRUE RED</t>
         </is>
       </c>
       <c r="H10" s="10" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="K10" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L10" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/D3004102.html</t>
         </is>
       </c>
       <c r="M10" s="10" t="inlineStr"/>
@@ -1052,17 +1052,17 @@
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Converse Grade School SHAI 001 Blush BOYS GRADE SCHOOL • OX TICKEKLED PINK/GERANIUM PINK</t>
+          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>exclusive</t>
+          <t>retro</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
@@ -1076,11 +1076,11 @@
         </is>
       </c>
       <c r="K11" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L11" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/converse/A19838C.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
         </is>
       </c>
       <c r="M11" s="10" t="inlineStr"/>
@@ -1097,9 +1097,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
+          <t>ENTRIES OPEN App entry Converse Grade School SHAI 001 Blush BOYS GRADE SCHOOL • OX TICKEKLED PINK/GERANIUM PINK</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
@@ -1133,11 +1133,11 @@
         </is>
       </c>
       <c r="K12" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L12" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/crocs/46212953.html</t>
+          <t>https://www.footlocker.com/release-calendar/converse/A19838C.html</t>
         </is>
       </c>
       <c r="M12" s="10" t="inlineStr"/>
@@ -1166,27 +1166,27 @@
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>Air Max Ishod Iron Grey and Photon Dust</t>
+          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>exclusive</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J13" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K13" s="9" t="n">
@@ -1194,7 +1194,7 @@
       </c>
       <c r="L13" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-max-ishod-iron-grey-and-photon-dust-1</t>
+          <t>https://www.footlocker.com/release-calendar/crocs/46212953.html</t>
         </is>
       </c>
       <c r="M13" s="10" t="inlineStr"/>
@@ -2055,7 +2055,7 @@
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+          <t>Nike LeBron 23 'LeBronto'</t>
         </is>
       </c>
       <c r="H29" s="10" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J29" s="9" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K29" s="9" t="n">
@@ -2078,7 +2078,7 @@
       </c>
       <c r="L29" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
+          <t>https://thedropdate.com/sneakers/nike-lebron-23-lebronto-ih1513-602/706595</t>
         </is>
       </c>
       <c r="M29" s="10" t="inlineStr"/>
@@ -2095,9 +2095,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
@@ -2112,10 +2112,14 @@
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="H30" s="10" t="inlineStr"/>
+          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -2127,11 +2131,11 @@
         </is>
       </c>
       <c r="K30" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L30" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
         </is>
       </c>
       <c r="M30" s="10" t="inlineStr"/>
@@ -2148,9 +2152,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -2165,14 +2169,10 @@
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t>Nike Sabrina 3 MENS • YELLOW STRIKE/APPLE GREEN/PALE YELLOW</t>
-        </is>
-      </c>
-      <c r="H31" s="10" t="inlineStr">
-        <is>
-          <t>basketball</t>
-        </is>
-      </c>
+          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="H31" s="10" t="inlineStr"/>
       <c r="I31" s="9" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -2184,11 +2184,11 @@
         </is>
       </c>
       <c r="K31" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L31" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/R2478700.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
         </is>
       </c>
       <c r="M31" s="10" t="inlineStr"/>
@@ -2222,18 +2222,22 @@
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>Nike SB Ishod Apparel Collection</t>
-        </is>
-      </c>
-      <c r="H32" s="10" t="inlineStr"/>
+          <t>Nike Sabrina 3 MENS • YELLOW STRIKE/APPLE GREEN/PALE YELLOW</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K32" s="9" t="n">
@@ -2241,7 +2245,7 @@
       </c>
       <c r="L32" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/nike-sb-ishod-apparel-collection-static</t>
+          <t>https://www.footlocker.com/release-calendar/nike/R2478700.html</t>
         </is>
       </c>
       <c r="M32" s="10" t="inlineStr"/>
@@ -4255,7 +4259,7 @@
       </c>
       <c r="G69" s="10" t="inlineStr">
         <is>
-          <t>Finesse x ASICS GEL-CUMULUS 16 'Desert Rose' From £ 165</t>
+          <t>ASICS Gel-kayano 14 'Olive' From £ 165</t>
         </is>
       </c>
       <c r="H69" s="10" t="inlineStr"/>
@@ -4274,7 +4278,7 @@
       </c>
       <c r="L69" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/asics-gel-cumulus-16-finesse-desert-rose-1203b003-200/668694</t>
+          <t>https://thedropdate.com/sneakers/asics-gel-kayano-14-white-1203a537-111/705592</t>
         </is>
       </c>
       <c r="M69" s="10" t="inlineStr"/>
@@ -4303,12 +4307,12 @@
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="G70" s="10" t="inlineStr">
         <is>
-          <t>New Balance 993 Made in USA 'Passion Fruit' From £ 205</t>
+          <t>Finesse x ASICS GEL-CUMULUS 16 'Desert Rose' From £ 165</t>
         </is>
       </c>
       <c r="H70" s="10" t="inlineStr"/>
@@ -4327,7 +4331,7 @@
       </c>
       <c r="L70" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-993-made-in-usa-passion-fruit-u9934ja/705132</t>
+          <t>https://thedropdate.com/sneakers/asics-gel-cumulus-16-finesse-desert-rose-1203b003-200/668694</t>
         </is>
       </c>
       <c r="M70" s="10" t="inlineStr"/>
@@ -4356,12 +4360,12 @@
       </c>
       <c r="F71" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G71" s="10" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 ’07 'Cherry Blossom' From £ 120</t>
+          <t>CAYL x New Balance M10L 'Black Ink' From £ 140</t>
         </is>
       </c>
       <c r="H71" s="10" t="inlineStr"/>
@@ -4380,7 +4384,7 @@
       </c>
       <c r="L71" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nikes-air-force-1-07-spring-flowers-iq3472-298/669922</t>
+          <t>https://thedropdate.com/sneakers/new-balance-m10l-blue-mtm10lcl/671644</t>
         </is>
       </c>
       <c r="M71" s="10" t="inlineStr"/>
@@ -4392,9 +4396,9 @@
         <v>46093</v>
       </c>
       <c r="B72" s="5" t="inlineStr"/>
-      <c r="C72" s="11" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
@@ -4409,19 +4413,15 @@
       </c>
       <c r="F72" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G72" s="10" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 'Paisley Bandana' From £ 180</t>
-        </is>
-      </c>
-      <c r="H72" s="10" t="inlineStr">
-        <is>
-          <t>hot-model, running</t>
-        </is>
-      </c>
+          <t>CAYL x New Balance UTRNCA 'Slate Grey' From £ 155</t>
+        </is>
+      </c>
+      <c r="H72" s="10" t="inlineStr"/>
       <c r="I72" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -4437,7 +4437,7 @@
       </c>
       <c r="L72" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-air-max-95-paisley-bandana-iq0620-100/705853</t>
+          <t>https://thedropdate.com/sneakers/cayl-x-new-balance-utrnv11-slate-grey-utrnca/705387</t>
         </is>
       </c>
       <c r="M72" s="10" t="inlineStr"/>
@@ -4446,12 +4446,12 @@
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="B73" s="5" t="inlineStr"/>
-      <c r="C73" s="11" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
@@ -4466,27 +4466,23 @@
       </c>
       <c r="F73" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G73" s="10" t="inlineStr">
         <is>
-          <t>Mar 13 Kobe 3 Low Protro Pink Quartz</t>
-        </is>
-      </c>
-      <c r="H73" s="10" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
+          <t>New Balance 993 Made in USA 'Passion Fruit' From £ 205</t>
+        </is>
+      </c>
+      <c r="H73" s="10" t="inlineStr"/>
       <c r="I73" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J73" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K73" s="9" t="n">
@@ -4494,7 +4490,7 @@
       </c>
       <c r="L73" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/kobe-3-low-protro-pink-quartz</t>
+          <t>https://thedropdate.com/sneakers/new-balance-993-made-in-usa-passion-fruit-u9934ja/705132</t>
         </is>
       </c>
       <c r="M73" s="10" t="inlineStr"/>
@@ -4503,7 +4499,7 @@
     </row>
     <row r="74">
       <c r="A74" s="4" t="n">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="B74" s="5" t="inlineStr"/>
       <c r="C74" s="6" t="inlineStr">
@@ -4528,7 +4524,7 @@
       </c>
       <c r="G74" s="10" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low 'Asparagus &amp; Chlorophyll' From £ 118</t>
+          <t>Nike Air Force 1 ’07 'Cherry Blossom' From £ 120</t>
         </is>
       </c>
       <c r="H74" s="10" t="inlineStr"/>
@@ -4547,7 +4543,7 @@
       </c>
       <c r="L74" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-air-force-1-low-io5011-300/704355</t>
+          <t>https://thedropdate.com/sneakers/nikes-air-force-1-07-spring-flowers-iq3472-298/669922</t>
         </is>
       </c>
       <c r="M74" s="10" t="inlineStr"/>
@@ -4556,12 +4552,12 @@
     </row>
     <row r="75">
       <c r="A75" s="4" t="n">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="B75" s="5" t="inlineStr"/>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C75" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
@@ -4581,12 +4577,12 @@
       </c>
       <c r="G75" s="10" t="inlineStr">
         <is>
-          <t>Veneda Carter x Nike Air Max Muse 'White &amp; Racer Blue' From £ 145</t>
+          <t>Nike Air Max 95 'Paisley Bandana' From £ 180</t>
         </is>
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>hot-model, running</t>
         </is>
       </c>
       <c r="I75" s="9" t="inlineStr">
@@ -4604,7 +4600,7 @@
       </c>
       <c r="L75" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/veneda-carter-x-nike-air-max-muse-white-racer-blue-hv9929-100/700942</t>
+          <t>https://thedropdate.com/sneakers/nike-air-max-95-paisley-bandana-iq0620-100/705853</t>
         </is>
       </c>
       <c r="M75" s="10" t="inlineStr"/>
@@ -4613,12 +4609,12 @@
     </row>
     <row r="76">
       <c r="A76" s="4" t="n">
-        <v>46095</v>
+        <v>46093</v>
       </c>
       <c r="B76" s="5" t="inlineStr"/>
-      <c r="C76" s="11" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
@@ -4633,19 +4629,15 @@
       </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G76" s="10" t="inlineStr">
         <is>
-          <t>Air Jordan 13 Retro 'True Red' - 2026 From £ 185</t>
-        </is>
-      </c>
-      <c r="H76" s="10" t="inlineStr">
-        <is>
-          <t>hot-model, retro</t>
-        </is>
-      </c>
+          <t>NikeSKIMS Rift Mesh 'Black' From £ 145</t>
+        </is>
+      </c>
+      <c r="H76" s="10" t="inlineStr"/>
       <c r="I76" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -4661,7 +4653,7 @@
       </c>
       <c r="L76" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/air-jordan-13-retro-true-red-2026-414571-102/705921</t>
+          <t>https://thedropdate.com/sneakers/skims-x-nike-air-rift-black-io7694-001/700295</t>
         </is>
       </c>
       <c r="M76" s="10" t="inlineStr"/>
@@ -4670,7 +4662,7 @@
     </row>
     <row r="77">
       <c r="A77" s="4" t="n">
-        <v>46095</v>
+        <v>46093</v>
       </c>
       <c r="B77" s="5" t="inlineStr"/>
       <c r="C77" s="6" t="inlineStr">
@@ -4690,19 +4682,15 @@
       </c>
       <c r="F77" s="9" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G77" s="10" t="inlineStr">
         <is>
-          <t>Air Jordan 9 Retro 'Flint Grey' - 2026 From £ 189</t>
-        </is>
-      </c>
-      <c r="H77" s="10" t="inlineStr">
-        <is>
-          <t>retro</t>
-        </is>
-      </c>
+          <t>NikeSKIMS Rift Mesh 'Light Bone' From £ 145</t>
+        </is>
+      </c>
+      <c r="H77" s="10" t="inlineStr"/>
       <c r="I77" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -4718,7 +4706,7 @@
       </c>
       <c r="L77" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/air-jordan-9-retro-flint-grey-and-french-blue-hv4794-100/701944</t>
+          <t>https://thedropdate.com/sneakers/nikeskims-rift-mesh-light-bone-io7694-002/706596</t>
         </is>
       </c>
       <c r="M77" s="10" t="inlineStr"/>
@@ -4727,55 +4715,51 @@
     </row>
     <row r="78">
       <c r="A78" s="4" t="n">
-        <v>46095</v>
+        <v>46093</v>
       </c>
       <c r="B78" s="5" t="inlineStr"/>
-      <c r="C78" s="11" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D78" s="12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E78" s="13" t="inlineStr">
-        <is>
-          <t>Watch</t>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F78" s="9" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G78" s="10" t="inlineStr">
         <is>
-          <t>Mar 14 Infant/Toddler Shoes Jordan 13 Retro</t>
-        </is>
-      </c>
-      <c r="H78" s="10" t="inlineStr">
-        <is>
-          <t>hot-model, retro</t>
-        </is>
-      </c>
+          <t>NikeSKIMS Rift Mesh 'Velvet Brown' From £ 145</t>
+        </is>
+      </c>
+      <c r="H78" s="10" t="inlineStr"/>
       <c r="I78" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J78" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K78" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L78" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
+          <t>https://thedropdate.com/sneakers/skims-x-nike-air-rift-velvet-brown-io7694-200/700297</t>
         </is>
       </c>
       <c r="M78" s="10" t="inlineStr"/>
@@ -4784,12 +4768,12 @@
     </row>
     <row r="79">
       <c r="A79" s="4" t="n">
-        <v>46095</v>
+        <v>46094</v>
       </c>
       <c r="B79" s="5" t="inlineStr"/>
-      <c r="C79" s="11" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -4804,19 +4788,15 @@
       </c>
       <c r="F79" s="9" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="G79" s="10" t="inlineStr">
         <is>
-          <t>Travis Scott x Air Jordan Jumpman Jack 'Green Spark' From £ 185</t>
-        </is>
-      </c>
-      <c r="H79" s="10" t="inlineStr">
-        <is>
-          <t>collab</t>
-        </is>
-      </c>
+          <t>adidas Anthony Edwards 2 'Georgia Bulldogs' From £ 120</t>
+        </is>
+      </c>
+      <c r="H79" s="10" t="inlineStr"/>
       <c r="I79" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -4832,7 +4812,7 @@
       </c>
       <c r="L79" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/air-jordan-x-travis-scott-jumpman-jack-green-spark-im9113-300/704688</t>
+          <t>https://thedropdate.com/sneakers/adidas-anthony-edwards-2-georgia-bulldogs-jq9497/706523</t>
         </is>
       </c>
       <c r="M79" s="10" t="inlineStr"/>
@@ -4841,7 +4821,7 @@
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
-        <v>46099</v>
+        <v>46094</v>
       </c>
       <c r="B80" s="5" t="inlineStr"/>
       <c r="C80" s="11" t="inlineStr">
@@ -4861,17 +4841,17 @@
       </c>
       <c r="F80" s="9" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G80" s="10" t="inlineStr">
         <is>
-          <t>Mar 18 Air Jordan 1 Low OG Sail and Coconut Milk</t>
+          <t>Mar 13 Kobe 3 Low Protro Pink Quartz</t>
         </is>
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>hot-model</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="I80" s="9" t="inlineStr">
@@ -4889,7 +4869,7 @@
       </c>
       <c r="L80" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
+          <t>/launch/t/kobe-3-low-protro-pink-quartz</t>
         </is>
       </c>
       <c r="M80" s="10" t="inlineStr"/>
@@ -4898,7 +4878,7 @@
     </row>
     <row r="81">
       <c r="A81" s="4" t="n">
-        <v>46099</v>
+        <v>46094</v>
       </c>
       <c r="B81" s="5" t="inlineStr"/>
       <c r="C81" s="6" t="inlineStr">
@@ -4918,12 +4898,12 @@
       </c>
       <c r="F81" s="9" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G81" s="10" t="inlineStr">
         <is>
-          <t>One Piece x Crocs Classic Clog 'Zoro'</t>
+          <t>Nike Air Force 1 Low 'Asparagus &amp; Chlorophyll' From £ 118</t>
         </is>
       </c>
       <c r="H81" s="10" t="inlineStr"/>
@@ -4942,7 +4922,7 @@
       </c>
       <c r="L81" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-zoro-212953-90h/706159</t>
+          <t>https://thedropdate.com/sneakers/nike-air-force-1-low-io5011-300/704355</t>
         </is>
       </c>
       <c r="M81" s="10" t="inlineStr"/>
@@ -4951,7 +4931,7 @@
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
-        <v>46100</v>
+        <v>46094</v>
       </c>
       <c r="B82" s="5" t="inlineStr"/>
       <c r="C82" s="6" t="inlineStr">
@@ -4971,15 +4951,19 @@
       </c>
       <c r="F82" s="9" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G82" s="10" t="inlineStr">
         <is>
-          <t>New Balance 991v1 Made in UK 'Oyster Grey' From £ 220</t>
-        </is>
-      </c>
-      <c r="H82" s="10" t="inlineStr"/>
+          <t>Veneda Carter x Nike Air Max Muse 'White &amp; Racer Blue' From £ 145</t>
+        </is>
+      </c>
+      <c r="H82" s="10" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
       <c r="I82" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -4995,7 +4979,7 @@
       </c>
       <c r="L82" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-991v1-made-in-uk-oyster-grey-m991cr1/706155</t>
+          <t>https://thedropdate.com/sneakers/veneda-carter-x-nike-air-max-muse-white-racer-blue-hv9929-100/700942</t>
         </is>
       </c>
       <c r="M82" s="10" t="inlineStr"/>
@@ -5004,12 +4988,12 @@
     </row>
     <row r="83">
       <c r="A83" s="4" t="n">
-        <v>46101</v>
+        <v>46095</v>
       </c>
       <c r="B83" s="5" t="inlineStr"/>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C83" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
@@ -5024,17 +5008,17 @@
       </c>
       <c r="F83" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G83" s="10" t="inlineStr">
         <is>
-          <t>Nike First Sight Noir WMNS 'Black' From £ 110</t>
+          <t>Air Jordan 13 Retro 'True Red' - 2026 From £ 185</t>
         </is>
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="I83" s="9" t="inlineStr">
@@ -5052,12 +5036,737 @@
       </c>
       <c r="L83" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-first-sight-noir-wmns-black-hq2409-001/706328</t>
+          <t>https://thedropdate.com/sneakers/air-jordan-13-retro-true-red-2026-414571-102/705921</t>
         </is>
       </c>
       <c r="M83" s="10" t="inlineStr"/>
       <c r="N83" s="10" t="inlineStr"/>
       <c r="O83" s="5" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" s="4" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B84" s="5" t="inlineStr"/>
+      <c r="C84" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D84" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F84" s="9" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="G84" s="10" t="inlineStr">
+        <is>
+          <t>Air Jordan 9 Retro 'Flint Grey' - 2026 From £ 189</t>
+        </is>
+      </c>
+      <c r="H84" s="10" t="inlineStr">
+        <is>
+          <t>retro</t>
+        </is>
+      </c>
+      <c r="I84" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J84" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K84" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L84" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/air-jordan-9-retro-flint-grey-and-french-blue-hv4794-100/701944</t>
+        </is>
+      </c>
+      <c r="M84" s="10" t="inlineStr"/>
+      <c r="N84" s="10" t="inlineStr"/>
+      <c r="O84" s="5" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="4" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B85" s="5" t="inlineStr"/>
+      <c r="C85" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D85" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E85" s="13" t="inlineStr">
+        <is>
+          <t>Watch</t>
+        </is>
+      </c>
+      <c r="F85" s="9" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="G85" s="10" t="inlineStr">
+        <is>
+          <t>Mar 14 Infant/Toddler Shoes Jordan 13 Retro</t>
+        </is>
+      </c>
+      <c r="H85" s="10" t="inlineStr">
+        <is>
+          <t>hot-model, retro</t>
+        </is>
+      </c>
+      <c r="I85" s="9" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="J85" s="9" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="K85" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L85" s="10" t="inlineStr">
+        <is>
+          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
+        </is>
+      </c>
+      <c r="M85" s="10" t="inlineStr"/>
+      <c r="N85" s="10" t="inlineStr"/>
+      <c r="O85" s="5" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="4" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B86" s="5" t="inlineStr"/>
+      <c r="C86" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D86" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E86" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F86" s="9" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="G86" s="10" t="inlineStr">
+        <is>
+          <t>Travis Scott x Air Jordan Jumpman Jack 'Green Spark' From £ 185</t>
+        </is>
+      </c>
+      <c r="H86" s="10" t="inlineStr">
+        <is>
+          <t>collab</t>
+        </is>
+      </c>
+      <c r="I86" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J86" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K86" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L86" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/air-jordan-x-travis-scott-jumpman-jack-green-spark-im9113-300/704688</t>
+        </is>
+      </c>
+      <c r="M86" s="10" t="inlineStr"/>
+      <c r="N86" s="10" t="inlineStr"/>
+      <c r="O86" s="5" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" s="4" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B87" s="5" t="inlineStr"/>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D87" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E87" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F87" s="9" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G87" s="10" t="inlineStr">
+        <is>
+          <t>Jacquemus x Nike Moon Shoe SP 'Fauna Brown' From £ 163</t>
+        </is>
+      </c>
+      <c r="H87" s="10" t="inlineStr"/>
+      <c r="I87" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J87" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K87" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L87" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/jacquemus-x-nike-moon-shoe-sp-fauna-brown-hv8547-200/705860</t>
+        </is>
+      </c>
+      <c r="M87" s="10" t="inlineStr"/>
+      <c r="N87" s="10" t="inlineStr"/>
+      <c r="O87" s="5" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" s="4" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B88" s="5" t="inlineStr"/>
+      <c r="C88" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D88" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E88" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F88" s="9" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G88" s="10" t="inlineStr">
+        <is>
+          <t>Jacquemus x Nike Moon Shoe SP 'Soft Pearl' From £ 163</t>
+        </is>
+      </c>
+      <c r="H88" s="10" t="inlineStr">
+        <is>
+          <t>exclusive</t>
+        </is>
+      </c>
+      <c r="I88" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J88" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K88" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L88" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/jacquemus-x-nike-moon-shoe-sp-soft-pearl-hv8547-002/705859</t>
+        </is>
+      </c>
+      <c r="M88" s="10" t="inlineStr"/>
+      <c r="N88" s="10" t="inlineStr"/>
+      <c r="O88" s="5" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" s="4" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B89" s="5" t="inlineStr"/>
+      <c r="C89" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E89" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F89" s="9" t="inlineStr">
+        <is>
+          <t>Adidas</t>
+        </is>
+      </c>
+      <c r="G89" s="10" t="inlineStr">
+        <is>
+          <t>adidas Hyperboost Edge 'White &amp; Pure Ruby' From £ 170</t>
+        </is>
+      </c>
+      <c r="H89" s="10" t="inlineStr">
+        <is>
+          <t>exclusive</t>
+        </is>
+      </c>
+      <c r="I89" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J89" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K89" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L89" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/adidas-hyperboost-edge-white-pure-ruby-ki1913/706498</t>
+        </is>
+      </c>
+      <c r="M89" s="10" t="inlineStr"/>
+      <c r="N89" s="10" t="inlineStr"/>
+      <c r="O89" s="5" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" s="4" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B90" s="5" t="inlineStr"/>
+      <c r="C90" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D90" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E90" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F90" s="9" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="G90" s="10" t="inlineStr">
+        <is>
+          <t>Dashawn Jordan x Nike SB Dunk Low 'Bright Spruce' From £ 120</t>
+        </is>
+      </c>
+      <c r="H90" s="10" t="inlineStr">
+        <is>
+          <t>hot-model</t>
+        </is>
+      </c>
+      <c r="I90" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J90" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K90" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L90" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/nike-sb-x-dashawn-jordan-dunk-low-black-bright-spruce-ib6208-200/703258</t>
+        </is>
+      </c>
+      <c r="M90" s="10" t="inlineStr"/>
+      <c r="N90" s="10" t="inlineStr"/>
+      <c r="O90" s="5" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B91" s="5" t="inlineStr"/>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D91" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E91" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F91" s="9" t="inlineStr">
+        <is>
+          <t>Adidas</t>
+        </is>
+      </c>
+      <c r="G91" s="10" t="inlineStr">
+        <is>
+          <t>adidas Adizero Dropset Elite 'Solar Red' From £ 230</t>
+        </is>
+      </c>
+      <c r="H91" s="10" t="inlineStr"/>
+      <c r="I91" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J91" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K91" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L91" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/adidas-adizero-dropset-elite-solar-red-la6218/706499</t>
+        </is>
+      </c>
+      <c r="M91" s="10" t="inlineStr"/>
+      <c r="N91" s="10" t="inlineStr"/>
+      <c r="O91" s="5" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B92" s="5" t="inlineStr"/>
+      <c r="C92" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D92" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E92" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F92" s="9" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="G92" s="10" t="inlineStr">
+        <is>
+          <t>Air Jordan 3 'Spring Is In The Air' From £ 189</t>
+        </is>
+      </c>
+      <c r="H92" s="10" t="inlineStr">
+        <is>
+          <t>hot-model</t>
+        </is>
+      </c>
+      <c r="I92" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J92" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K92" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L92" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/air-jordan-3-spring-is-in-the-air-if4396-100/703366</t>
+        </is>
+      </c>
+      <c r="M92" s="10" t="inlineStr"/>
+      <c r="N92" s="10" t="inlineStr"/>
+      <c r="O92" s="5" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B93" s="5" t="inlineStr"/>
+      <c r="C93" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F93" s="9" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="G93" s="10" t="inlineStr">
+        <is>
+          <t>Mar 18 Air Jordan 1 Low OG Sail and Coconut Milk</t>
+        </is>
+      </c>
+      <c r="H93" s="10" t="inlineStr">
+        <is>
+          <t>hot-model</t>
+        </is>
+      </c>
+      <c r="I93" s="9" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="J93" s="9" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="K93" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L93" s="10" t="inlineStr">
+        <is>
+          <t>/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
+        </is>
+      </c>
+      <c r="M93" s="10" t="inlineStr"/>
+      <c r="N93" s="10" t="inlineStr"/>
+      <c r="O93" s="5" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B94" s="5" t="inlineStr"/>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F94" s="9" t="inlineStr">
+        <is>
+          <t>Crocs</t>
+        </is>
+      </c>
+      <c r="G94" s="10" t="inlineStr">
+        <is>
+          <t>One Piece x Crocs Classic Clog 'Zoro'</t>
+        </is>
+      </c>
+      <c r="H94" s="10" t="inlineStr"/>
+      <c r="I94" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J94" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K94" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L94" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-zoro-212953-90h/706159</t>
+        </is>
+      </c>
+      <c r="M94" s="10" t="inlineStr"/>
+      <c r="N94" s="10" t="inlineStr"/>
+      <c r="O94" s="5" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B95" s="5" t="inlineStr"/>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F95" s="9" t="inlineStr">
+        <is>
+          <t>New Balance</t>
+        </is>
+      </c>
+      <c r="G95" s="10" t="inlineStr">
+        <is>
+          <t>New Balance 991v1 Made in UK 'Oyster Grey' From £ 220</t>
+        </is>
+      </c>
+      <c r="H95" s="10" t="inlineStr"/>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J95" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K95" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L95" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/new-balance-991v1-made-in-uk-oyster-grey-m991cr1/706155</t>
+        </is>
+      </c>
+      <c r="M95" s="10" t="inlineStr"/>
+      <c r="N95" s="10" t="inlineStr"/>
+      <c r="O95" s="5" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B96" s="5" t="inlineStr"/>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F96" s="9" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G96" s="10" t="inlineStr">
+        <is>
+          <t>Nike First Sight Noir WMNS 'Black' From £ 110</t>
+        </is>
+      </c>
+      <c r="H96" s="10" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J96" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K96" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L96" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/nike-first-sight-noir-wmns-black-hq2409-001/706328</t>
+        </is>
+      </c>
+      <c r="M96" s="10" t="inlineStr"/>
+      <c r="N96" s="10" t="inlineStr"/>
+      <c r="O96" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -5074,7 +5783,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O92"/>
+  <dimension ref="A1:O102"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="39" customWidth="1" min="1" max="1"/>
@@ -5529,9 +6238,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D10" s="12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="D10" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="E10" s="8" t="inlineStr">
@@ -5546,7 +6255,7 @@
       </c>
       <c r="G10" s="10" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>Jordan Retro 13 BOYS TODDLER • WHITE/BLACK/TRUE RED</t>
         </is>
       </c>
       <c r="H10" s="10" t="inlineStr">
@@ -5565,11 +6274,11 @@
         </is>
       </c>
       <c r="K10" s="9" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L10" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/D3004102.html</t>
         </is>
       </c>
       <c r="M10" s="10" t="inlineStr"/>
@@ -5598,17 +6307,17 @@
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G11" s="10" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Converse Grade School SHAI 001 Blush BOYS GRADE SCHOOL • OX TICKEKLED PINK/GERANIUM PINK</t>
+          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="H11" s="10" t="inlineStr">
         <is>
-          <t>exclusive</t>
+          <t>retro</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
@@ -5622,11 +6331,11 @@
         </is>
       </c>
       <c r="K11" s="9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L11" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/converse/A19838C.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
         </is>
       </c>
       <c r="M11" s="10" t="inlineStr"/>
@@ -5643,9 +6352,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D12" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
@@ -5655,12 +6364,12 @@
       </c>
       <c r="F12" s="9" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="G12" s="10" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
+          <t>ENTRIES OPEN App entry Converse Grade School SHAI 001 Blush BOYS GRADE SCHOOL • OX TICKEKLED PINK/GERANIUM PINK</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
@@ -5679,11 +6388,11 @@
         </is>
       </c>
       <c r="K12" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L12" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/crocs/46212953.html</t>
+          <t>https://www.footlocker.com/release-calendar/converse/A19838C.html</t>
         </is>
       </c>
       <c r="M12" s="10" t="inlineStr"/>
@@ -5712,27 +6421,27 @@
       </c>
       <c r="F13" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="G13" s="10" t="inlineStr">
         <is>
-          <t>Air Max Ishod Iron Grey and Photon Dust</t>
+          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
         </is>
       </c>
       <c r="H13" s="10" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>exclusive</t>
         </is>
       </c>
       <c r="I13" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J13" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K13" s="9" t="n">
@@ -5740,7 +6449,7 @@
       </c>
       <c r="L13" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-max-ishod-iron-grey-and-photon-dust-1</t>
+          <t>https://www.footlocker.com/release-calendar/crocs/46212953.html</t>
         </is>
       </c>
       <c r="M13" s="10" t="inlineStr"/>
@@ -6601,7 +7310,7 @@
       </c>
       <c r="G29" s="10" t="inlineStr">
         <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+          <t>Nike LeBron 23 'LeBronto'</t>
         </is>
       </c>
       <c r="H29" s="10" t="inlineStr">
@@ -6611,12 +7320,12 @@
       </c>
       <c r="I29" s="9" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J29" s="9" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K29" s="9" t="n">
@@ -6624,7 +7333,7 @@
       </c>
       <c r="L29" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
+          <t>https://thedropdate.com/sneakers/nike-lebron-23-lebronto-ih1513-602/706595</t>
         </is>
       </c>
       <c r="M29" s="10" t="inlineStr"/>
@@ -6641,9 +7350,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="E30" s="8" t="inlineStr">
@@ -6658,10 +7367,14 @@
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="H30" s="10" t="inlineStr"/>
+          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+        </is>
+      </c>
+      <c r="H30" s="10" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
       <c r="I30" s="9" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -6673,11 +7386,11 @@
         </is>
       </c>
       <c r="K30" s="9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L30" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
         </is>
       </c>
       <c r="M30" s="10" t="inlineStr"/>
@@ -6694,9 +7407,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D31" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="D31" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E31" s="8" t="inlineStr">
@@ -6711,14 +7424,10 @@
       </c>
       <c r="G31" s="10" t="inlineStr">
         <is>
-          <t>Nike Sabrina 3 MENS • YELLOW STRIKE/APPLE GREEN/PALE YELLOW</t>
-        </is>
-      </c>
-      <c r="H31" s="10" t="inlineStr">
-        <is>
-          <t>basketball</t>
-        </is>
-      </c>
+          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="H31" s="10" t="inlineStr"/>
       <c r="I31" s="9" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -6730,11 +7439,11 @@
         </is>
       </c>
       <c r="K31" s="9" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L31" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/R2478700.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
         </is>
       </c>
       <c r="M31" s="10" t="inlineStr"/>
@@ -6768,18 +7477,22 @@
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>Nike SB Ishod Apparel Collection</t>
-        </is>
-      </c>
-      <c r="H32" s="10" t="inlineStr"/>
+          <t>Nike Sabrina 3 MENS • YELLOW STRIKE/APPLE GREEN/PALE YELLOW</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
       <c r="I32" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K32" s="9" t="n">
@@ -6787,7 +7500,7 @@
       </c>
       <c r="L32" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/nike-sb-ishod-apparel-collection-static</t>
+          <t>https://www.footlocker.com/release-calendar/nike/R2478700.html</t>
         </is>
       </c>
       <c r="M32" s="10" t="inlineStr"/>
@@ -8801,7 +9514,7 @@
       </c>
       <c r="G69" s="10" t="inlineStr">
         <is>
-          <t>Finesse x ASICS GEL-CUMULUS 16 'Desert Rose' From £ 165</t>
+          <t>ASICS Gel-kayano 14 'Olive' From £ 165</t>
         </is>
       </c>
       <c r="H69" s="10" t="inlineStr"/>
@@ -8820,7 +9533,7 @@
       </c>
       <c r="L69" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/asics-gel-cumulus-16-finesse-desert-rose-1203b003-200/668694</t>
+          <t>https://thedropdate.com/sneakers/asics-gel-kayano-14-white-1203a537-111/705592</t>
         </is>
       </c>
       <c r="M69" s="10" t="inlineStr"/>
@@ -8849,12 +9562,12 @@
       </c>
       <c r="F70" s="9" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="G70" s="10" t="inlineStr">
         <is>
-          <t>New Balance 993 Made in USA 'Passion Fruit' From £ 205</t>
+          <t>Finesse x ASICS GEL-CUMULUS 16 'Desert Rose' From £ 165</t>
         </is>
       </c>
       <c r="H70" s="10" t="inlineStr"/>
@@ -8873,7 +9586,7 @@
       </c>
       <c r="L70" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-993-made-in-usa-passion-fruit-u9934ja/705132</t>
+          <t>https://thedropdate.com/sneakers/asics-gel-cumulus-16-finesse-desert-rose-1203b003-200/668694</t>
         </is>
       </c>
       <c r="M70" s="10" t="inlineStr"/>
@@ -8902,12 +9615,12 @@
       </c>
       <c r="F71" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G71" s="10" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 ’07 'Cherry Blossom' From £ 120</t>
+          <t>CAYL x New Balance M10L 'Black Ink' From £ 140</t>
         </is>
       </c>
       <c r="H71" s="10" t="inlineStr"/>
@@ -8926,7 +9639,7 @@
       </c>
       <c r="L71" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nikes-air-force-1-07-spring-flowers-iq3472-298/669922</t>
+          <t>https://thedropdate.com/sneakers/new-balance-m10l-blue-mtm10lcl/671644</t>
         </is>
       </c>
       <c r="M71" s="10" t="inlineStr"/>
@@ -8938,9 +9651,9 @@
         <v>46093</v>
       </c>
       <c r="B72" s="5" t="inlineStr"/>
-      <c r="C72" s="11" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D72" s="7" t="inlineStr">
@@ -8955,19 +9668,15 @@
       </c>
       <c r="F72" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G72" s="10" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 'Paisley Bandana' From £ 180</t>
-        </is>
-      </c>
-      <c r="H72" s="10" t="inlineStr">
-        <is>
-          <t>hot-model, running</t>
-        </is>
-      </c>
+          <t>CAYL x New Balance UTRNCA 'Slate Grey' From £ 155</t>
+        </is>
+      </c>
+      <c r="H72" s="10" t="inlineStr"/>
       <c r="I72" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -8983,7 +9692,7 @@
       </c>
       <c r="L72" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-air-max-95-paisley-bandana-iq0620-100/705853</t>
+          <t>https://thedropdate.com/sneakers/cayl-x-new-balance-utrnv11-slate-grey-utrnca/705387</t>
         </is>
       </c>
       <c r="M72" s="10" t="inlineStr"/>
@@ -8992,12 +9701,12 @@
     </row>
     <row r="73">
       <c r="A73" s="4" t="n">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="B73" s="5" t="inlineStr"/>
-      <c r="C73" s="11" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D73" s="7" t="inlineStr">
@@ -9012,27 +9721,23 @@
       </c>
       <c r="F73" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G73" s="10" t="inlineStr">
         <is>
-          <t>Mar 13 Kobe 3 Low Protro Pink Quartz</t>
-        </is>
-      </c>
-      <c r="H73" s="10" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
+          <t>New Balance 993 Made in USA 'Passion Fruit' From £ 205</t>
+        </is>
+      </c>
+      <c r="H73" s="10" t="inlineStr"/>
       <c r="I73" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J73" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K73" s="9" t="n">
@@ -9040,7 +9745,7 @@
       </c>
       <c r="L73" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/kobe-3-low-protro-pink-quartz</t>
+          <t>https://thedropdate.com/sneakers/new-balance-993-made-in-usa-passion-fruit-u9934ja/705132</t>
         </is>
       </c>
       <c r="M73" s="10" t="inlineStr"/>
@@ -9049,7 +9754,7 @@
     </row>
     <row r="74">
       <c r="A74" s="4" t="n">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="B74" s="5" t="inlineStr"/>
       <c r="C74" s="6" t="inlineStr">
@@ -9074,7 +9779,7 @@
       </c>
       <c r="G74" s="10" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low 'Asparagus &amp; Chlorophyll' From £ 118</t>
+          <t>Nike Air Force 1 ’07 'Cherry Blossom' From £ 120</t>
         </is>
       </c>
       <c r="H74" s="10" t="inlineStr"/>
@@ -9093,7 +9798,7 @@
       </c>
       <c r="L74" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-air-force-1-low-io5011-300/704355</t>
+          <t>https://thedropdate.com/sneakers/nikes-air-force-1-07-spring-flowers-iq3472-298/669922</t>
         </is>
       </c>
       <c r="M74" s="10" t="inlineStr"/>
@@ -9102,12 +9807,12 @@
     </row>
     <row r="75">
       <c r="A75" s="4" t="n">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="B75" s="5" t="inlineStr"/>
-      <c r="C75" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C75" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D75" s="7" t="inlineStr">
@@ -9127,12 +9832,12 @@
       </c>
       <c r="G75" s="10" t="inlineStr">
         <is>
-          <t>Veneda Carter x Nike Air Max Muse 'White &amp; Racer Blue' From £ 145</t>
+          <t>Nike Air Max 95 'Paisley Bandana' From £ 180</t>
         </is>
       </c>
       <c r="H75" s="10" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>hot-model, running</t>
         </is>
       </c>
       <c r="I75" s="9" t="inlineStr">
@@ -9150,7 +9855,7 @@
       </c>
       <c r="L75" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/veneda-carter-x-nike-air-max-muse-white-racer-blue-hv9929-100/700942</t>
+          <t>https://thedropdate.com/sneakers/nike-air-max-95-paisley-bandana-iq0620-100/705853</t>
         </is>
       </c>
       <c r="M75" s="10" t="inlineStr"/>
@@ -9159,12 +9864,12 @@
     </row>
     <row r="76">
       <c r="A76" s="4" t="n">
-        <v>46095</v>
+        <v>46093</v>
       </c>
       <c r="B76" s="5" t="inlineStr"/>
-      <c r="C76" s="11" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D76" s="7" t="inlineStr">
@@ -9179,19 +9884,15 @@
       </c>
       <c r="F76" s="9" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G76" s="10" t="inlineStr">
         <is>
-          <t>Air Jordan 13 Retro 'True Red' - 2026 From £ 185</t>
-        </is>
-      </c>
-      <c r="H76" s="10" t="inlineStr">
-        <is>
-          <t>hot-model, retro</t>
-        </is>
-      </c>
+          <t>NikeSKIMS Rift Mesh 'Black' From £ 145</t>
+        </is>
+      </c>
+      <c r="H76" s="10" t="inlineStr"/>
       <c r="I76" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -9207,7 +9908,7 @@
       </c>
       <c r="L76" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/air-jordan-13-retro-true-red-2026-414571-102/705921</t>
+          <t>https://thedropdate.com/sneakers/skims-x-nike-air-rift-black-io7694-001/700295</t>
         </is>
       </c>
       <c r="M76" s="10" t="inlineStr"/>
@@ -9216,7 +9917,7 @@
     </row>
     <row r="77">
       <c r="A77" s="4" t="n">
-        <v>46095</v>
+        <v>46093</v>
       </c>
       <c r="B77" s="5" t="inlineStr"/>
       <c r="C77" s="6" t="inlineStr">
@@ -9236,19 +9937,15 @@
       </c>
       <c r="F77" s="9" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G77" s="10" t="inlineStr">
         <is>
-          <t>Air Jordan 9 Retro 'Flint Grey' - 2026 From £ 189</t>
-        </is>
-      </c>
-      <c r="H77" s="10" t="inlineStr">
-        <is>
-          <t>retro</t>
-        </is>
-      </c>
+          <t>NikeSKIMS Rift Mesh 'Light Bone' From £ 145</t>
+        </is>
+      </c>
+      <c r="H77" s="10" t="inlineStr"/>
       <c r="I77" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -9264,7 +9961,7 @@
       </c>
       <c r="L77" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/air-jordan-9-retro-flint-grey-and-french-blue-hv4794-100/701944</t>
+          <t>https://thedropdate.com/sneakers/nikeskims-rift-mesh-light-bone-io7694-002/706596</t>
         </is>
       </c>
       <c r="M77" s="10" t="inlineStr"/>
@@ -9273,55 +9970,51 @@
     </row>
     <row r="78">
       <c r="A78" s="4" t="n">
-        <v>46095</v>
+        <v>46093</v>
       </c>
       <c r="B78" s="5" t="inlineStr"/>
-      <c r="C78" s="11" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="D78" s="12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
-        </is>
-      </c>
-      <c r="E78" s="13" t="inlineStr">
-        <is>
-          <t>Watch</t>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D78" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F78" s="9" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G78" s="10" t="inlineStr">
         <is>
-          <t>Mar 14 Infant/Toddler Shoes Jordan 13 Retro</t>
-        </is>
-      </c>
-      <c r="H78" s="10" t="inlineStr">
-        <is>
-          <t>hot-model, retro</t>
-        </is>
-      </c>
+          <t>NikeSKIMS Rift Mesh 'Velvet Brown' From £ 145</t>
+        </is>
+      </c>
+      <c r="H78" s="10" t="inlineStr"/>
       <c r="I78" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J78" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K78" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L78" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
+          <t>https://thedropdate.com/sneakers/skims-x-nike-air-rift-velvet-brown-io7694-200/700297</t>
         </is>
       </c>
       <c r="M78" s="10" t="inlineStr"/>
@@ -9330,12 +10023,12 @@
     </row>
     <row r="79">
       <c r="A79" s="4" t="n">
-        <v>46095</v>
+        <v>46094</v>
       </c>
       <c r="B79" s="5" t="inlineStr"/>
-      <c r="C79" s="11" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D79" s="7" t="inlineStr">
@@ -9350,19 +10043,15 @@
       </c>
       <c r="F79" s="9" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="G79" s="10" t="inlineStr">
         <is>
-          <t>Travis Scott x Air Jordan Jumpman Jack 'Green Spark' From £ 185</t>
-        </is>
-      </c>
-      <c r="H79" s="10" t="inlineStr">
-        <is>
-          <t>collab</t>
-        </is>
-      </c>
+          <t>adidas Anthony Edwards 2 'Georgia Bulldogs' From £ 120</t>
+        </is>
+      </c>
+      <c r="H79" s="10" t="inlineStr"/>
       <c r="I79" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -9378,7 +10067,7 @@
       </c>
       <c r="L79" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/air-jordan-x-travis-scott-jumpman-jack-green-spark-im9113-300/704688</t>
+          <t>https://thedropdate.com/sneakers/adidas-anthony-edwards-2-georgia-bulldogs-jq9497/706523</t>
         </is>
       </c>
       <c r="M79" s="10" t="inlineStr"/>
@@ -9387,7 +10076,7 @@
     </row>
     <row r="80">
       <c r="A80" s="4" t="n">
-        <v>46099</v>
+        <v>46094</v>
       </c>
       <c r="B80" s="5" t="inlineStr"/>
       <c r="C80" s="11" t="inlineStr">
@@ -9407,17 +10096,17 @@
       </c>
       <c r="F80" s="9" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G80" s="10" t="inlineStr">
         <is>
-          <t>Mar 18 Air Jordan 1 Low OG Sail and Coconut Milk</t>
+          <t>Mar 13 Kobe 3 Low Protro Pink Quartz</t>
         </is>
       </c>
       <c r="H80" s="10" t="inlineStr">
         <is>
-          <t>hot-model</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="I80" s="9" t="inlineStr">
@@ -9435,7 +10124,7 @@
       </c>
       <c r="L80" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
+          <t>/launch/t/kobe-3-low-protro-pink-quartz</t>
         </is>
       </c>
       <c r="M80" s="10" t="inlineStr"/>
@@ -9444,7 +10133,7 @@
     </row>
     <row r="81">
       <c r="A81" s="4" t="n">
-        <v>46099</v>
+        <v>46094</v>
       </c>
       <c r="B81" s="5" t="inlineStr"/>
       <c r="C81" s="6" t="inlineStr">
@@ -9464,12 +10153,12 @@
       </c>
       <c r="F81" s="9" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G81" s="10" t="inlineStr">
         <is>
-          <t>One Piece x Crocs Classic Clog 'Zoro'</t>
+          <t>Nike Air Force 1 Low 'Asparagus &amp; Chlorophyll' From £ 118</t>
         </is>
       </c>
       <c r="H81" s="10" t="inlineStr"/>
@@ -9488,7 +10177,7 @@
       </c>
       <c r="L81" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-zoro-212953-90h/706159</t>
+          <t>https://thedropdate.com/sneakers/nike-air-force-1-low-io5011-300/704355</t>
         </is>
       </c>
       <c r="M81" s="10" t="inlineStr"/>
@@ -9497,7 +10186,7 @@
     </row>
     <row r="82">
       <c r="A82" s="4" t="n">
-        <v>46100</v>
+        <v>46094</v>
       </c>
       <c r="B82" s="5" t="inlineStr"/>
       <c r="C82" s="6" t="inlineStr">
@@ -9517,15 +10206,19 @@
       </c>
       <c r="F82" s="9" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G82" s="10" t="inlineStr">
         <is>
-          <t>New Balance 991v1 Made in UK 'Oyster Grey' From £ 220</t>
-        </is>
-      </c>
-      <c r="H82" s="10" t="inlineStr"/>
+          <t>Veneda Carter x Nike Air Max Muse 'White &amp; Racer Blue' From £ 145</t>
+        </is>
+      </c>
+      <c r="H82" s="10" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
       <c r="I82" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -9541,7 +10234,7 @@
       </c>
       <c r="L82" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-991v1-made-in-uk-oyster-grey-m991cr1/706155</t>
+          <t>https://thedropdate.com/sneakers/veneda-carter-x-nike-air-max-muse-white-racer-blue-hv9929-100/700942</t>
         </is>
       </c>
       <c r="M82" s="10" t="inlineStr"/>
@@ -9550,12 +10243,12 @@
     </row>
     <row r="83">
       <c r="A83" s="4" t="n">
-        <v>46101</v>
+        <v>46095</v>
       </c>
       <c r="B83" s="5" t="inlineStr"/>
-      <c r="C83" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C83" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D83" s="7" t="inlineStr">
@@ -9570,17 +10263,17 @@
       </c>
       <c r="F83" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G83" s="10" t="inlineStr">
         <is>
-          <t>Nike First Sight Noir WMNS 'Black' From £ 110</t>
+          <t>Air Jordan 13 Retro 'True Red' - 2026 From £ 185</t>
         </is>
       </c>
       <c r="H83" s="10" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="I83" s="9" t="inlineStr">
@@ -9598,7 +10291,7 @@
       </c>
       <c r="L83" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-first-sight-noir-wmns-black-hq2409-001/706328</t>
+          <t>https://thedropdate.com/sneakers/air-jordan-13-retro-true-red-2026-414571-102/705921</t>
         </is>
       </c>
       <c r="M83" s="10" t="inlineStr"/>
@@ -9607,7 +10300,7 @@
     </row>
     <row r="84">
       <c r="A84" s="4" t="n">
-        <v>46107</v>
+        <v>46095</v>
       </c>
       <c r="B84" s="5" t="inlineStr"/>
       <c r="C84" s="6" t="inlineStr">
@@ -9627,15 +10320,19 @@
       </c>
       <c r="F84" s="9" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G84" s="10" t="inlineStr">
         <is>
-          <t>One Piece x Crocs Classic Clog 'Thousand Sunny'</t>
-        </is>
-      </c>
-      <c r="H84" s="10" t="inlineStr"/>
+          <t>Air Jordan 9 Retro 'Flint Grey' - 2026 From £ 189</t>
+        </is>
+      </c>
+      <c r="H84" s="10" t="inlineStr">
+        <is>
+          <t>retro</t>
+        </is>
+      </c>
       <c r="I84" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -9651,7 +10348,7 @@
       </c>
       <c r="L84" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-thousand-sunny-212126-90h/706160</t>
+          <t>https://thedropdate.com/sneakers/air-jordan-9-retro-flint-grey-and-french-blue-hv4794-100/701944</t>
         </is>
       </c>
       <c r="M84" s="10" t="inlineStr"/>
@@ -9660,51 +10357,55 @@
     </row>
     <row r="85">
       <c r="A85" s="4" t="n">
-        <v>46107</v>
+        <v>46095</v>
       </c>
       <c r="B85" s="5" t="inlineStr"/>
-      <c r="C85" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
-        </is>
-      </c>
-      <c r="D85" s="7" t="inlineStr">
-        <is>
-          <t>MED</t>
-        </is>
-      </c>
-      <c r="E85" s="8" t="inlineStr">
-        <is>
-          <t>Low Priority</t>
+      <c r="C85" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D85" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E85" s="13" t="inlineStr">
+        <is>
+          <t>Watch</t>
         </is>
       </c>
       <c r="F85" s="9" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G85" s="10" t="inlineStr">
         <is>
-          <t>New Balance 1890 'Star Burst' From £ 160</t>
-        </is>
-      </c>
-      <c r="H85" s="10" t="inlineStr"/>
+          <t>Mar 14 Infant/Toddler Shoes Jordan 13 Retro</t>
+        </is>
+      </c>
+      <c r="H85" s="10" t="inlineStr">
+        <is>
+          <t>hot-model, retro</t>
+        </is>
+      </c>
       <c r="I85" s="9" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="J85" s="9" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="K85" s="9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L85" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-1890-black-yellow-u18903rb/705946</t>
+          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
       <c r="M85" s="10" t="inlineStr"/>
@@ -9713,12 +10414,12 @@
     </row>
     <row r="86">
       <c r="A86" s="4" t="n">
-        <v>46108</v>
+        <v>46095</v>
       </c>
       <c r="B86" s="5" t="inlineStr"/>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C86" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D86" s="7" t="inlineStr">
@@ -9733,23 +10434,27 @@
       </c>
       <c r="F86" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G86" s="10" t="inlineStr">
         <is>
-          <t>Mar 27 Baby/Toddler Shoes Nike Little Posite Pro</t>
-        </is>
-      </c>
-      <c r="H86" s="10" t="inlineStr"/>
+          <t>Travis Scott x Air Jordan Jumpman Jack 'Green Spark' From £ 185</t>
+        </is>
+      </c>
+      <c r="H86" s="10" t="inlineStr">
+        <is>
+          <t>collab</t>
+        </is>
+      </c>
       <c r="I86" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J86" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K86" s="9" t="n">
@@ -9757,7 +10462,7 @@
       </c>
       <c r="L86" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/air-foamposite-pro-university-blue-and-white</t>
+          <t>https://thedropdate.com/sneakers/air-jordan-x-travis-scott-jumpman-jack-green-spark-im9113-300/704688</t>
         </is>
       </c>
       <c r="M86" s="10" t="inlineStr"/>
@@ -9766,12 +10471,12 @@
     </row>
     <row r="87">
       <c r="A87" s="4" t="n">
-        <v>46109</v>
+        <v>46097</v>
       </c>
       <c r="B87" s="5" t="inlineStr"/>
-      <c r="C87" s="11" t="inlineStr">
-        <is>
-          <t>MED</t>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D87" s="7" t="inlineStr">
@@ -9786,19 +10491,15 @@
       </c>
       <c r="F87" s="9" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G87" s="10" t="inlineStr">
         <is>
-          <t>Air Jordan 3 'Spring Is In The Air' From £ 190</t>
-        </is>
-      </c>
-      <c r="H87" s="10" t="inlineStr">
-        <is>
-          <t>hot-model</t>
-        </is>
-      </c>
+          <t>Jacquemus x Nike Moon Shoe SP 'Fauna Brown' From £ 163</t>
+        </is>
+      </c>
+      <c r="H87" s="10" t="inlineStr"/>
       <c r="I87" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -9814,7 +10515,7 @@
       </c>
       <c r="L87" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/air-jordan-3-spring-is-in-the-air-if4396-100/703366</t>
+          <t>https://thedropdate.com/sneakers/jacquemus-x-nike-moon-shoe-sp-fauna-brown-hv8547-200/705860</t>
         </is>
       </c>
       <c r="M87" s="10" t="inlineStr"/>
@@ -9823,12 +10524,12 @@
     </row>
     <row r="88">
       <c r="A88" s="4" t="n">
-        <v>46113</v>
+        <v>46097</v>
       </c>
       <c r="B88" s="5" t="inlineStr"/>
-      <c r="C88" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C88" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D88" s="7" t="inlineStr">
@@ -9848,18 +10549,22 @@
       </c>
       <c r="G88" s="10" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="H88" s="10" t="inlineStr"/>
+          <t>Jacquemus x Nike Moon Shoe SP 'Soft Pearl' From £ 163</t>
+        </is>
+      </c>
+      <c r="H88" s="10" t="inlineStr">
+        <is>
+          <t>exclusive</t>
+        </is>
+      </c>
       <c r="I88" s="9" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J88" s="9" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K88" s="9" t="n">
@@ -9867,7 +10572,7 @@
       </c>
       <c r="L88" s="10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://thedropdate.com/sneakers/jacquemus-x-nike-moon-shoe-sp-soft-pearl-hv8547-002/705859</t>
         </is>
       </c>
       <c r="M88" s="10" t="inlineStr"/>
@@ -9876,7 +10581,7 @@
     </row>
     <row r="89">
       <c r="A89" s="4" t="n">
-        <v>46113</v>
+        <v>46098</v>
       </c>
       <c r="B89" s="5" t="inlineStr"/>
       <c r="C89" s="6" t="inlineStr">
@@ -9884,9 +10589,9 @@
           <t>LOW</t>
         </is>
       </c>
-      <c r="D89" s="12" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+      <c r="D89" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="E89" s="8" t="inlineStr">
@@ -9896,15 +10601,19 @@
       </c>
       <c r="F89" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="G89" s="10" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Pregame Mule 'Light Smoke Grey' From £ 80</t>
-        </is>
-      </c>
-      <c r="H89" s="10" t="inlineStr"/>
+          <t>adidas Hyperboost Edge 'White &amp; Pure Ruby' From £ 170</t>
+        </is>
+      </c>
+      <c r="H89" s="10" t="inlineStr">
+        <is>
+          <t>exclusive</t>
+        </is>
+      </c>
       <c r="I89" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -9916,11 +10625,11 @@
         </is>
       </c>
       <c r="K89" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L89" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mule-light-smoke-grey-hq4307-003/647220</t>
+          <t>https://thedropdate.com/sneakers/adidas-hyperboost-edge-white-pure-ruby-ki1913/706498</t>
         </is>
       </c>
       <c r="M89" s="10" t="inlineStr"/>
@@ -9929,12 +10638,12 @@
     </row>
     <row r="90">
       <c r="A90" s="4" t="n">
-        <v>46113</v>
+        <v>46098</v>
       </c>
       <c r="B90" s="5" t="inlineStr"/>
-      <c r="C90" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C90" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D90" s="7" t="inlineStr">
@@ -9949,15 +10658,19 @@
       </c>
       <c r="F90" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G90" s="10" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Slide 'Black' From £ 80</t>
-        </is>
-      </c>
-      <c r="H90" s="10" t="inlineStr"/>
+          <t>Dashawn Jordan x Nike SB Dunk Low 'Bright Spruce' From £ 120</t>
+        </is>
+      </c>
+      <c r="H90" s="10" t="inlineStr">
+        <is>
+          <t>hot-model</t>
+        </is>
+      </c>
       <c r="I90" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -9973,7 +10686,7 @@
       </c>
       <c r="L90" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-mind-001-slide-black-hq4307-001/672235</t>
+          <t>https://thedropdate.com/sneakers/nike-sb-x-dashawn-jordan-dunk-low-black-bright-spruce-ib6208-200/703258</t>
         </is>
       </c>
       <c r="M90" s="10" t="inlineStr"/>
@@ -9982,7 +10695,7 @@
     </row>
     <row r="91">
       <c r="A91" s="4" t="n">
-        <v>46113</v>
+        <v>46099</v>
       </c>
       <c r="B91" s="5" t="inlineStr"/>
       <c r="C91" s="6" t="inlineStr">
@@ -10002,19 +10715,15 @@
       </c>
       <c r="F91" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="G91" s="10" t="inlineStr">
         <is>
-          <t>Nike Mind 001 WMNS Pregame Mules 'Black' From £ 80</t>
-        </is>
-      </c>
-      <c r="H91" s="10" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>adidas Adizero Dropset Elite 'Solar Red' From £ 230</t>
+        </is>
+      </c>
+      <c r="H91" s="10" t="inlineStr"/>
       <c r="I91" s="9" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -10030,7 +10739,7 @@
       </c>
       <c r="L91" s="10" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mules-hq4309-001/678052</t>
+          <t>https://thedropdate.com/sneakers/adidas-adizero-dropset-elite-solar-red-la6218/706499</t>
         </is>
       </c>
       <c r="M91" s="10" t="inlineStr"/>
@@ -10039,12 +10748,12 @@
     </row>
     <row r="92">
       <c r="A92" s="4" t="n">
-        <v>46115</v>
+        <v>46099</v>
       </c>
       <c r="B92" s="5" t="inlineStr"/>
-      <c r="C92" s="6" t="inlineStr">
-        <is>
-          <t>LOW</t>
+      <c r="C92" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
         </is>
       </c>
       <c r="D92" s="7" t="inlineStr">
@@ -10059,27 +10768,27 @@
       </c>
       <c r="F92" s="9" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G92" s="10" t="inlineStr">
         <is>
-          <t>Apr 3 Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
+          <t>Air Jordan 3 'Spring Is In The Air' From £ 189</t>
         </is>
       </c>
       <c r="H92" s="10" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>hot-model</t>
         </is>
       </c>
       <c r="I92" s="9" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J92" s="9" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K92" s="9" t="n">
@@ -10087,12 +10796,554 @@
       </c>
       <c r="L92" s="10" t="inlineStr">
         <is>
-          <t>/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
+          <t>https://thedropdate.com/sneakers/air-jordan-3-spring-is-in-the-air-if4396-100/703366</t>
         </is>
       </c>
       <c r="M92" s="10" t="inlineStr"/>
       <c r="N92" s="10" t="inlineStr"/>
       <c r="O92" s="5" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B93" s="5" t="inlineStr"/>
+      <c r="C93" s="11" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D93" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E93" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F93" s="9" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="G93" s="10" t="inlineStr">
+        <is>
+          <t>Mar 18 Air Jordan 1 Low OG Sail and Coconut Milk</t>
+        </is>
+      </c>
+      <c r="H93" s="10" t="inlineStr">
+        <is>
+          <t>hot-model</t>
+        </is>
+      </c>
+      <c r="I93" s="9" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="J93" s="9" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="K93" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L93" s="10" t="inlineStr">
+        <is>
+          <t>/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
+        </is>
+      </c>
+      <c r="M93" s="10" t="inlineStr"/>
+      <c r="N93" s="10" t="inlineStr"/>
+      <c r="O93" s="5" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B94" s="5" t="inlineStr"/>
+      <c r="C94" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D94" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E94" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F94" s="9" t="inlineStr">
+        <is>
+          <t>Crocs</t>
+        </is>
+      </c>
+      <c r="G94" s="10" t="inlineStr">
+        <is>
+          <t>One Piece x Crocs Classic Clog 'Zoro'</t>
+        </is>
+      </c>
+      <c r="H94" s="10" t="inlineStr"/>
+      <c r="I94" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J94" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K94" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L94" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-zoro-212953-90h/706159</t>
+        </is>
+      </c>
+      <c r="M94" s="10" t="inlineStr"/>
+      <c r="N94" s="10" t="inlineStr"/>
+      <c r="O94" s="5" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B95" s="5" t="inlineStr"/>
+      <c r="C95" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D95" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E95" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F95" s="9" t="inlineStr">
+        <is>
+          <t>New Balance</t>
+        </is>
+      </c>
+      <c r="G95" s="10" t="inlineStr">
+        <is>
+          <t>New Balance 991v1 Made in UK 'Oyster Grey' From £ 220</t>
+        </is>
+      </c>
+      <c r="H95" s="10" t="inlineStr"/>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J95" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K95" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L95" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/new-balance-991v1-made-in-uk-oyster-grey-m991cr1/706155</t>
+        </is>
+      </c>
+      <c r="M95" s="10" t="inlineStr"/>
+      <c r="N95" s="10" t="inlineStr"/>
+      <c r="O95" s="5" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B96" s="5" t="inlineStr"/>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D96" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E96" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F96" s="9" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G96" s="10" t="inlineStr">
+        <is>
+          <t>Nike First Sight Noir WMNS 'Black' From £ 110</t>
+        </is>
+      </c>
+      <c r="H96" s="10" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I96" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J96" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K96" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L96" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/nike-first-sight-noir-wmns-black-hq2409-001/706328</t>
+        </is>
+      </c>
+      <c r="M96" s="10" t="inlineStr"/>
+      <c r="N96" s="10" t="inlineStr"/>
+      <c r="O96" s="5" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B97" s="5" t="inlineStr"/>
+      <c r="C97" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D97" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E97" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F97" s="9" t="inlineStr">
+        <is>
+          <t>Crocs</t>
+        </is>
+      </c>
+      <c r="G97" s="10" t="inlineStr">
+        <is>
+          <t>One Piece x Crocs Classic Clog 'Thousand Sunny'</t>
+        </is>
+      </c>
+      <c r="H97" s="10" t="inlineStr"/>
+      <c r="I97" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J97" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K97" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L97" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-thousand-sunny-212126-90h/706160</t>
+        </is>
+      </c>
+      <c r="M97" s="10" t="inlineStr"/>
+      <c r="N97" s="10" t="inlineStr"/>
+      <c r="O97" s="5" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B98" s="5" t="inlineStr"/>
+      <c r="C98" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D98" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E98" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F98" s="9" t="inlineStr">
+        <is>
+          <t>New Balance</t>
+        </is>
+      </c>
+      <c r="G98" s="10" t="inlineStr">
+        <is>
+          <t>New Balance 1890 'Star Burst' From £ 160</t>
+        </is>
+      </c>
+      <c r="H98" s="10" t="inlineStr"/>
+      <c r="I98" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J98" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K98" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L98" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/new-balance-1890-black-yellow-u18903rb/705946</t>
+        </is>
+      </c>
+      <c r="M98" s="10" t="inlineStr"/>
+      <c r="N98" s="10" t="inlineStr"/>
+      <c r="O98" s="5" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B99" s="5" t="inlineStr"/>
+      <c r="C99" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D99" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E99" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F99" s="9" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G99" s="10" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="H99" s="10" t="inlineStr"/>
+      <c r="I99" s="9" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="J99" s="9" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="K99" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L99" s="10" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+        </is>
+      </c>
+      <c r="M99" s="10" t="inlineStr"/>
+      <c r="N99" s="10" t="inlineStr"/>
+      <c r="O99" s="5" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B100" s="5" t="inlineStr"/>
+      <c r="C100" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D100" s="12" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E100" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F100" s="9" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G100" s="10" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Pregame Mule 'Light Smoke Grey' From £ 80</t>
+        </is>
+      </c>
+      <c r="H100" s="10" t="inlineStr"/>
+      <c r="I100" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J100" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K100" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="L100" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mule-light-smoke-grey-hq4307-003/647220</t>
+        </is>
+      </c>
+      <c r="M100" s="10" t="inlineStr"/>
+      <c r="N100" s="10" t="inlineStr"/>
+      <c r="O100" s="5" t="inlineStr"/>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B101" s="5" t="inlineStr"/>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D101" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E101" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F101" s="9" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G101" s="10" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Slide 'Black' From £ 80</t>
+        </is>
+      </c>
+      <c r="H101" s="10" t="inlineStr"/>
+      <c r="I101" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J101" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K101" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L101" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/nike-mind-001-slide-black-hq4307-001/672235</t>
+        </is>
+      </c>
+      <c r="M101" s="10" t="inlineStr"/>
+      <c r="N101" s="10" t="inlineStr"/>
+      <c r="O101" s="5" t="inlineStr"/>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B102" s="5" t="inlineStr"/>
+      <c r="C102" s="6" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D102" s="7" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E102" s="8" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F102" s="9" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G102" s="10" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 WMNS Pregame Mules 'Black' From £ 80</t>
+        </is>
+      </c>
+      <c r="H102" s="10" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I102" s="9" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J102" s="9" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K102" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="L102" s="10" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mules-hq4309-001/678052</t>
+        </is>
+      </c>
+      <c r="M102" s="10" t="inlineStr"/>
+      <c r="N102" s="10" t="inlineStr"/>
+      <c r="O102" s="5" t="inlineStr"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -10109,13 +11360,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H74"/>
+  <dimension ref="A1:H21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="12" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="70" customWidth="1" min="4" max="4"/>
+    <col width="13" customWidth="1" min="3" max="3"/>
+    <col width="62" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
     <col width="11" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
@@ -10167,22 +11418,22 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Magliano x VEJA Panenka 'Black' From £ 182</t>
+          <t>Jordan Retro 13 BOYS TODDLER • WHITE/BLACK/TRUE RED</t>
         </is>
       </c>
       <c r="E2" t="inlineStr"/>
@@ -10190,29 +11441,29 @@
       <c r="G2" t="inlineStr"/>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Magliano x VEJA Panenka 'Nacre'</t>
+          <t>Nike LeBron 23 'LeBronto'</t>
         </is>
       </c>
       <c r="E3" t="inlineStr"/>
@@ -10220,7 +11471,7 @@
       <c r="G3" t="inlineStr"/>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
@@ -10232,17 +11483,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-08</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Magliano x VEJA Panenka 'White' From £ 182</t>
+          <t>Air Max Ishod Iron Grey and Photon Dust</t>
         </is>
       </c>
       <c r="E4" t="inlineStr"/>
@@ -10250,7 +11501,7 @@
       <c r="G4" t="inlineStr"/>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
@@ -10262,17 +11513,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
+          <t>Nike SB Ishod Apparel Collection</t>
         </is>
       </c>
       <c r="E5" t="inlineStr"/>
@@ -10280,29 +11531,29 @@
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
+          <t>ASICS Gel-kayano 14 'Olive' From £ 165</t>
         </is>
       </c>
       <c r="E6" t="inlineStr"/>
@@ -10310,29 +11561,29 @@
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Air Jordan 4 Imperial Purple</t>
+          <t>CAYL x New Balance M10L 'Black Ink' From £ 140</t>
         </is>
       </c>
       <c r="E7" t="inlineStr"/>
@@ -10340,29 +11591,29 @@
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Air Max Ishod Iron Grey and Photon Dust</t>
+          <t>CAYL x New Balance UTRNCA 'Slate Grey' From £ 155</t>
         </is>
       </c>
       <c r="E8" t="inlineStr"/>
@@ -10370,19 +11621,19 @@
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -10392,7 +11643,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Jacquemus x Nike Moon Soft Pearl / Sail</t>
+          <t>NikeSKIMS Rift Mesh 'Black' From £ 145</t>
         </is>
       </c>
       <c r="E9" t="inlineStr"/>
@@ -10400,19 +11651,19 @@
       <c r="G9" t="inlineStr"/>
       <c r="H9" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -10422,7 +11673,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Nike SB Ishod Apparel Collection</t>
+          <t>NikeSKIMS Rift Mesh 'Light Bone' From £ 145</t>
         </is>
       </c>
       <c r="E10" t="inlineStr"/>
@@ -10430,19 +11681,19 @@
       <c r="G10" t="inlineStr"/>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>REMOVED</t>
+          <t>NEW</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-03-09</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -10452,7 +11703,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Zoom Vomero 5 Hyper Royal</t>
+          <t>NikeSKIMS Rift Mesh 'Velvet Brown' From £ 145</t>
         </is>
       </c>
       <c r="E11" t="inlineStr"/>
@@ -10460,7 +11711,7 @@
       <c r="G11" t="inlineStr"/>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
@@ -10472,7 +11723,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -10482,7 +11733,7 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>adidas Anthony Edwards 2 MENS • SILVER METALLIC/PURE RUBY/CORE BLACK</t>
+          <t>adidas Anthony Edwards 2 'Georgia Bulldogs' From £ 120</t>
         </is>
       </c>
       <c r="E12" t="inlineStr"/>
@@ -10490,7 +11741,7 @@
       <c r="G12" t="inlineStr"/>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
@@ -10502,17 +11753,17 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
+          <t>Jacquemus x Nike Moon Shoe SP 'Fauna Brown' From £ 163</t>
         </is>
       </c>
       <c r="E13" t="inlineStr"/>
@@ -10520,7 +11771,7 @@
       <c r="G13" t="inlineStr"/>
       <c r="H13" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
@@ -10532,17 +11783,17 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Air Jordan 1 Low OG Sail and Coconut Milk</t>
+          <t>Jacquemus x Nike Moon Shoe SP 'Soft Pearl' From £ 163</t>
         </is>
       </c>
       <c r="E14" t="inlineStr"/>
@@ -10550,7 +11801,7 @@
       <c r="G14" t="inlineStr"/>
       <c r="H14" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
@@ -10562,17 +11813,17 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Air Jordan 13 Retro White and University Red</t>
+          <t>adidas Hyperboost Edge 'White &amp; Pure Ruby' From £ 170</t>
         </is>
       </c>
       <c r="E15" t="inlineStr"/>
@@ -10580,7 +11831,7 @@
       <c r="G15" t="inlineStr"/>
       <c r="H15" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
@@ -10592,7 +11843,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-17</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -10602,7 +11853,7 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Air Jordan 4 Imperial Purple</t>
+          <t>Dashawn Jordan x Nike SB Dunk Low 'Bright Spruce' From £ 120</t>
         </is>
       </c>
       <c r="E16" t="inlineStr"/>
@@ -10610,7 +11861,7 @@
       <c r="G16" t="inlineStr"/>
       <c r="H16" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
@@ -10622,17 +11873,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Air Max Ishod Iron Grey and Photon Dust</t>
+          <t>adidas Adizero Dropset Elite 'Solar Red' From £ 230</t>
         </is>
       </c>
       <c r="E17" t="inlineStr"/>
@@ -10640,7 +11891,7 @@
       <c r="G17" t="inlineStr"/>
       <c r="H17" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
@@ -10652,17 +11903,17 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-18</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Unknown</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Balenciaga Monday Ultra WMNS Brown / White</t>
+          <t>Air Jordan 3 'Spring Is In The Air' From £ 189</t>
         </is>
       </c>
       <c r="E18" t="inlineStr"/>
@@ -10670,29 +11921,29 @@
       <c r="G18" t="inlineStr"/>
       <c r="H18" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-27</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Converse Grade School SHAI 001 Blush BOYS GRADE SCHOOL • OX TICKEKLED PINK/GERANIUM PINK</t>
+          <t>Mar 27 Baby/Toddler Shoes Nike Little Posite Pro</t>
         </is>
       </c>
       <c r="E19" t="inlineStr"/>
@@ -10700,29 +11951,29 @@
       <c r="G19" t="inlineStr"/>
       <c r="H19" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-03-28</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
+          <t>Air Jordan 3 'Spring Is In The Air' From £ 190</t>
         </is>
       </c>
       <c r="E20" t="inlineStr"/>
@@ -10730,29 +11981,29 @@
       <c r="G20" t="inlineStr"/>
       <c r="H20" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>REMOVED</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-04-03</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Jordan Grade School Retro 13 True Red BOYS GRADE SCHOOL • WHITE/BLACK/TRUE RED</t>
+          <t>Apr 3 Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
         </is>
       </c>
       <c r="E21" t="inlineStr"/>
@@ -10760,1597 +12011,7 @@
       <c r="G21" t="inlineStr"/>
       <c r="H21" t="inlineStr">
         <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Nike Air Max Uptempo '95 MENS • UNIVERSITY RED/WHITE/BLACK</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr"/>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr"/>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Kobe 3 Low Protro Pink Quartz</t>
-        </is>
-      </c>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr"/>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Mar 10 Zoom Vomero 5 Hyper Royal</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr"/>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Nike Air Force 1 '07 MENS • YELLOW PULSE/PINK FOAM/MULTI</t>
-        </is>
-      </c>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr"/>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
-        </is>
-      </c>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr"/>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
-        </is>
-      </c>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr"/>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr"/>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Nike Dunk Low MENS • EMERALD RISE/YELLOW PULSE/HYDRANGEAS</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr"/>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Nike G.T. Cut 4 MENS • PINKSICLE/MULTICOLOR/VIVID PINK</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr"/>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
-        </is>
-      </c>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr"/>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Nike Grade School Air Force 1 '07 BOYS GRADE SCHOOL • YELLOW PULSE/PINK FOAM/EMERALD RISE</t>
-        </is>
-      </c>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr"/>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Nike Grade School LeBron XXIII BOYS GRADE SCHOOL • SILT RED/METALLIC COPPER/BLACK</t>
-        </is>
-      </c>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr"/>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
-        </is>
-      </c>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr"/>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr"/>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr"/>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr"/>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Nike Sabrina 3 MENS • YELLOW STRIKE/APPLE GREEN/PALE YELLOW</t>
-        </is>
-      </c>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr"/>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Nike SB Ishod Apparel Collection</t>
-        </is>
-      </c>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr"/>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D42" t="inlineStr">
-        <is>
-          <t>PUMA All-Pro NITRO MENS • SAND DUNE/PURE PINK/GREEN FRUIT</t>
-        </is>
-      </c>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr"/>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr">
-        <is>
-          <t>PUMA Grade School Hali 1 BOYS GRADE SCHOOL • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr"/>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>PUMA Pre-School Hali 1 BOYS PRE-SCHOOL • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr"/>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr">
-        <is>
-          <t>Reebok</t>
-        </is>
-      </c>
-      <c r="D45" t="inlineStr">
-        <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • GREEN/PURPLE</t>
-        </is>
-      </c>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr"/>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D46" t="inlineStr">
-        <is>
-          <t>Skip To Main</t>
-        </is>
-      </c>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr"/>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Vans Pearlized LX Old Skool 36 MENS • BLACK/NAVY</t>
-        </is>
-      </c>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr"/>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>Vans Pearlized LX Old Skool 36 WOMENS • BLACK/NAVY</t>
-        </is>
-      </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Adidas</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>adidas Harden Volume 10 MENS • CORE BLACK/LUCID LEMON</t>
-        </is>
-      </c>
-      <c r="E49" t="inlineStr"/>
-      <c r="F49" t="inlineStr"/>
-      <c r="G49" t="inlineStr"/>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Converse</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Converse SHAI 001 Blush MENS • TICKLED PINK/GERANIUM PINK</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr"/>
-      <c r="F50" t="inlineStr"/>
-      <c r="G50" t="inlineStr"/>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Crocs</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr"/>
-      <c r="F51" t="inlineStr"/>
-      <c r="G51" t="inlineStr"/>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D52" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Jordan Grade School Retro 13 True Red BOYS GRADE SCHOOL • WHITE/BLACK/TRUE RED</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr"/>
-      <c r="F52" t="inlineStr"/>
-      <c r="G52" t="inlineStr"/>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>ENTRIES OPEN App entry Nike Air Max Uptempo '95 MENS • UNIVERSITY RED/WHITE/BLACK</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr"/>
-      <c r="F53" t="inlineStr"/>
-      <c r="G53" t="inlineStr"/>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C54" t="inlineStr">
-        <is>
-          <t>Air Jordan</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr"/>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C55" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Nike Air Foamposite Pro MENS • UNIVERSITY BLUE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="E55" t="inlineStr"/>
-      <c r="F55" t="inlineStr"/>
-      <c r="G55" t="inlineStr"/>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C56" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Nike Air Force 1 '07 MENS • YELLOW PULSE/PINK FOAM/MULTI</t>
-        </is>
-      </c>
-      <c r="E56" t="inlineStr"/>
-      <c r="F56" t="inlineStr"/>
-      <c r="G56" t="inlineStr"/>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C57" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Nike Air Max 95 WOMENS • BLACK/PINK/WHITE</t>
-        </is>
-      </c>
-      <c r="E57" t="inlineStr"/>
-      <c r="F57" t="inlineStr"/>
-      <c r="G57" t="inlineStr"/>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C58" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom G.T. Cut 1 MENS • BRIGHT VIOLET/MULTI/PINK FOAM</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr"/>
-      <c r="F58" t="inlineStr"/>
-      <c r="G58" t="inlineStr"/>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C59" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>Nike Air Zoom Hyperflight MENS • BLACK/BLACK/WHITE</t>
-        </is>
-      </c>
-      <c r="E59" t="inlineStr"/>
-      <c r="F59" t="inlineStr"/>
-      <c r="G59" t="inlineStr"/>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C60" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Nike Dunk Low MENS • EMERALD RISE/YELLOW PULSE/HYDRANGEAS</t>
-        </is>
-      </c>
-      <c r="E60" t="inlineStr"/>
-      <c r="F60" t="inlineStr"/>
-      <c r="G60" t="inlineStr"/>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Nike G.T. Future MENS • PSYCHIC PURPLE/BLACK</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr"/>
-      <c r="F61" t="inlineStr"/>
-      <c r="G61" t="inlineStr"/>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C62" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Nike Grade School Air Force 1 '07 BOYS GRADE SCHOOL • YELLOW PULSE/PINK FOAM/EMERALD RISE</t>
-        </is>
-      </c>
-      <c r="E62" t="inlineStr"/>
-      <c r="F62" t="inlineStr"/>
-      <c r="G62" t="inlineStr"/>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C63" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D63" t="inlineStr">
-        <is>
-          <t>Nike Ja 3 BOYS GRADE SCHOOL • BLACK/BALTIC BLUE</t>
-        </is>
-      </c>
-      <c r="E63" t="inlineStr"/>
-      <c r="F63" t="inlineStr"/>
-      <c r="G63" t="inlineStr"/>
-      <c r="H63" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C64" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Nike KD VI MENS • LASER ORANGE/RASPBERRY RED/BLACK</t>
-        </is>
-      </c>
-      <c r="E64" t="inlineStr"/>
-      <c r="F64" t="inlineStr"/>
-      <c r="G64" t="inlineStr"/>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
-        </is>
-      </c>
-      <c r="E65" t="inlineStr"/>
-      <c r="F65" t="inlineStr"/>
-      <c r="G65" t="inlineStr"/>
-      <c r="H65" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr"/>
-      <c r="F66" t="inlineStr"/>
-      <c r="G66" t="inlineStr"/>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>Nike Sabrina 3 MENS • YELLOW STRIKE/APPLE GREEN/PALE YELLOW</t>
-        </is>
-      </c>
-      <c r="E67" t="inlineStr"/>
-      <c r="F67" t="inlineStr"/>
-      <c r="G67" t="inlineStr"/>
-      <c r="H67" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>PUMA All-Pro NITRO MENS • SAND DUNE/PURE PINK/GREEN FRUIT</t>
-        </is>
-      </c>
-      <c r="E68" t="inlineStr"/>
-      <c r="F68" t="inlineStr"/>
-      <c r="G68" t="inlineStr"/>
-      <c r="H68" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>Puma</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>PUMA Hali 1 MENS • MUSTARD SEED/SEA KELP</t>
-        </is>
-      </c>
-      <c r="E69" t="inlineStr"/>
-      <c r="F69" t="inlineStr"/>
-      <c r="G69" t="inlineStr"/>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>Reebok</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>Reebok Angel Reese 1 GIRLS GRADE SCHOOL • BLUE/GREEN</t>
-        </is>
-      </c>
-      <c r="E70" t="inlineStr"/>
-      <c r="F70" t="inlineStr"/>
-      <c r="G70" t="inlineStr"/>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C71" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr">
-        <is>
-          <t>Skip To Main</t>
-        </is>
-      </c>
-      <c r="E71" t="inlineStr"/>
-      <c r="F71" t="inlineStr"/>
-      <c r="G71" t="inlineStr"/>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>REMOVED</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr">
-        <is>
-          <t>Vans Pearlized LX Old Skool 36 WOMENS • BLACK/NAVY</t>
-        </is>
-      </c>
-      <c r="E72" t="inlineStr"/>
-      <c r="F72" t="inlineStr"/>
-      <c r="G72" t="inlineStr"/>
-      <c r="H72" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="C73" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Mar 13 Kobe 3 Low Protro Pink Quartz</t>
-        </is>
-      </c>
-      <c r="E73" t="inlineStr"/>
-      <c r="F73" t="inlineStr"/>
-      <c r="G73" t="inlineStr"/>
-      <c r="H73" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>NEW</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>2026-04-01</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Nike</t>
-        </is>
-      </c>
-      <c r="D74" t="inlineStr">
-        <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="E74" t="inlineStr"/>
-      <c r="F74" t="inlineStr"/>
-      <c r="G74" t="inlineStr"/>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>2026-03-09T07:36:50Z</t>
+          <t>2026-03-09T18:07:00Z</t>
         </is>
       </c>
     </row>
@@ -12365,7 +12026,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q90"/>
+  <dimension ref="A1:Q100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -12870,7 +12531,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -12885,7 +12546,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
+          <t>Jordan Retro 13 BOYS TODDLER • WHITE/BLACK/TRUE RED</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -12904,11 +12565,11 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/D3004102.html</t>
         </is>
       </c>
       <c r="M8" t="inlineStr"/>
@@ -12917,7 +12578,7 @@
         <v>12</v>
       </c>
       <c r="P8" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="Q8" t="inlineStr"/>
     </row>
@@ -12945,17 +12606,17 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Converse</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Converse Grade School SHAI 001 Blush BOYS GRADE SCHOOL • OX TICKEKLED PINK/GERANIUM PINK</t>
+          <t>Jordan Retro 14 BOYS GRADE SCHOOL • BLACK/WHITE/UNIVERSITY BLUE</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>exclusive</t>
+          <t>retro</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -12969,17 +12630,17 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/converse/A19838C.html</t>
+          <t>https://www.footlocker.com/release-calendar/jordan/87524007.html</t>
         </is>
       </c>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr"/>
       <c r="O9" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="P9" t="n">
         <v>70</v>
@@ -13000,7 +12661,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -13010,12 +12671,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Converse</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
+          <t>ENTRIES OPEN App entry Converse Grade School SHAI 001 Blush BOYS GRADE SCHOOL • OX TICKEKLED PINK/GERANIUM PINK</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -13034,11 +12695,11 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/crocs/46212953.html</t>
+          <t>https://www.footlocker.com/release-calendar/converse/A19838C.html</t>
         </is>
       </c>
       <c r="M10" t="inlineStr"/>
@@ -13047,7 +12708,7 @@
         <v>14</v>
       </c>
       <c r="P10" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="Q10" t="inlineStr"/>
     </row>
@@ -13075,27 +12736,27 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Air Max Ishod Iron Grey and Photon Dust</t>
+          <t>ENTRIES OPEN App entry Crocs Classic Clog Zoro One Piece MENS • GREEN/BLACK</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>exclusive</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -13103,13 +12764,13 @@
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>/launch/t/air-max-ishod-iron-grey-and-photon-dust-1</t>
+          <t>https://www.footlocker.com/release-calendar/crocs/46212953.html</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P11" t="n">
         <v>50</v>
@@ -14092,7 +13753,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+          <t>Nike LeBron 23 'LeBronto'</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -14102,12 +13763,12 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -14115,7 +13776,7 @@
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
+          <t>https://thedropdate.com/sneakers/nike-lebron-23-lebronto-ih1513-602/706595</t>
         </is>
       </c>
       <c r="M27" t="inlineStr"/>
@@ -14142,7 +13803,7 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -14157,10 +13818,14 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
-        </is>
-      </c>
-      <c r="H28" t="inlineStr"/>
+          <t>Nike LeBron XXIII BOYS GRADE SCHOOL • BLACK/BLACK/MEDIUM ASH</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
       <c r="I28" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -14172,11 +13837,11 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/V3596003.html</t>
         </is>
       </c>
       <c r="M28" t="inlineStr"/>
@@ -14185,7 +13850,7 @@
         <v>12</v>
       </c>
       <c r="P28" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="Q28" t="inlineStr"/>
     </row>
@@ -14203,7 +13868,7 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -14218,14 +13883,10 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Nike Sabrina 3 MENS • YELLOW STRIKE/APPLE GREEN/PALE YELLOW</t>
-        </is>
-      </c>
-      <c r="H29" t="inlineStr">
-        <is>
-          <t>basketball</t>
-        </is>
-      </c>
+          <t>Nike Little Posite Pro BOYS GRADE SCHOOL • UNIVERSITY BLUE/WHITE/MIDNIGHT NAVY</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
       <c r="I29" t="inlineStr">
         <is>
           <t>footlocker</t>
@@ -14237,11 +13898,11 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/R2478700.html</t>
+          <t>https://www.footlocker.com/release-calendar/nike/Q7230400.html</t>
         </is>
       </c>
       <c r="M29" t="inlineStr"/>
@@ -14250,7 +13911,7 @@
         <v>12</v>
       </c>
       <c r="P29" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="Q29" t="inlineStr"/>
     </row>
@@ -14283,18 +13944,22 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Nike SB Ishod Apparel Collection</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr"/>
+          <t>Nike Sabrina 3 MENS • YELLOW STRIKE/APPLE GREEN/PALE YELLOW</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>basketball</t>
+        </is>
+      </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>footlocker</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch</t>
+          <t>https://www.footlocker.com/release-calendar.html</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -14302,7 +13967,7 @@
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>/launch/t/nike-sb-ishod-apparel-collection-static</t>
+          <t>https://www.footlocker.com/release-calendar/nike/R2478700.html</t>
         </is>
       </c>
       <c r="M30" t="inlineStr"/>
@@ -16612,7 +16277,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Finesse x ASICS GEL-CUMULUS 16 'Desert Rose' From £ 165</t>
+          <t>ASICS Gel-kayano 14 'Olive' From £ 165</t>
         </is>
       </c>
       <c r="H67" t="inlineStr"/>
@@ -16631,7 +16296,7 @@
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/asics-gel-cumulus-16-finesse-desert-rose-1203b003-200/668694</t>
+          <t>https://thedropdate.com/sneakers/asics-gel-kayano-14-white-1203a537-111/705592</t>
         </is>
       </c>
       <c r="M67" t="inlineStr"/>
@@ -16668,12 +16333,12 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>New Balance 993 Made in USA 'Passion Fruit' From £ 205</t>
+          <t>Finesse x ASICS GEL-CUMULUS 16 'Desert Rose' From £ 165</t>
         </is>
       </c>
       <c r="H68" t="inlineStr"/>
@@ -16692,7 +16357,7 @@
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-993-made-in-usa-passion-fruit-u9934ja/705132</t>
+          <t>https://thedropdate.com/sneakers/asics-gel-cumulus-16-finesse-desert-rose-1203b003-200/668694</t>
         </is>
       </c>
       <c r="M68" t="inlineStr"/>
@@ -16729,12 +16394,12 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 ’07 'Cherry Blossom' From £ 120</t>
+          <t>CAYL x New Balance M10L 'Black Ink' From £ 140</t>
         </is>
       </c>
       <c r="H69" t="inlineStr"/>
@@ -16753,13 +16418,13 @@
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nikes-air-force-1-07-spring-flowers-iq3472-298/669922</t>
+          <t>https://thedropdate.com/sneakers/new-balance-m10l-blue-mtm10lcl/671644</t>
         </is>
       </c>
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P69" t="n">
         <v>50</v>
@@ -16775,7 +16440,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -16790,19 +16455,15 @@
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Nike Air Max 95 'Paisley Bandana' From £ 180</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>hot-model, running</t>
-        </is>
-      </c>
+          <t>CAYL x New Balance UTRNCA 'Slate Grey' From £ 155</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
       <c r="I70" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -16818,13 +16479,13 @@
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-air-max-95-paisley-bandana-iq0620-100/705853</t>
+          <t>https://thedropdate.com/sneakers/cayl-x-new-balance-utrnv11-slate-grey-utrnca/705387</t>
         </is>
       </c>
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="P70" t="n">
         <v>50</v>
@@ -16833,14 +16494,14 @@
     </row>
     <row r="71">
       <c r="A71" s="14" t="n">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="B71" t="n">
         <v>0</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -16855,27 +16516,23 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>New Balance</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Mar 13 Kobe 3 Low Protro Pink Quartz</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>hot-model, basketball</t>
-        </is>
-      </c>
+          <t>New Balance 993 Made in USA 'Passion Fruit' From £ 205</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
       <c r="I71" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K71" t="n">
@@ -16883,13 +16540,13 @@
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>/launch/t/kobe-3-low-protro-pink-quartz</t>
+          <t>https://thedropdate.com/sneakers/new-balance-993-made-in-usa-passion-fruit-u9934ja/705132</t>
         </is>
       </c>
       <c r="M71" t="inlineStr"/>
       <c r="N71" t="inlineStr"/>
       <c r="O71" t="n">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="P71" t="n">
         <v>50</v>
@@ -16898,7 +16555,7 @@
     </row>
     <row r="72">
       <c r="A72" s="14" t="n">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="B72" t="n">
         <v>0</v>
@@ -16925,7 +16582,7 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Nike Air Force 1 Low 'Asparagus &amp; Chlorophyll' From £ 118</t>
+          <t>Nike Air Force 1 ’07 'Cherry Blossom' From £ 120</t>
         </is>
       </c>
       <c r="H72" t="inlineStr"/>
@@ -16944,7 +16601,7 @@
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-air-force-1-low-io5011-300/704355</t>
+          <t>https://thedropdate.com/sneakers/nikes-air-force-1-07-spring-flowers-iq3472-298/669922</t>
         </is>
       </c>
       <c r="M72" t="inlineStr"/>
@@ -16959,14 +16616,14 @@
     </row>
     <row r="73">
       <c r="A73" s="14" t="n">
-        <v>46094</v>
+        <v>46093</v>
       </c>
       <c r="B73" t="n">
         <v>0</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -16986,12 +16643,12 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Veneda Carter x Nike Air Max Muse 'White &amp; Racer Blue' From £ 145</t>
+          <t>Nike Air Max 95 'Paisley Bandana' From £ 180</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>running</t>
+          <t>hot-model, running</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -17009,13 +16666,13 @@
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/veneda-carter-x-nike-air-max-muse-white-racer-blue-hv9929-100/700942</t>
+          <t>https://thedropdate.com/sneakers/nike-air-max-95-paisley-bandana-iq0620-100/705853</t>
         </is>
       </c>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="P73" t="n">
         <v>50</v>
@@ -17024,14 +16681,14 @@
     </row>
     <row r="74">
       <c r="A74" s="14" t="n">
-        <v>46095</v>
+        <v>46093</v>
       </c>
       <c r="B74" t="n">
         <v>0</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -17046,19 +16703,15 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Air Jordan 13 Retro 'True Red' - 2026 From £ 185</t>
-        </is>
-      </c>
-      <c r="H74" t="inlineStr">
-        <is>
-          <t>hot-model, retro</t>
-        </is>
-      </c>
+          <t>NikeSKIMS Rift Mesh 'Black' From £ 145</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr"/>
       <c r="I74" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -17074,13 +16727,13 @@
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/air-jordan-13-retro-true-red-2026-414571-102/705921</t>
+          <t>https://thedropdate.com/sneakers/skims-x-nike-air-rift-black-io7694-001/700295</t>
         </is>
       </c>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="P74" t="n">
         <v>50</v>
@@ -17089,7 +16742,7 @@
     </row>
     <row r="75">
       <c r="A75" s="14" t="n">
-        <v>46095</v>
+        <v>46093</v>
       </c>
       <c r="B75" t="n">
         <v>0</v>
@@ -17111,19 +16764,15 @@
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Air Jordan 9 Retro 'Flint Grey' - 2026 From £ 189</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr">
-        <is>
-          <t>retro</t>
-        </is>
-      </c>
+          <t>NikeSKIMS Rift Mesh 'Light Bone' From £ 145</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr"/>
       <c r="I75" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -17139,7 +16788,7 @@
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/air-jordan-9-retro-flint-grey-and-french-blue-hv4794-100/701944</t>
+          <t>https://thedropdate.com/sneakers/nikeskims-rift-mesh-light-bone-io7694-002/706596</t>
         </is>
       </c>
       <c r="M75" t="inlineStr"/>
@@ -17154,79 +16803,75 @@
     </row>
     <row r="76">
       <c r="A76" s="14" t="n">
-        <v>46095</v>
+        <v>46093</v>
       </c>
       <c r="B76" t="n">
         <v>0</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Watch</t>
+          <t>Low Priority</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Mar 14 Infant/Toddler Shoes Jordan 13 Retro</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>hot-model, retro</t>
-        </is>
-      </c>
+          <t>NikeSKIMS Rift Mesh 'Velvet Brown' From £ 145</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
       <c r="I76" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K76" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
+          <t>https://thedropdate.com/sneakers/skims-x-nike-air-rift-velvet-brown-io7694-200/700297</t>
         </is>
       </c>
       <c r="M76" t="inlineStr"/>
       <c r="N76" t="inlineStr"/>
       <c r="O76" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="P76" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="Q76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="14" t="n">
-        <v>46095</v>
+        <v>46094</v>
       </c>
       <c r="B77" t="n">
         <v>0</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -17241,19 +16886,15 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Travis Scott x Air Jordan Jumpman Jack 'Green Spark' From £ 185</t>
-        </is>
-      </c>
-      <c r="H77" t="inlineStr">
-        <is>
-          <t>collab</t>
-        </is>
-      </c>
+          <t>adidas Anthony Edwards 2 'Georgia Bulldogs' From £ 120</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr"/>
       <c r="I77" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -17269,13 +16910,13 @@
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/air-jordan-x-travis-scott-jumpman-jack-green-spark-im9113-300/704688</t>
+          <t>https://thedropdate.com/sneakers/adidas-anthony-edwards-2-georgia-bulldogs-jq9497/706523</t>
         </is>
       </c>
       <c r="M77" t="inlineStr"/>
       <c r="N77" t="inlineStr"/>
       <c r="O77" t="n">
-        <v>30</v>
+        <v>4</v>
       </c>
       <c r="P77" t="n">
         <v>50</v>
@@ -17284,7 +16925,7 @@
     </row>
     <row r="78">
       <c r="A78" s="14" t="n">
-        <v>46099</v>
+        <v>46094</v>
       </c>
       <c r="B78" t="n">
         <v>0</v>
@@ -17306,17 +16947,17 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Mar 18 Air Jordan 1 Low OG Sail and Coconut Milk</t>
+          <t>Mar 13 Kobe 3 Low Protro Pink Quartz</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>hot-model</t>
+          <t>hot-model, basketball</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -17334,7 +16975,7 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
+          <t>/launch/t/kobe-3-low-protro-pink-quartz</t>
         </is>
       </c>
       <c r="M78" t="inlineStr"/>
@@ -17349,7 +16990,7 @@
     </row>
     <row r="79">
       <c r="A79" s="14" t="n">
-        <v>46099</v>
+        <v>46094</v>
       </c>
       <c r="B79" t="n">
         <v>0</v>
@@ -17371,12 +17012,12 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>One Piece x Crocs Classic Clog 'Zoro'</t>
+          <t>Nike Air Force 1 Low 'Asparagus &amp; Chlorophyll' From £ 118</t>
         </is>
       </c>
       <c r="H79" t="inlineStr"/>
@@ -17395,13 +17036,13 @@
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-zoro-212953-90h/706159</t>
+          <t>https://thedropdate.com/sneakers/nike-air-force-1-low-io5011-300/704355</t>
         </is>
       </c>
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P79" t="n">
         <v>50</v>
@@ -17410,7 +17051,7 @@
     </row>
     <row r="80">
       <c r="A80" s="14" t="n">
-        <v>46100</v>
+        <v>46094</v>
       </c>
       <c r="B80" t="n">
         <v>0</v>
@@ -17432,15 +17073,19 @@
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>New Balance 991v1 Made in UK 'Oyster Grey' From £ 220</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
+          <t>Veneda Carter x Nike Air Max Muse 'White &amp; Racer Blue' From £ 145</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>running</t>
+        </is>
+      </c>
       <c r="I80" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -17456,13 +17101,13 @@
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-991v1-made-in-uk-oyster-grey-m991cr1/706155</t>
+          <t>https://thedropdate.com/sneakers/veneda-carter-x-nike-air-max-muse-white-racer-blue-hv9929-100/700942</t>
         </is>
       </c>
       <c r="M80" t="inlineStr"/>
       <c r="N80" t="inlineStr"/>
       <c r="O80" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P80" t="n">
         <v>50</v>
@@ -17471,14 +17116,14 @@
     </row>
     <row r="81">
       <c r="A81" s="14" t="n">
-        <v>46101</v>
+        <v>46095</v>
       </c>
       <c r="B81" t="n">
         <v>0</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -17493,17 +17138,17 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Nike First Sight Noir WMNS 'Black' From £ 110</t>
+          <t>Air Jordan 13 Retro 'True Red' - 2026 From £ 185</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>women</t>
+          <t>hot-model, retro</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -17521,13 +17166,13 @@
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-first-sight-noir-wmns-black-hq2409-001/706328</t>
+          <t>https://thedropdate.com/sneakers/air-jordan-13-retro-true-red-2026-414571-102/705921</t>
         </is>
       </c>
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="P81" t="n">
         <v>50</v>
@@ -17536,7 +17181,7 @@
     </row>
     <row r="82">
       <c r="A82" s="14" t="n">
-        <v>46107</v>
+        <v>46095</v>
       </c>
       <c r="B82" t="n">
         <v>0</v>
@@ -17558,15 +17203,19 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>One Piece x Crocs Classic Clog 'Thousand Sunny'</t>
-        </is>
-      </c>
-      <c r="H82" t="inlineStr"/>
+          <t>Air Jordan 9 Retro 'Flint Grey' - 2026 From £ 189</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>retro</t>
+        </is>
+      </c>
       <c r="I82" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -17582,13 +17231,13 @@
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-thousand-sunny-212126-90h/706160</t>
+          <t>https://thedropdate.com/sneakers/air-jordan-9-retro-flint-grey-and-french-blue-hv4794-100/701944</t>
         </is>
       </c>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="P82" t="n">
         <v>50</v>
@@ -17597,75 +17246,79 @@
     </row>
     <row r="83">
       <c r="A83" s="14" t="n">
-        <v>46107</v>
+        <v>46095</v>
       </c>
       <c r="B83" t="n">
         <v>0</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Low Priority</t>
+          <t>Watch</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>New Balance</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>New Balance 1890 'Star Burst' From £ 160</t>
-        </is>
-      </c>
-      <c r="H83" t="inlineStr"/>
+          <t>Mar 14 Infant/Toddler Shoes Jordan 13 Retro</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>hot-model, retro</t>
+        </is>
+      </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>thedropdate</t>
+          <t>playwright-linkscan</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/releases</t>
+          <t>https://www.nike.com/launch/upcoming</t>
         </is>
       </c>
       <c r="K83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/new-balance-1890-black-yellow-u18903rb/705946</t>
+          <t>/launch/t/air-jordan-13-retro-white-and-university-red</t>
         </is>
       </c>
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="P83" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="Q83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="14" t="n">
-        <v>46108</v>
+        <v>46095</v>
       </c>
       <c r="B84" t="n">
         <v>0</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -17680,23 +17333,27 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Mar 27 Baby/Toddler Shoes Nike Little Posite Pro</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
+          <t>Travis Scott x Air Jordan Jumpman Jack 'Green Spark' From £ 185</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>collab</t>
+        </is>
+      </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K84" t="n">
@@ -17704,13 +17361,13 @@
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>/launch/t/air-foamposite-pro-university-blue-and-white</t>
+          <t>https://thedropdate.com/sneakers/air-jordan-x-travis-scott-jumpman-jack-green-spark-im9113-300/704688</t>
         </is>
       </c>
       <c r="M84" t="inlineStr"/>
       <c r="N84" t="inlineStr"/>
       <c r="O84" t="n">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="P84" t="n">
         <v>50</v>
@@ -17719,14 +17376,14 @@
     </row>
     <row r="85">
       <c r="A85" s="14" t="n">
-        <v>46109</v>
+        <v>46097</v>
       </c>
       <c r="B85" t="n">
         <v>0</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>MED</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17741,19 +17398,15 @@
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Air Jordan</t>
+          <t>Nike</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Air Jordan 3 'Spring Is In The Air' From £ 190</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>hot-model</t>
-        </is>
-      </c>
+          <t>Jacquemus x Nike Moon Shoe SP 'Fauna Brown' From £ 163</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr"/>
       <c r="I85" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -17769,13 +17422,13 @@
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/air-jordan-3-spring-is-in-the-air-if4396-100/703366</t>
+          <t>https://thedropdate.com/sneakers/jacquemus-x-nike-moon-shoe-sp-fauna-brown-hv8547-200/705860</t>
         </is>
       </c>
       <c r="M85" t="inlineStr"/>
       <c r="N85" t="inlineStr"/>
       <c r="O85" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="P85" t="n">
         <v>50</v>
@@ -17784,14 +17437,14 @@
     </row>
     <row r="86">
       <c r="A86" s="14" t="n">
-        <v>46113</v>
+        <v>46097</v>
       </c>
       <c r="B86" t="n">
         <v>0</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17811,18 +17464,22 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
-        </is>
-      </c>
-      <c r="H86" t="inlineStr"/>
+          <t>Jacquemus x Nike Moon Shoe SP 'Soft Pearl' From £ 163</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>exclusive</t>
+        </is>
+      </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>footlocker</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar.html</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K86" t="n">
@@ -17830,13 +17487,13 @@
       </c>
       <c r="L86" t="inlineStr">
         <is>
-          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+          <t>https://thedropdate.com/sneakers/jacquemus-x-nike-moon-shoe-sp-soft-pearl-hv8547-002/705859</t>
         </is>
       </c>
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="P86" t="n">
         <v>50</v>
@@ -17845,7 +17502,7 @@
     </row>
     <row r="87">
       <c r="A87" s="14" t="n">
-        <v>46113</v>
+        <v>46098</v>
       </c>
       <c r="B87" t="n">
         <v>0</v>
@@ -17857,7 +17514,7 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>HIGH</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -17867,15 +17524,19 @@
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Pregame Mule 'Light Smoke Grey' From £ 80</t>
-        </is>
-      </c>
-      <c r="H87" t="inlineStr"/>
+          <t>adidas Hyperboost Edge 'White &amp; Pure Ruby' From £ 170</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>exclusive</t>
+        </is>
+      </c>
       <c r="I87" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -17887,33 +17548,33 @@
         </is>
       </c>
       <c r="K87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L87" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mule-light-smoke-grey-hq4307-003/647220</t>
+          <t>https://thedropdate.com/sneakers/adidas-hyperboost-edge-white-pure-ruby-ki1913/706498</t>
         </is>
       </c>
       <c r="M87" t="inlineStr"/>
       <c r="N87" t="inlineStr"/>
       <c r="O87" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P87" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="Q87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="14" t="n">
-        <v>46113</v>
+        <v>46098</v>
       </c>
       <c r="B88" t="n">
         <v>0</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17928,15 +17589,19 @@
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Nike Mind 001 Slide 'Black' From £ 80</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>Dashawn Jordan x Nike SB Dunk Low 'Bright Spruce' From £ 120</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>hot-model</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -17952,13 +17617,13 @@
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-mind-001-slide-black-hq4307-001/672235</t>
+          <t>https://thedropdate.com/sneakers/nike-sb-x-dashawn-jordan-dunk-low-black-bright-spruce-ib6208-200/703258</t>
         </is>
       </c>
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="P88" t="n">
         <v>50</v>
@@ -17967,7 +17632,7 @@
     </row>
     <row r="89">
       <c r="A89" s="14" t="n">
-        <v>46113</v>
+        <v>46099</v>
       </c>
       <c r="B89" t="n">
         <v>0</v>
@@ -17989,19 +17654,15 @@
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Nike Mind 001 WMNS Pregame Mules 'Black' From £ 80</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr">
-        <is>
-          <t>women</t>
-        </is>
-      </c>
+          <t>adidas Adizero Dropset Elite 'Solar Red' From £ 230</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
       <c r="I89" t="inlineStr">
         <is>
           <t>thedropdate</t>
@@ -18017,13 +17678,13 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mules-hq4309-001/678052</t>
+          <t>https://thedropdate.com/sneakers/adidas-adizero-dropset-elite-solar-red-la6218/706499</t>
         </is>
       </c>
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="n">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="P89" t="n">
         <v>50</v>
@@ -18032,14 +17693,14 @@
     </row>
     <row r="90">
       <c r="A90" s="14" t="n">
-        <v>46115</v>
+        <v>46099</v>
       </c>
       <c r="B90" t="n">
         <v>0</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>LOW</t>
+          <t>MED</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18054,27 +17715,27 @@
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nike</t>
+          <t>Air Jordan</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Apr 3 Basketball Shoes LeBron XXIII Elite "Good Intentions"</t>
+          <t>Air Jordan 3 'Spring Is In The Air' From £ 189</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>basketball</t>
+          <t>hot-model</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>playwright-linkscan</t>
+          <t>thedropdate</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>https://www.nike.com/launch/upcoming</t>
+          <t>https://thedropdate.com/releases</t>
         </is>
       </c>
       <c r="K90" t="n">
@@ -18082,18 +17743,640 @@
       </c>
       <c r="L90" t="inlineStr">
         <is>
-          <t>/launch/t/lebron-xxiii-elite-good-intentions-hyper-pink-and-black</t>
+          <t>https://thedropdate.com/sneakers/air-jordan-3-spring-is-in-the-air-if4396-100/703366</t>
         </is>
       </c>
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="P90" t="n">
         <v>50</v>
       </c>
       <c r="Q90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" s="14" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B91" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Air Jordan</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Mar 18 Air Jordan 1 Low OG Sail and Coconut Milk</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>hot-model</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>playwright-linkscan</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>https://www.nike.com/launch/upcoming</t>
+        </is>
+      </c>
+      <c r="K91" t="n">
+        <v>1</v>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>/launch/t/air-jordan-1-low-og-sail-and-coconut-milk</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr"/>
+      <c r="N91" t="inlineStr"/>
+      <c r="O91" t="n">
+        <v>22</v>
+      </c>
+      <c r="P91" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" s="14" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B92" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Crocs</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>One Piece x Crocs Classic Clog 'Zoro'</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J92" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K92" t="n">
+        <v>1</v>
+      </c>
+      <c r="L92" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-zoro-212953-90h/706159</t>
+        </is>
+      </c>
+      <c r="M92" t="inlineStr"/>
+      <c r="N92" t="inlineStr"/>
+      <c r="O92" t="n">
+        <v>4</v>
+      </c>
+      <c r="P92" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" s="14" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B93" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>New Balance</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>New Balance 991v1 Made in UK 'Oyster Grey' From £ 220</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr"/>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K93" t="n">
+        <v>1</v>
+      </c>
+      <c r="L93" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/new-balance-991v1-made-in-uk-oyster-grey-m991cr1/706155</t>
+        </is>
+      </c>
+      <c r="M93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
+      <c r="O93" t="n">
+        <v>4</v>
+      </c>
+      <c r="P93" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" s="14" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B94" t="n">
+        <v>0</v>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Nike First Sight Noir WMNS 'Black' From £ 110</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K94" t="n">
+        <v>1</v>
+      </c>
+      <c r="L94" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/nike-first-sight-noir-wmns-black-hq2409-001/706328</t>
+        </is>
+      </c>
+      <c r="M94" t="inlineStr"/>
+      <c r="N94" t="inlineStr"/>
+      <c r="O94" t="n">
+        <v>12</v>
+      </c>
+      <c r="P94" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" s="14" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B95" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Crocs</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>One Piece x Crocs Classic Clog 'Thousand Sunny'</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J95" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K95" t="n">
+        <v>1</v>
+      </c>
+      <c r="L95" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/one-piece-x-crocs-classic-clog-thousand-sunny-212126-90h/706160</t>
+        </is>
+      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
+      <c r="O95" t="n">
+        <v>4</v>
+      </c>
+      <c r="P95" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" s="14" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B96" t="n">
+        <v>0</v>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>New Balance</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>New Balance 1890 'Star Burst' From £ 160</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr"/>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J96" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K96" t="n">
+        <v>1</v>
+      </c>
+      <c r="L96" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/new-balance-1890-black-yellow-u18903rb/705946</t>
+        </is>
+      </c>
+      <c r="M96" t="inlineStr"/>
+      <c r="N96" t="inlineStr"/>
+      <c r="O96" t="n">
+        <v>4</v>
+      </c>
+      <c r="P96" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" s="14" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B97" t="n">
+        <v>0</v>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Mule MENS • LIGHT SMOKE GREY/CHROME/PHOTON DUST</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr"/>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>footlocker</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar.html</t>
+        </is>
+      </c>
+      <c r="K97" t="n">
+        <v>1</v>
+      </c>
+      <c r="L97" t="inlineStr">
+        <is>
+          <t>https://www.footlocker.com/release-calendar/nike/Q4307003.html</t>
+        </is>
+      </c>
+      <c r="M97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="O97" t="n">
+        <v>12</v>
+      </c>
+      <c r="P97" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" s="14" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B98" t="n">
+        <v>0</v>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>HIGH</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Pregame Mule 'Light Smoke Grey' From £ 80</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K98" t="n">
+        <v>2</v>
+      </c>
+      <c r="L98" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mule-light-smoke-grey-hq4307-003/647220</t>
+        </is>
+      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
+      <c r="O98" t="n">
+        <v>12</v>
+      </c>
+      <c r="P98" t="n">
+        <v>70</v>
+      </c>
+      <c r="Q98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" s="14" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B99" t="n">
+        <v>0</v>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 Slide 'Black' From £ 80</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J99" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K99" t="n">
+        <v>1</v>
+      </c>
+      <c r="L99" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/nike-mind-001-slide-black-hq4307-001/672235</t>
+        </is>
+      </c>
+      <c r="M99" t="inlineStr"/>
+      <c r="N99" t="inlineStr"/>
+      <c r="O99" t="n">
+        <v>12</v>
+      </c>
+      <c r="P99" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q99" t="inlineStr"/>
+    </row>
+    <row r="100">
+      <c r="A100" s="14" t="n">
+        <v>46113</v>
+      </c>
+      <c r="B100" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>LOW</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>MED</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>Low Priority</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Nike</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Nike Mind 001 WMNS Pregame Mules 'Black' From £ 80</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>women</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>thedropdate</t>
+        </is>
+      </c>
+      <c r="J100" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/releases</t>
+        </is>
+      </c>
+      <c r="K100" t="n">
+        <v>1</v>
+      </c>
+      <c r="L100" t="inlineStr">
+        <is>
+          <t>https://thedropdate.com/sneakers/nike-mind-001-pregame-mules-hq4309-001/678052</t>
+        </is>
+      </c>
+      <c r="M100" t="inlineStr"/>
+      <c r="N100" t="inlineStr"/>
+      <c r="O100" t="n">
+        <v>12</v>
+      </c>
+      <c r="P100" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q100" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -18275,7 +18558,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>80</v>
+        <v>93</v>
       </c>
     </row>
     <row r="4">
@@ -18285,7 +18568,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5"/>
@@ -18303,7 +18586,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="8">
@@ -18323,7 +18606,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
     <row r="10">
@@ -18333,23 +18616,23 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Crocs</t>
+          <t>Adidas</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Puma</t>
+          <t>ASICS</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -18359,21 +18642,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>ASICS</t>
+          <t>Crocs</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Adidas</t>
+          <t>Puma</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -18421,7 +18704,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -18431,7 +18714,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>71</v>
+        <v>79</v>
       </c>
     </row>
     <row r="22"/>
@@ -18459,7 +18742,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
     </row>
     <row r="26">
